--- a/ResultatWimbeldon.xlsx
+++ b/ResultatWimbeldon.xlsx
@@ -1,33 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/iker/Code/TFG/Me-vs.-IBM/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ikerr\Code\TFG\Program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBF6CAE5-775F-C74D-A426-811534E3447B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EACAAD8-24BF-443E-AB6F-088A7576F703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="620" windowWidth="25420" windowHeight="16300" activeTab="4" xr2:uid="{0ED45994-5EFE-4A4E-8BA9-C3AA32741888}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25420" windowHeight="16300" activeTab="3" xr2:uid="{0ED45994-5EFE-4A4E-8BA9-C3AA32741888}"/>
   </bookViews>
   <sheets>
     <sheet name="Ronda 1" sheetId="1" r:id="rId1"/>
-    <sheet name="Ronda 2" sheetId="2" r:id="rId2"/>
-    <sheet name="Ronda 3" sheetId="3" r:id="rId3"/>
-    <sheet name="Ronda 4" sheetId="4" r:id="rId4"/>
-    <sheet name="Quarts" sheetId="5" r:id="rId5"/>
-    <sheet name="Semi" sheetId="6" r:id="rId6"/>
-    <sheet name="Final" sheetId="7" r:id="rId7"/>
-    <sheet name="Resultats" sheetId="8" r:id="rId8"/>
+    <sheet name="Sheet6" sheetId="14" r:id="rId2"/>
+    <sheet name="Ronda 2" sheetId="2" r:id="rId3"/>
+    <sheet name="Ronda 3" sheetId="3" r:id="rId4"/>
+    <sheet name="Ronda 4" sheetId="4" r:id="rId5"/>
+    <sheet name="Quarts" sheetId="5" r:id="rId6"/>
+    <sheet name="Semi" sheetId="6" r:id="rId7"/>
+    <sheet name="Final" sheetId="7" r:id="rId8"/>
+    <sheet name="Resultats" sheetId="8" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ronda 1'!$A$1:$G$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Ronda 2'!$A$1:$G$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Ronda 3'!$A$1:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Ronda 2'!$A$1:$G$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ronda 3'!$A$1:$G$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="87" r:id="rId10"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -48,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="247">
   <si>
     <t>Jugador 1</t>
   </si>
@@ -675,6 +679,120 @@
   </si>
   <si>
     <t>Iker V3 % acert:</t>
+  </si>
+  <si>
+    <t>Iker Winner</t>
+  </si>
+  <si>
+    <t>Correcte</t>
+  </si>
+  <si>
+    <t>POPYRIN</t>
+  </si>
+  <si>
+    <t>MEDVEDEV</t>
+  </si>
+  <si>
+    <t>RUNE</t>
+  </si>
+  <si>
+    <t>GRIEKSPOOR</t>
+  </si>
+  <si>
+    <t>BERGS</t>
+  </si>
+  <si>
+    <t>TSITSIPAS</t>
+  </si>
+  <si>
+    <t>RIEDI</t>
+  </si>
+  <si>
+    <t>BERRETTINI</t>
+  </si>
+  <si>
+    <t>ZVEREV</t>
+  </si>
+  <si>
+    <t>CERUNDOLO</t>
+  </si>
+  <si>
+    <t>SAFIULLIN</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>ETCHEVERRY</t>
+  </si>
+  <si>
+    <t>HALYS</t>
+  </si>
+  <si>
+    <t>LOFFHAGEN</t>
+  </si>
+  <si>
+    <t>SHAPOVALOV</t>
+  </si>
+  <si>
+    <t>MEDJEDOVIC</t>
+  </si>
+  <si>
+    <t>HUMBERT</t>
+  </si>
+  <si>
+    <t>BUBLIK</t>
+  </si>
+  <si>
+    <t>BASILASHVILI</t>
+  </si>
+  <si>
+    <t>MICHELSEN</t>
+  </si>
+  <si>
+    <t>ARNALDI</t>
+  </si>
+  <si>
+    <t>Guanyador de les prediccions</t>
+  </si>
+  <si>
+    <t>Qui prediu millor</t>
+  </si>
+  <si>
+    <t>Count of Guanyador de les prediccions</t>
+  </si>
+  <si>
+    <t>Empat</t>
+  </si>
+  <si>
+    <t>Guanyem</t>
+  </si>
+  <si>
+    <t>Perdem</t>
+  </si>
+  <si>
+    <t>Probabilitat A Model Propi</t>
+  </si>
+  <si>
+    <t>Probabilitat B Model Propi</t>
+  </si>
+  <si>
+    <t>Probabilitat A IBM</t>
+  </si>
+  <si>
+    <t>Probabilitat B IBM</t>
+  </si>
+  <si>
+    <t>Partit</t>
+  </si>
+  <si>
+    <t>Acert IBM</t>
+  </si>
+  <si>
+    <t>Acert Iker</t>
+  </si>
+  <si>
+    <t>THOMSON</t>
   </si>
 </sst>
 </file>
@@ -862,7 +980,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -882,16 +1000,55 @@
     <xf numFmtId="10" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="29">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF92D050"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -926,6 +1083,13 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFF5050"/>
         </patternFill>
       </fill>
@@ -934,6 +1098,122 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -976,8 +1256,2593 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="693340096"/>
+        <c:axId val="693327136"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="693340096"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="693327136"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="693327136"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="693340096"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[ResultatWimbeldon.xlsx]Sheet6!PivotTable48</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Count of Guanyador de les prediccions</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet6!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet6!$A$4:$A$6</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>Empat</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Guanyem</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Perdem</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet6!$B$4:$B$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-79AD-4526-905E-86909A91E942}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="693352096"/>
+        <c:axId val="693361216"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="693352096"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="693361216"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="693361216"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="693352096"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>367393</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>11794</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>984250</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>33565</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2E80DA1-27BE-9393-BECF-8BC8B2B153E8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1978025</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>555625</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AED3CA1E-E103-9FDE-21CE-3957D8440473}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Iker Ruiz" refreshedDate="46026.953020949077" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="32" xr:uid="{71E54D72-922A-494A-9371-400A1EE1345E}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:P33" sheet="Ronda 2"/>
+  </cacheSource>
+  <cacheFields count="16">
+    <cacheField name="Jugador 1" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Jugador 2" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Probabilitat 1" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="6" maxValue="90"/>
+    </cacheField>
+    <cacheField name="Probabilitat 2" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="10" maxValue="94"/>
+    </cacheField>
+    <cacheField name="Ganador" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="IBM Winner" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Acert IBM" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
+    </cacheField>
+    <cacheField name="Iker Winner" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Acert Iker" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
+    </cacheField>
+    <cacheField name="Probabilitat A Model Propi" numFmtId="10">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="6.9466999999999945E-2" maxValue="0.96246200000000004"/>
+    </cacheField>
+    <cacheField name="Probabilitat B Model Propi" numFmtId="10">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.753799999999996E-2" maxValue="0.93053300000000005"/>
+    </cacheField>
+    <cacheField name="Guanyador de les prediccions" numFmtId="0">
+      <sharedItems count="3">
+        <s v="Empat"/>
+        <s v="Guanyem"/>
+        <s v="Perdem"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Qui prediu millor" numFmtId="10">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-0.35645500000000002" maxValue="0.28518999999999994"/>
+    </cacheField>
+    <cacheField name="Probabilitat A IBM" numFmtId="10">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.06" maxValue="0.9"/>
+    </cacheField>
+    <cacheField name="Probabilitat B IBM" numFmtId="10">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.1" maxValue="0.94"/>
+    </cacheField>
+    <cacheField name="Partit" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="32">
+  <r>
+    <s v="AUGER-ALIASSIME, Felix"/>
+    <s v="STRUFF, Jan-Lennard"/>
+    <n v="72"/>
+    <n v="28"/>
+    <s v="STRUFF"/>
+    <s v="AUGER-ALIASSIME"/>
+    <n v="0"/>
+    <s v="AUGER-ALIASSIME"/>
+    <n v="0"/>
+    <n v="0.69422300000000003"/>
+    <n v="0.30577699999999997"/>
+    <x v="0"/>
+    <n v="2.5776999999999939E-2"/>
+    <n v="0.72"/>
+    <n v="0.28000000000000003"/>
+    <s v="AUGER-ALIASSIME vs. STRUFF"/>
+  </r>
+  <r>
+    <s v="BORGES, Nuno"/>
+    <s v="HARRIS, Billy"/>
+    <n v="66"/>
+    <n v="34"/>
+    <s v="BORGES"/>
+    <s v="BORGES"/>
+    <n v="1"/>
+    <s v="BORGES"/>
+    <n v="1"/>
+    <n v="0.65856000000000003"/>
+    <n v="0.34143999999999997"/>
+    <x v="0"/>
+    <n v="-1.4399999999999968E-3"/>
+    <n v="0.66"/>
+    <n v="0.34"/>
+    <s v="BORGES vs. HARRIS"/>
+  </r>
+  <r>
+    <s v="COBOLLI, Flavio"/>
+    <s v="PINNINGTON JONES, Jack"/>
+    <n v="75"/>
+    <n v="25"/>
+    <s v="COBOLLI"/>
+    <s v="COBOLLI"/>
+    <n v="1"/>
+    <s v="COBOLLI"/>
+    <n v="1"/>
+    <n v="0.74198200000000003"/>
+    <n v="0.25801799999999997"/>
+    <x v="0"/>
+    <n v="-8.0179999999999696E-3"/>
+    <n v="0.75"/>
+    <n v="0.25"/>
+    <s v="COBOLLI vs. PINNINGTON JONES"/>
+  </r>
+  <r>
+    <s v="DE MINAUR, Alex"/>
+    <s v="CAZAUX, Arthur"/>
+    <n v="68"/>
+    <n v="32"/>
+    <s v="DE MINAUR"/>
+    <s v="DE MINAUR"/>
+    <n v="1"/>
+    <s v="DE MINAUR"/>
+    <n v="1"/>
+    <n v="0.96246200000000004"/>
+    <n v="3.753799999999996E-2"/>
+    <x v="0"/>
+    <n v="0.28246199999999999"/>
+    <n v="0.68"/>
+    <n v="0.32"/>
+    <s v="DE MINAUR vs. CAZAUX"/>
+  </r>
+  <r>
+    <s v="DIMITROV, Grigor"/>
+    <s v="MOUTET, Corentin"/>
+    <n v="53"/>
+    <n v="47"/>
+    <s v="DIMITROV"/>
+    <s v="DIMITROV"/>
+    <n v="1"/>
+    <s v="DIMITROV"/>
+    <n v="1"/>
+    <n v="0.63892800000000005"/>
+    <n v="0.36107199999999995"/>
+    <x v="0"/>
+    <n v="0.10892800000000002"/>
+    <n v="0.53"/>
+    <n v="0.47"/>
+    <s v="DIMITROV vs. MOUTET"/>
+  </r>
+  <r>
+    <s v="DRAPER, Jack"/>
+    <s v="CILIC, Marin"/>
+    <n v="85"/>
+    <n v="15"/>
+    <s v="CILIC"/>
+    <s v="DRAPER"/>
+    <n v="0"/>
+    <s v="DRAPER"/>
+    <n v="0"/>
+    <n v="0.82929399999999998"/>
+    <n v="0.17070600000000002"/>
+    <x v="0"/>
+    <n v="2.070600000000003E-2"/>
+    <n v="0.85"/>
+    <n v="0.15"/>
+    <s v="DRAPER vs. CILIC"/>
+  </r>
+  <r>
+    <s v="EVANS, Daniel"/>
+    <s v="DJOKOVIC, Novak"/>
+    <n v="13"/>
+    <n v="87"/>
+    <s v="DJOKOVIC"/>
+    <s v="DJOKOVIC"/>
+    <n v="1"/>
+    <s v="DJOKOVIC"/>
+    <n v="1"/>
+    <n v="6.9466999999999945E-2"/>
+    <n v="0.93053300000000005"/>
+    <x v="0"/>
+    <n v="6.0533000000000059E-2"/>
+    <n v="0.13"/>
+    <n v="0.87"/>
+    <s v="EVANS vs. DJOKOVIC"/>
+  </r>
+  <r>
+    <s v="FERY, Arthur"/>
+    <s v="DARDERI, Luciano"/>
+    <n v="24"/>
+    <n v="76"/>
+    <s v="DARDERI"/>
+    <s v="DARDERI"/>
+    <n v="1"/>
+    <s v="DARDERI"/>
+    <n v="1"/>
+    <n v="0.46909000000000001"/>
+    <n v="0.53090999999999999"/>
+    <x v="0"/>
+    <n v="-0.22909000000000002"/>
+    <n v="0.24"/>
+    <n v="0.76"/>
+    <s v="FERY vs. DARDERI"/>
+  </r>
+  <r>
+    <s v="FONSECA, Joao"/>
+    <s v="BROOKSBY, Jenson"/>
+    <n v="63"/>
+    <n v="37"/>
+    <s v="FONSECA"/>
+    <s v="FONSECA"/>
+    <n v="1"/>
+    <s v="FONSECA"/>
+    <n v="1"/>
+    <n v="0.686145"/>
+    <n v="0.313855"/>
+    <x v="0"/>
+    <n v="5.6145E-2"/>
+    <n v="0.63"/>
+    <n v="0.37"/>
+    <s v="FONSECA vs. BROOKSBY"/>
+  </r>
+  <r>
+    <s v="FRITZ, Taylor"/>
+    <s v="DIALLO, Gabriel"/>
+    <n v="72"/>
+    <n v="28"/>
+    <s v="FRITZ"/>
+    <s v="FRITZ"/>
+    <n v="1"/>
+    <s v="FRITZ"/>
+    <n v="1"/>
+    <n v="0.78715099999999993"/>
+    <n v="0.21284900000000007"/>
+    <x v="0"/>
+    <n v="6.7150999999999961E-2"/>
+    <n v="0.72"/>
+    <n v="0.28000000000000003"/>
+    <s v="FRITZ vs. DIALLO"/>
+  </r>
+  <r>
+    <s v="FUCSOVICS, Marton"/>
+    <s v="MONFILS, Gael"/>
+    <n v="37"/>
+    <n v="63"/>
+    <s v="FUCSOVICS"/>
+    <s v="MONFILS"/>
+    <n v="0"/>
+    <s v="FUCSOVICS"/>
+    <n v="1"/>
+    <n v="0.53553099999999998"/>
+    <n v="0.46446900000000002"/>
+    <x v="1"/>
+    <n v="0.16553099999999998"/>
+    <n v="0.37"/>
+    <n v="0.63"/>
+    <s v="FUCSOVICS vs. MONFILS"/>
+  </r>
+  <r>
+    <s v="GARIN, Cristian"/>
+    <s v="RINDERKNECH, Arthur"/>
+    <n v="47"/>
+    <n v="53"/>
+    <s v="RINDERKNECH"/>
+    <s v="RINDERKNECH"/>
+    <n v="1"/>
+    <s v="RINDERKNECH"/>
+    <n v="1"/>
+    <n v="0.412935"/>
+    <n v="0.58706499999999995"/>
+    <x v="0"/>
+    <n v="5.7064999999999921E-2"/>
+    <n v="0.47"/>
+    <n v="0.53"/>
+    <s v="GARIN vs. RINDERKNECH"/>
+  </r>
+  <r>
+    <s v="GIRON, Marcos"/>
+    <s v="MENSIK, Jakub"/>
+    <n v="39"/>
+    <n v="61"/>
+    <s v="MENSIK"/>
+    <s v="MENSIK"/>
+    <n v="1"/>
+    <s v="MENSIK"/>
+    <n v="1"/>
+    <n v="0.41428300000000001"/>
+    <n v="0.58571700000000004"/>
+    <x v="0"/>
+    <n v="-2.4282999999999944E-2"/>
+    <n v="0.39"/>
+    <n v="0.61"/>
+    <s v="GIRON vs. MENSIK"/>
+  </r>
+  <r>
+    <s v="HOLMGREN, August"/>
+    <s v="MACHAC, Tomas"/>
+    <n v="28"/>
+    <n v="72"/>
+    <s v="HOLMGREN"/>
+    <s v="MACHAC"/>
+    <n v="0"/>
+    <s v="MACHAC"/>
+    <n v="0"/>
+    <n v="0.301927"/>
+    <n v="0.69807299999999994"/>
+    <x v="0"/>
+    <n v="2.1926999999999974E-2"/>
+    <n v="0.28000000000000003"/>
+    <n v="0.72"/>
+    <s v="HOLMGREN vs. MACHAC"/>
+  </r>
+  <r>
+    <s v="JARRY, Nicolas"/>
+    <s v="TIEN, Learner"/>
+    <n v="38"/>
+    <n v="62"/>
+    <s v="JARRY"/>
+    <s v="TIEN"/>
+    <n v="0"/>
+    <s v="JARRY"/>
+    <n v="1"/>
+    <n v="0.59473699999999996"/>
+    <n v="0.40526300000000004"/>
+    <x v="1"/>
+    <n v="0.21473699999999996"/>
+    <n v="0.38"/>
+    <n v="0.62"/>
+    <s v="JARRY vs. TIEN"/>
+  </r>
+  <r>
+    <s v="KECMANOVIC, Miomir"/>
+    <s v="DE JONG, Jesper"/>
+    <n v="62"/>
+    <n v="38"/>
+    <s v="KECMANOVIC"/>
+    <s v="KECMANOVIC"/>
+    <n v="1"/>
+    <s v="KECMANOVIC"/>
+    <n v="1"/>
+    <n v="0.72543899999999994"/>
+    <n v="0.27456100000000006"/>
+    <x v="0"/>
+    <n v="0.10543899999999995"/>
+    <n v="0.62"/>
+    <n v="0.38"/>
+    <s v="KECMANOVIC vs. DE JONG"/>
+  </r>
+  <r>
+    <s v="LEHECKA, Jiri"/>
+    <s v="BELLUCCI, Mattia"/>
+    <n v="56"/>
+    <n v="44"/>
+    <s v="BELLUCCI"/>
+    <s v="LEHECKA"/>
+    <n v="0"/>
+    <s v="LEHECKA"/>
+    <n v="0"/>
+    <n v="0.91645500000000002"/>
+    <n v="8.354499999999998E-2"/>
+    <x v="0"/>
+    <n v="-0.35645500000000002"/>
+    <n v="0.56000000000000005"/>
+    <n v="0.44"/>
+    <s v="LEHECKA vs. BELLUCCI"/>
+  </r>
+  <r>
+    <s v="MAJCHRZAK, Kamil"/>
+    <s v="QUINN, Ethan"/>
+    <n v="42"/>
+    <n v="58"/>
+    <s v="MAJCHRZAK"/>
+    <s v="QUINN"/>
+    <n v="0"/>
+    <s v="QUINN"/>
+    <n v="0"/>
+    <n v="0.48952899999999999"/>
+    <n v="0.51047100000000001"/>
+    <x v="0"/>
+    <n v="6.9529000000000007E-2"/>
+    <n v="0.42"/>
+    <n v="0.57999999999999996"/>
+    <s v="MAJCHRZAK vs. QUINN"/>
+  </r>
+  <r>
+    <s v="MANNARINO, Adrian"/>
+    <s v="ROYER, Valentin"/>
+    <n v="42"/>
+    <n v="58"/>
+    <s v="MANNARINO"/>
+    <s v="ROYER"/>
+    <n v="0"/>
+    <s v="MANNARINO"/>
+    <n v="1"/>
+    <n v="0.69118900000000005"/>
+    <n v="0.30881099999999995"/>
+    <x v="1"/>
+    <n v="0.27118900000000007"/>
+    <n v="0.42"/>
+    <n v="0.57999999999999996"/>
+    <s v="MANNARINO vs. ROYER"/>
+  </r>
+  <r>
+    <s v="MAROZSAN, Fabian"/>
+    <s v="MUNAR, Jaume"/>
+    <n v="42"/>
+    <n v="58"/>
+    <s v="MUNAR"/>
+    <s v="MUNAR"/>
+    <n v="1"/>
+    <s v="MUNAR"/>
+    <n v="1"/>
+    <n v="0.49672500000000003"/>
+    <n v="0.50327499999999992"/>
+    <x v="0"/>
+    <n v="-7.6725000000000043E-2"/>
+    <n v="0.42"/>
+    <n v="0.57999999999999996"/>
+    <s v="MAROZSAN vs. MUNAR"/>
+  </r>
+  <r>
+    <s v="MARTÍNEZ, Pedro"/>
+    <s v="NAVONE, Mariano"/>
+    <n v="55"/>
+    <n v="45"/>
+    <s v="MARTÍNEZ"/>
+    <s v="MARTÍNEZ"/>
+    <n v="1"/>
+    <s v="NAVONE"/>
+    <n v="0"/>
+    <n v="0.41036899999999998"/>
+    <n v="0.58963100000000002"/>
+    <x v="2"/>
+    <n v="-0.13963100000000006"/>
+    <n v="0.55000000000000004"/>
+    <n v="0.45"/>
+    <s v="MARTÍNEZ vs. NAVONE"/>
+  </r>
+  <r>
+    <s v="MOCHIZUKI, Shintaro"/>
+    <s v="KHACHANOV, Karen"/>
+    <n v="37"/>
+    <n v="63"/>
+    <s v="KHACHANOV"/>
+    <s v="KHACHANOV"/>
+    <n v="1"/>
+    <s v="KHACHANOV"/>
+    <n v="1"/>
+    <n v="8.4810000000000052E-2"/>
+    <n v="0.91518999999999995"/>
+    <x v="0"/>
+    <n v="0.28518999999999994"/>
+    <n v="0.37"/>
+    <n v="0.63"/>
+    <s v="MOCHIZUKI vs. KHACHANOV"/>
+  </r>
+  <r>
+    <s v="NAKASHIMA, Brandon"/>
+    <s v="OPELKA, Reilly"/>
+    <n v="55"/>
+    <n v="45"/>
+    <s v="NAKASHIMA"/>
+    <s v="NAKASHIMA"/>
+    <n v="1"/>
+    <s v="NAKASHIMA"/>
+    <n v="1"/>
+    <n v="0.63892800000000005"/>
+    <n v="0.36107199999999995"/>
+    <x v="0"/>
+    <n v="8.8928000000000007E-2"/>
+    <n v="0.55000000000000004"/>
+    <n v="0.45"/>
+    <s v="NAKASHIMA vs. OPELKA"/>
+  </r>
+  <r>
+    <s v="NORRIE, Cameron"/>
+    <s v="TIAFOE, Frances"/>
+    <n v="38"/>
+    <n v="63"/>
+    <s v="NORRIE"/>
+    <s v="TIAFOE"/>
+    <n v="0"/>
+    <s v="TIAFOE"/>
+    <n v="0"/>
+    <n v="0.44528000000000001"/>
+    <n v="0.55471999999999999"/>
+    <x v="0"/>
+    <n v="6.5280000000000005E-2"/>
+    <n v="0.38"/>
+    <n v="0.63"/>
+    <s v="NORRIE vs. TIAFOE"/>
+  </r>
+  <r>
+    <s v="OFNER, Sebastian"/>
+    <s v="PAUL, Tommy"/>
+    <n v="27"/>
+    <n v="73"/>
+    <s v="OFNER"/>
+    <s v="PAUL"/>
+    <n v="0"/>
+    <s v="PAUL"/>
+    <n v="0"/>
+    <n v="0.160053"/>
+    <n v="0.839947"/>
+    <x v="0"/>
+    <n v="-0.10994700000000002"/>
+    <n v="0.27"/>
+    <n v="0.73"/>
+    <s v="OFNER vs. PAUL"/>
+  </r>
+  <r>
+    <s v="RUBLEV, Andrey"/>
+    <s v="HARRIS, Lloyd"/>
+    <n v="77"/>
+    <n v="23"/>
+    <s v="RUBLEV"/>
+    <s v="RUBLEV"/>
+    <n v="1"/>
+    <s v="RUBLEV"/>
+    <n v="1"/>
+    <n v="0.70881400000000006"/>
+    <n v="0.29118599999999994"/>
+    <x v="0"/>
+    <n v="-6.1185999999999963E-2"/>
+    <n v="0.77"/>
+    <n v="0.23"/>
+    <s v="RUBLEV vs. HARRIS"/>
+  </r>
+  <r>
+    <s v="SHELTON, Ben"/>
+    <s v="HIJIKATA, Rinky"/>
+    <n v="68"/>
+    <n v="32"/>
+    <s v="SHELTON"/>
+    <s v="SHELTON"/>
+    <n v="1"/>
+    <s v="SHELTON"/>
+    <n v="1"/>
+    <n v="0.57423400000000002"/>
+    <n v="0.42576599999999998"/>
+    <x v="0"/>
+    <n v="-0.10576600000000003"/>
+    <n v="0.68"/>
+    <n v="0.32"/>
+    <s v="SHELTON vs. HIJIKATA"/>
+  </r>
+  <r>
+    <s v="SINNER, Jannik"/>
+    <s v="VUKIC, Aleksandar"/>
+    <n v="90"/>
+    <n v="10"/>
+    <s v="SINNER"/>
+    <s v="SINNER"/>
+    <n v="1"/>
+    <s v="SINNER"/>
+    <n v="1"/>
+    <n v="0.96193600000000001"/>
+    <n v="3.8063999999999987E-2"/>
+    <x v="0"/>
+    <n v="6.1935999999999991E-2"/>
+    <n v="0.9"/>
+    <n v="0.1"/>
+    <s v="SINNER vs. VUKIC"/>
+  </r>
+  <r>
+    <s v="SONEGO, Lorenzo"/>
+    <s v="MUSETTI, Lorenzo"/>
+    <n v="65"/>
+    <n v="35"/>
+    <s v="SONEGO"/>
+    <s v="SONEGO"/>
+    <n v="1"/>
+    <s v="SONEGO"/>
+    <n v="1"/>
+    <n v="0.61302900000000005"/>
+    <n v="0.38697099999999995"/>
+    <x v="0"/>
+    <n v="-3.6970999999999976E-2"/>
+    <n v="0.65"/>
+    <n v="0.35"/>
+    <s v="SONEGO vs. MUSETTI"/>
+  </r>
+  <r>
+    <s v="TARVET, Oliver"/>
+    <s v="ALCARAZ, Carlos"/>
+    <n v="6"/>
+    <n v="94"/>
+    <s v="ALCARAZ"/>
+    <s v="ALCARAZ"/>
+    <n v="1"/>
+    <s v="ALCARAZ"/>
+    <n v="1"/>
+    <n v="0.25403699999999996"/>
+    <n v="0.74596300000000004"/>
+    <x v="0"/>
+    <n v="-0.1940369999999999"/>
+    <n v="0.06"/>
+    <n v="0.94"/>
+    <s v="TARVET vs. ALCARAZ"/>
+  </r>
+  <r>
+    <s v="THOMPSON, Jordan"/>
+    <s v="BONZI, Benjamin"/>
+    <n v="53"/>
+    <n v="47"/>
+    <s v="THOMPSON"/>
+    <s v="THOMPSON"/>
+    <n v="1"/>
+    <s v="BONZI"/>
+    <n v="0"/>
+    <n v="0.38696600000000003"/>
+    <n v="0.61303399999999997"/>
+    <x v="2"/>
+    <n v="-0.14303399999999999"/>
+    <n v="0.53"/>
+    <n v="0.47"/>
+    <s v="THOMPSON vs. BONZI"/>
+  </r>
+  <r>
+    <s v="VAN DE ZANDSCHULP, Botic"/>
+    <s v="DAVIDOVICH FOKINA, Alejandro"/>
+    <n v="35"/>
+    <n v="65"/>
+    <s v="DAVIDOVICH FOKINA"/>
+    <s v="DAVIDOVICH FOKINA"/>
+    <n v="1"/>
+    <s v="DAVIDOVICH FOKINA"/>
+    <n v="1"/>
+    <n v="0.23676200000000003"/>
+    <n v="0.76323799999999997"/>
+    <x v="0"/>
+    <n v="0.11323799999999995"/>
+    <n v="0.35"/>
+    <n v="0.65"/>
+    <s v="VAN DE ZANDSCHULP vs. DAVIDOVICH FOKINA"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4E558E51-84D4-45E2-ABAD-64FB8739C946}" name="PivotTable48" cacheId="87" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
+  <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="16">
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" numFmtId="10" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" numFmtId="10" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField axis="axisRow" dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+      </items>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" numFmtId="10" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" numFmtId="10" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" numFmtId="10" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
+          <x14:pivotField fillDownLabels="1"/>
+        </ext>
+      </extLst>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="11"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Guanyador de les prediccions" fld="11" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" fillDownLabelsDefault="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1293,18 +4158,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{733616C7-25F8-4522-B3D0-0114E321248B}">
-  <dimension ref="A1:K65"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:S65"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="48.36328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1326,8 +4200,35 @@
       <c r="G1" s="1" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H1" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1351,8 +4252,43 @@
         <f>IF(F2=E2, 1, 0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <f>IF(H2=E2, 1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="J2" s="7">
+        <f>(1-0.047222)</f>
+        <v>0.95277800000000001</v>
+      </c>
+      <c r="K2" s="7">
+        <f>1-J2</f>
+        <v>4.7221999999999986E-2</v>
+      </c>
+      <c r="L2" t="str">
+        <f>IF(G2=I2, "Empat", IF(I2=1, "Guanyem", "Perdem"))</f>
+        <v>Empat</v>
+      </c>
+      <c r="M2" s="7">
+        <f>IF(ISNUMBER(SEARCH(E2, A2)), J2-(C2/100), K2-(D2/100))</f>
+        <v>0.16277799999999998</v>
+      </c>
+      <c r="N2" s="7">
+        <f>C2/100</f>
+        <v>0.79</v>
+      </c>
+      <c r="O2" s="7">
+        <f>D2/100</f>
+        <v>0.21</v>
+      </c>
+      <c r="P2" t="str">
+        <f>_xlfn.TEXTBEFORE(A2, ",") &amp; " vs. " &amp; _xlfn.TEXTBEFORE(B2, ",")</f>
+        <v>SINNER vs. NARDI</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1369,15 +4305,49 @@
         <v>8</v>
       </c>
       <c r="F3" t="str">
-        <f t="shared" ref="F3:F65" si="0">LEFT(IF(C3&gt;D3, A3, B3), FIND(",", IF(C3&gt;D3, A3, B3)) - 1)</f>
+        <f t="shared" ref="F3:H65" si="0">LEFT(IF(C3&gt;D3, A3, B3), FIND(",", IF(C3&gt;D3, A3, B3)) - 1)</f>
         <v>TSENG</v>
       </c>
       <c r="G3">
         <f t="shared" ref="G3:G65" si="1">IF(F3=E3, 1, 0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3">
+        <f>IF(H3=E3, 1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="J3" s="7">
+        <v>0.32434299999999999</v>
+      </c>
+      <c r="K3" s="7">
+        <f t="shared" ref="K3:K65" si="2">1-J3</f>
+        <v>0.67565699999999995</v>
+      </c>
+      <c r="L3" t="str">
+        <f t="shared" ref="L3:L65" si="3">IF(G3=I3, "Empat", IF(I3=1, "Guanyem", "Perdem"))</f>
+        <v>Guanyem</v>
+      </c>
+      <c r="M3" s="7">
+        <f t="shared" ref="M3:M65" si="4">IF(ISNUMBER(SEARCH(E3, A3)), J3-(C3/100), K3-(D3/100))</f>
+        <v>0.20565699999999998</v>
+      </c>
+      <c r="N3" s="7">
+        <f t="shared" ref="N3:N65" si="5">C3/100</f>
+        <v>0.53</v>
+      </c>
+      <c r="O3" s="7">
+        <f t="shared" ref="O3:O65" si="6">D3/100</f>
+        <v>0.47</v>
+      </c>
+      <c r="P3" t="str">
+        <f t="shared" ref="P3:P65" si="7">_xlfn.TEXTBEFORE(A3, ",") &amp; " vs. " &amp; _xlfn.TEXTBEFORE(B3, ",")</f>
+        <v>TSENG vs. VUKIC</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1401,14 +4371,49 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="H4" t="s">
+        <v>225</v>
+      </c>
+      <c r="I4">
+        <f t="shared" ref="I4:I65" si="8">IF(H4=E4, 1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="7">
+        <f>(1-0.725827)</f>
+        <v>0.274173</v>
+      </c>
+      <c r="K4" s="7">
+        <f t="shared" si="2"/>
+        <v>0.725827</v>
+      </c>
+      <c r="L4" t="str">
+        <f t="shared" si="3"/>
+        <v>Perdem</v>
+      </c>
+      <c r="M4" s="7">
+        <f t="shared" si="4"/>
+        <v>-0.42582699999999996</v>
+      </c>
+      <c r="N4" s="7">
+        <f t="shared" si="5"/>
+        <v>0.7</v>
+      </c>
+      <c r="O4" s="7">
+        <f t="shared" si="6"/>
+        <v>0.3</v>
+      </c>
+      <c r="P4" t="str">
+        <f t="shared" si="7"/>
+        <v>MARTÍNEZ vs. LOFFHAGEN</v>
+      </c>
+      <c r="R4" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="K4" s="4">
+      <c r="S4" s="4">
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1432,15 +4437,49 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="H5" t="s">
+        <v>226</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="7">
+        <v>0.140101</v>
+      </c>
+      <c r="K5" s="7">
+        <f t="shared" si="2"/>
+        <v>0.85989899999999997</v>
+      </c>
+      <c r="L5" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M5" s="7">
+        <f t="shared" si="4"/>
+        <v>-0.269899</v>
+      </c>
+      <c r="N5" s="7">
+        <f t="shared" si="5"/>
+        <v>0.41</v>
+      </c>
+      <c r="O5" s="7">
+        <f t="shared" si="6"/>
+        <v>0.59</v>
+      </c>
+      <c r="P5" t="str">
+        <f t="shared" si="7"/>
+        <v>NAVONE vs. SHAPOVALOV</v>
+      </c>
+      <c r="R5" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="K5" s="6">
+      <c r="S5" s="6">
         <f>37/64</f>
         <v>0.578125</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -1464,15 +4503,49 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="H6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J6" s="7">
+        <v>0.57850999999999997</v>
+      </c>
+      <c r="K6" s="7">
+        <f t="shared" si="2"/>
+        <v>0.42149000000000003</v>
+      </c>
+      <c r="L6" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M6" s="7">
+        <f t="shared" si="4"/>
+        <v>-9.1490000000000071E-2</v>
+      </c>
+      <c r="N6" s="7">
+        <f t="shared" si="5"/>
+        <v>0.67</v>
+      </c>
+      <c r="O6" s="7">
+        <f t="shared" si="6"/>
+        <v>0.33</v>
+      </c>
+      <c r="P6" t="str">
+        <f t="shared" si="7"/>
+        <v>DIMITROV vs. NISHIOKA</v>
+      </c>
+      <c r="R6" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="K6" s="6">
+      <c r="S6" s="6">
         <f>58/64</f>
         <v>0.90625</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1496,15 +4569,49 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="H7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J7" s="7">
+        <v>0.32292799999999999</v>
+      </c>
+      <c r="K7" s="7">
+        <f t="shared" si="2"/>
+        <v>0.67707200000000001</v>
+      </c>
+      <c r="L7" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M7" s="7">
+        <f t="shared" si="4"/>
+        <v>0.13707199999999997</v>
+      </c>
+      <c r="N7" s="7">
+        <f t="shared" si="5"/>
+        <v>0.46</v>
+      </c>
+      <c r="O7" s="7">
+        <f t="shared" si="6"/>
+        <v>0.54</v>
+      </c>
+      <c r="P7" t="str">
+        <f t="shared" si="7"/>
+        <v>COMESANA vs. MOUTET</v>
+      </c>
+      <c r="R7" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="K7" s="6">
+      <c r="S7" s="6">
         <f>42/64</f>
         <v>0.65625</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -1528,15 +4635,50 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="H8" t="s">
+        <v>227</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="7">
+        <f>(1-0.66349)</f>
+        <v>0.33650999999999998</v>
+      </c>
+      <c r="K8" s="7">
+        <f t="shared" si="2"/>
+        <v>0.66349000000000002</v>
+      </c>
+      <c r="L8" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M8" s="7">
+        <f t="shared" si="4"/>
+        <v>-3.4900000000000486E-3</v>
+      </c>
+      <c r="N8" s="7">
+        <f t="shared" si="5"/>
+        <v>0.34</v>
+      </c>
+      <c r="O8" s="7">
+        <f t="shared" si="6"/>
+        <v>0.66</v>
+      </c>
+      <c r="P8" t="str">
+        <f t="shared" si="7"/>
+        <v>OFNER vs. MEDJEDOVIC</v>
+      </c>
+      <c r="R8" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="K8" s="6">
+      <c r="S8" s="6">
         <f>41/64</f>
         <v>0.640625</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -1560,8 +4702,42 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H9" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J9" s="7">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="K9" s="7">
+        <f t="shared" si="2"/>
+        <v>0.995</v>
+      </c>
+      <c r="L9" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M9" s="7">
+        <f t="shared" si="4"/>
+        <v>0.28500000000000003</v>
+      </c>
+      <c r="N9" s="7">
+        <f t="shared" si="5"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="O9" s="7">
+        <f t="shared" si="6"/>
+        <v>0.71</v>
+      </c>
+      <c r="P9" t="str">
+        <f t="shared" si="7"/>
+        <v>MONDAY vs. PAUL</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -1585,8 +4761,43 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H10" t="s">
+        <v>29</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J10" s="7">
+        <f>(1-0.183868)</f>
+        <v>0.81613199999999997</v>
+      </c>
+      <c r="K10" s="7">
+        <f t="shared" si="2"/>
+        <v>0.18386800000000003</v>
+      </c>
+      <c r="L10" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M10" s="7">
+        <f t="shared" si="4"/>
+        <v>9.6131999999999995E-2</v>
+      </c>
+      <c r="N10" s="7">
+        <f t="shared" si="5"/>
+        <v>0.72</v>
+      </c>
+      <c r="O10" s="7">
+        <f t="shared" si="6"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="P10" t="str">
+        <f t="shared" si="7"/>
+        <v>SHELTON vs. BOLT</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1610,8 +4821,43 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H11" t="s">
+        <v>32</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J11" s="7">
+        <f>(1-0.46723)</f>
+        <v>0.53276999999999997</v>
+      </c>
+      <c r="K11" s="7">
+        <f t="shared" si="2"/>
+        <v>0.46723000000000003</v>
+      </c>
+      <c r="L11" t="str">
+        <f t="shared" si="3"/>
+        <v>Guanyem</v>
+      </c>
+      <c r="M11" s="7">
+        <f t="shared" si="4"/>
+        <v>6.2769999999999992E-2</v>
+      </c>
+      <c r="N11" s="7">
+        <f t="shared" si="5"/>
+        <v>0.47</v>
+      </c>
+      <c r="O11" s="7">
+        <f t="shared" si="6"/>
+        <v>0.53</v>
+      </c>
+      <c r="P11" t="str">
+        <f t="shared" si="7"/>
+        <v>HIJIKATA vs. GOFFIN</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -1635,8 +4881,43 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J12" s="7">
+        <f>(1-0.669093)</f>
+        <v>0.33090699999999995</v>
+      </c>
+      <c r="K12" s="7">
+        <f t="shared" si="2"/>
+        <v>0.66909300000000005</v>
+      </c>
+      <c r="L12" t="str">
+        <f t="shared" si="3"/>
+        <v>Guanyem</v>
+      </c>
+      <c r="M12" s="7">
+        <f t="shared" si="4"/>
+        <v>0.22909300000000005</v>
+      </c>
+      <c r="N12" s="7">
+        <f t="shared" si="5"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="O12" s="7">
+        <f t="shared" si="6"/>
+        <v>0.44</v>
+      </c>
+      <c r="P12" t="str">
+        <f t="shared" si="7"/>
+        <v>KOVACEVIC vs. FUCSOVICS</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -1660,8 +4941,43 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H13" t="s">
+        <v>228</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="7">
+        <f>(1-0.676231)</f>
+        <v>0.32376899999999997</v>
+      </c>
+      <c r="K13" s="7">
+        <f t="shared" si="2"/>
+        <v>0.67623100000000003</v>
+      </c>
+      <c r="L13" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M13" s="7">
+        <f t="shared" si="4"/>
+        <v>-0.146231</v>
+      </c>
+      <c r="N13" s="7">
+        <f t="shared" si="5"/>
+        <v>0.47</v>
+      </c>
+      <c r="O13" s="7">
+        <f t="shared" si="6"/>
+        <v>0.53</v>
+      </c>
+      <c r="P13" t="str">
+        <f t="shared" si="7"/>
+        <v>MONFILS vs. HUMBERT</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1685,8 +5001,43 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H14" t="s">
+        <v>41</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J14" s="7">
+        <f>(1-0.200857)</f>
+        <v>0.79914299999999994</v>
+      </c>
+      <c r="K14" s="7">
+        <f t="shared" si="2"/>
+        <v>0.20085700000000006</v>
+      </c>
+      <c r="L14" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M14" s="7">
+        <f t="shared" si="4"/>
+        <v>0.21914299999999998</v>
+      </c>
+      <c r="N14" s="7">
+        <f t="shared" si="5"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="O14" s="7">
+        <f t="shared" si="6"/>
+        <v>0.42</v>
+      </c>
+      <c r="P14" t="str">
+        <f t="shared" si="7"/>
+        <v>NAKASHIMA vs. BU</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1710,8 +5061,43 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H15" t="s">
+        <v>44</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J15" s="7">
+        <f>(1-0.738274)</f>
+        <v>0.26172600000000001</v>
+      </c>
+      <c r="K15" s="7">
+        <f t="shared" si="2"/>
+        <v>0.73827399999999999</v>
+      </c>
+      <c r="L15" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M15" s="7">
+        <f t="shared" si="4"/>
+        <v>0.13827400000000001</v>
+      </c>
+      <c r="N15" s="7">
+        <f t="shared" si="5"/>
+        <v>0.4</v>
+      </c>
+      <c r="O15" s="7">
+        <f t="shared" si="6"/>
+        <v>0.6</v>
+      </c>
+      <c r="P15" t="str">
+        <f t="shared" si="7"/>
+        <v>SHEVCHENKO vs. OPELKA</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -1735,8 +5121,42 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H16" t="s">
+        <v>47</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J16" s="7">
+        <v>0.16333500000000001</v>
+      </c>
+      <c r="K16" s="7">
+        <f t="shared" si="2"/>
+        <v>0.83666499999999999</v>
+      </c>
+      <c r="L16" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M16" s="7">
+        <f t="shared" si="4"/>
+        <v>0.22666500000000001</v>
+      </c>
+      <c r="N16" s="7">
+        <f t="shared" si="5"/>
+        <v>0.39</v>
+      </c>
+      <c r="O16" s="7">
+        <f t="shared" si="6"/>
+        <v>0.61</v>
+      </c>
+      <c r="P16" t="str">
+        <f t="shared" si="7"/>
+        <v>FARIA vs. SONEGO</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -1760,8 +5180,43 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H17" t="s">
+        <v>230</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J17" s="7">
+        <f>(1-0.238453)</f>
+        <v>0.76154699999999997</v>
+      </c>
+      <c r="K17" s="7">
+        <f t="shared" si="2"/>
+        <v>0.23845300000000003</v>
+      </c>
+      <c r="L17" t="str">
+        <f t="shared" si="3"/>
+        <v>Perdem</v>
+      </c>
+      <c r="M17" s="7">
+        <f t="shared" si="4"/>
+        <v>-0.60154699999999994</v>
+      </c>
+      <c r="N17" s="7">
+        <f t="shared" si="5"/>
+        <v>0.16</v>
+      </c>
+      <c r="O17" s="7">
+        <f t="shared" si="6"/>
+        <v>0.84</v>
+      </c>
+      <c r="P17" t="str">
+        <f t="shared" si="7"/>
+        <v>BASILASHVILI vs. MUSETTI</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>51</v>
       </c>
@@ -1785,8 +5240,43 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H18" t="s">
+        <v>53</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J18" s="7">
+        <f>(1-0.005)</f>
+        <v>0.995</v>
+      </c>
+      <c r="K18" s="7">
+        <f t="shared" si="2"/>
+        <v>5.0000000000000044E-3</v>
+      </c>
+      <c r="L18" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M18" s="7">
+        <f t="shared" si="4"/>
+        <v>0.19499999999999995</v>
+      </c>
+      <c r="N18" s="7">
+        <f t="shared" si="5"/>
+        <v>0.8</v>
+      </c>
+      <c r="O18" s="7">
+        <f t="shared" si="6"/>
+        <v>0.2</v>
+      </c>
+      <c r="P18" t="str">
+        <f t="shared" si="7"/>
+        <v>DRAPER vs. BAEZ</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>54</v>
       </c>
@@ -1810,8 +5300,43 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H19" t="s">
+        <v>56</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J19" s="7">
+        <f>(1-0.898889)</f>
+        <v>0.10111099999999995</v>
+      </c>
+      <c r="K19" s="7">
+        <f t="shared" si="2"/>
+        <v>0.89888900000000005</v>
+      </c>
+      <c r="L19" t="str">
+        <f t="shared" si="3"/>
+        <v>Guanyem</v>
+      </c>
+      <c r="M19" s="7">
+        <f t="shared" si="4"/>
+        <v>0.46888900000000006</v>
+      </c>
+      <c r="N19" s="7">
+        <f t="shared" si="5"/>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="O19" s="7">
+        <f t="shared" si="6"/>
+        <v>0.43</v>
+      </c>
+      <c r="P19" t="str">
+        <f t="shared" si="7"/>
+        <v>COLLIGNON vs. CILIC</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>57</v>
       </c>
@@ -1835,8 +5360,43 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H20" t="s">
+        <v>59</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J20" s="7">
+        <f>(1-0.68813)</f>
+        <v>0.31186999999999998</v>
+      </c>
+      <c r="K20" s="7">
+        <f t="shared" si="2"/>
+        <v>0.68813000000000002</v>
+      </c>
+      <c r="L20" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M20" s="7">
+        <f t="shared" si="4"/>
+        <v>5.8130000000000015E-2</v>
+      </c>
+      <c r="N20" s="7">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="O20" s="7">
+        <f t="shared" si="6"/>
+        <v>0.63</v>
+      </c>
+      <c r="P20" t="str">
+        <f t="shared" si="7"/>
+        <v>MCCABE vs. MAROZSAN</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>60</v>
       </c>
@@ -1860,8 +5420,43 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H21" t="s">
+        <v>229</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="7">
+        <f>(1-0.713091)</f>
+        <v>0.28690899999999997</v>
+      </c>
+      <c r="K21" s="7">
+        <f t="shared" si="2"/>
+        <v>0.71309100000000003</v>
+      </c>
+      <c r="L21" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M21" s="7">
+        <f t="shared" si="4"/>
+        <v>-0.19309100000000001</v>
+      </c>
+      <c r="N21" s="7">
+        <f t="shared" si="5"/>
+        <v>0.48</v>
+      </c>
+      <c r="O21" s="7">
+        <f t="shared" si="6"/>
+        <v>0.52</v>
+      </c>
+      <c r="P21" t="str">
+        <f t="shared" si="7"/>
+        <v>MUNAR vs. BUBLIK</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>63</v>
       </c>
@@ -1885,8 +5480,42 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H22" t="s">
+        <v>65</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J22" s="7">
+        <v>0.70024500000000001</v>
+      </c>
+      <c r="K22" s="7">
+        <f t="shared" si="2"/>
+        <v>0.29975499999999999</v>
+      </c>
+      <c r="L22" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M22" s="7">
+        <f t="shared" si="4"/>
+        <v>1.024500000000006E-2</v>
+      </c>
+      <c r="N22" s="7">
+        <f t="shared" si="5"/>
+        <v>0.69</v>
+      </c>
+      <c r="O22" s="7">
+        <f t="shared" si="6"/>
+        <v>0.31</v>
+      </c>
+      <c r="P22" t="str">
+        <f t="shared" si="7"/>
+        <v>COBOLLI vs. ZHUKAYEV</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>66</v>
       </c>
@@ -1910,8 +5539,42 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H23" t="s">
+        <v>223</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="7">
+        <v>0.74445399999999995</v>
+      </c>
+      <c r="K23" s="7">
+        <f t="shared" si="2"/>
+        <v>0.25554600000000005</v>
+      </c>
+      <c r="L23" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M23" s="7">
+        <f t="shared" si="4"/>
+        <v>-1.4453999999999967E-2</v>
+      </c>
+      <c r="N23" s="7">
+        <f t="shared" si="5"/>
+        <v>0.73</v>
+      </c>
+      <c r="O23" s="7">
+        <f t="shared" si="6"/>
+        <v>0.27</v>
+      </c>
+      <c r="P23" t="str">
+        <f t="shared" si="7"/>
+        <v>ETCHEVERRY vs. PINNINGTON JONES</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>69</v>
       </c>
@@ -1935,8 +5598,42 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H24" t="s">
+        <v>71</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J24" s="7">
+        <v>0.89686600000000005</v>
+      </c>
+      <c r="K24" s="7">
+        <f t="shared" si="2"/>
+        <v>0.10313399999999995</v>
+      </c>
+      <c r="L24" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M24" s="7">
+        <f t="shared" si="4"/>
+        <v>0.36686600000000003</v>
+      </c>
+      <c r="N24" s="7">
+        <f t="shared" si="5"/>
+        <v>0.53</v>
+      </c>
+      <c r="O24" s="7">
+        <f t="shared" si="6"/>
+        <v>0.47</v>
+      </c>
+      <c r="P24" t="str">
+        <f t="shared" si="7"/>
+        <v>GIRON vs. UGO CARABELLI</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>72</v>
       </c>
@@ -1960,8 +5657,42 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H25" t="s">
+        <v>74</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J25" s="7">
+        <v>6.1588999999999998E-2</v>
+      </c>
+      <c r="K25" s="7">
+        <f t="shared" si="2"/>
+        <v>0.938411</v>
+      </c>
+      <c r="L25" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M25" s="7">
+        <f t="shared" si="4"/>
+        <v>0.28841099999999997</v>
+      </c>
+      <c r="N25" s="7">
+        <f t="shared" si="5"/>
+        <v>0.35</v>
+      </c>
+      <c r="O25" s="7">
+        <f t="shared" si="6"/>
+        <v>0.65</v>
+      </c>
+      <c r="P25" t="str">
+        <f t="shared" si="7"/>
+        <v>GASTON vs. MENSIK</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>75</v>
       </c>
@@ -1985,8 +5716,43 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H26" t="s">
+        <v>77</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J26" s="7">
+        <f>(1-0.051478)</f>
+        <v>0.94852199999999998</v>
+      </c>
+      <c r="K26" s="7">
+        <f t="shared" si="2"/>
+        <v>5.1478000000000024E-2</v>
+      </c>
+      <c r="L26" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M26" s="7">
+        <f t="shared" si="4"/>
+        <v>0.29852199999999995</v>
+      </c>
+      <c r="N26" s="7">
+        <f t="shared" si="5"/>
+        <v>0.65</v>
+      </c>
+      <c r="O26" s="7">
+        <f t="shared" si="6"/>
+        <v>0.35</v>
+      </c>
+      <c r="P26" t="str">
+        <f t="shared" si="7"/>
+        <v>DE MINAUR vs. CARBALLES BAENA</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -2010,8 +5776,42 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H27" t="s">
+        <v>80</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J27" s="7">
+        <v>0.58135800000000004</v>
+      </c>
+      <c r="K27" s="7">
+        <f t="shared" si="2"/>
+        <v>0.41864199999999996</v>
+      </c>
+      <c r="L27" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M27" s="7">
+        <f t="shared" si="4"/>
+        <v>4.1358000000000006E-2</v>
+      </c>
+      <c r="N27" s="7">
+        <f t="shared" si="5"/>
+        <v>0.54</v>
+      </c>
+      <c r="O27" s="7">
+        <f t="shared" si="6"/>
+        <v>0.46</v>
+      </c>
+      <c r="P27" t="str">
+        <f t="shared" si="7"/>
+        <v>CAZAUX vs. WALTON</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>81</v>
       </c>
@@ -2035,8 +5835,42 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H28" t="s">
+        <v>224</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="7">
+        <v>0.81447899999999995</v>
+      </c>
+      <c r="K28" s="7">
+        <f t="shared" si="2"/>
+        <v>0.18552100000000005</v>
+      </c>
+      <c r="L28" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M28" s="7">
+        <f t="shared" si="4"/>
+        <v>-0.12447899999999995</v>
+      </c>
+      <c r="N28" s="7">
+        <f t="shared" si="5"/>
+        <v>0.69</v>
+      </c>
+      <c r="O28" s="7">
+        <f t="shared" si="6"/>
+        <v>0.31</v>
+      </c>
+      <c r="P28" t="str">
+        <f t="shared" si="7"/>
+        <v>HALYS vs. HOLMGREN</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>84</v>
       </c>
@@ -2060,8 +5894,42 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H29" t="s">
+        <v>86</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J29" s="7">
+        <v>0.167744</v>
+      </c>
+      <c r="K29" s="7">
+        <f t="shared" si="2"/>
+        <v>0.832256</v>
+      </c>
+      <c r="L29" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M29" s="7">
+        <f t="shared" si="4"/>
+        <v>0.20225599999999999</v>
+      </c>
+      <c r="N29" s="7">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="O29" s="7">
+        <f t="shared" si="6"/>
+        <v>0.63</v>
+      </c>
+      <c r="P29" t="str">
+        <f t="shared" si="7"/>
+        <v>DZUMHUR vs. MACHAC</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>87</v>
       </c>
@@ -2085,8 +5953,43 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H30" t="s">
+        <v>231</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J30" s="7">
+        <f>(1-0.348643)</f>
+        <v>0.65135699999999996</v>
+      </c>
+      <c r="K30" s="7">
+        <f t="shared" si="2"/>
+        <v>0.34864300000000004</v>
+      </c>
+      <c r="L30" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M30" s="7">
+        <f t="shared" si="4"/>
+        <v>-0.14135699999999995</v>
+      </c>
+      <c r="N30" s="7">
+        <f t="shared" si="5"/>
+        <v>0.51</v>
+      </c>
+      <c r="O30" s="7">
+        <f t="shared" si="6"/>
+        <v>0.49</v>
+      </c>
+      <c r="P30" t="str">
+        <f t="shared" si="7"/>
+        <v>MICHELSEN vs. KECMANOVIC</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>90</v>
       </c>
@@ -2110,8 +6013,42 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H31" t="s">
+        <v>92</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J31" s="7">
+        <v>0.61397100000000004</v>
+      </c>
+      <c r="K31" s="7">
+        <f t="shared" si="2"/>
+        <v>0.38602899999999996</v>
+      </c>
+      <c r="L31" t="str">
+        <f t="shared" si="3"/>
+        <v>Guanyem</v>
+      </c>
+      <c r="M31" s="7">
+        <f t="shared" si="4"/>
+        <v>0.13397100000000006</v>
+      </c>
+      <c r="N31" s="7">
+        <f t="shared" si="5"/>
+        <v>0.48</v>
+      </c>
+      <c r="O31" s="7">
+        <f t="shared" si="6"/>
+        <v>0.52</v>
+      </c>
+      <c r="P31" t="str">
+        <f t="shared" si="7"/>
+        <v>DE JONG vs. EUBANKS</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>93</v>
       </c>
@@ -2135,8 +6072,43 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H32" t="s">
+        <v>95</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J32" s="7">
+        <f>(1-0.106033)</f>
+        <v>0.89396699999999996</v>
+      </c>
+      <c r="K32" s="7">
+        <f t="shared" si="2"/>
+        <v>0.10603300000000004</v>
+      </c>
+      <c r="L32" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M32" s="7">
+        <f t="shared" si="4"/>
+        <v>0.37396699999999994</v>
+      </c>
+      <c r="N32" s="7">
+        <f t="shared" si="5"/>
+        <v>0.52</v>
+      </c>
+      <c r="O32" s="7">
+        <f t="shared" si="6"/>
+        <v>0.48</v>
+      </c>
+      <c r="P32" t="str">
+        <f t="shared" si="7"/>
+        <v>EVANS vs. CLARKE</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>96</v>
       </c>
@@ -2160,8 +6132,43 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H33" t="s">
+        <v>98</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J33" s="7">
+        <f>(1-0.927884)</f>
+        <v>7.2115999999999958E-2</v>
+      </c>
+      <c r="K33" s="7">
+        <f t="shared" si="2"/>
+        <v>0.92788400000000004</v>
+      </c>
+      <c r="L33" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M33" s="7">
+        <f t="shared" si="4"/>
+        <v>0.22788400000000009</v>
+      </c>
+      <c r="N33" s="7">
+        <f t="shared" si="5"/>
+        <v>0.3</v>
+      </c>
+      <c r="O33" s="7">
+        <f t="shared" si="6"/>
+        <v>0.7</v>
+      </c>
+      <c r="P33" t="str">
+        <f t="shared" si="7"/>
+        <v>MULLER vs. DJOKOVIC</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>99</v>
       </c>
@@ -2185,8 +6192,42 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H34" t="s">
+        <v>101</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J34" s="7">
+        <v>0.89076599999999995</v>
+      </c>
+      <c r="K34" s="7">
+        <f t="shared" si="2"/>
+        <v>0.10923400000000005</v>
+      </c>
+      <c r="L34" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M34" s="7">
+        <f t="shared" si="4"/>
+        <v>0.38076599999999994</v>
+      </c>
+      <c r="N34" s="7">
+        <f t="shared" si="5"/>
+        <v>0.51</v>
+      </c>
+      <c r="O34" s="7">
+        <f t="shared" si="6"/>
+        <v>0.49</v>
+      </c>
+      <c r="P34" t="str">
+        <f t="shared" si="7"/>
+        <v>FRITZ vs. MPETSHI PERRICARD</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>102</v>
       </c>
@@ -2210,8 +6251,43 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H35" t="s">
+        <v>104</v>
+      </c>
+      <c r="I35">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J35" s="7">
+        <f>(1-0.206905)</f>
+        <v>0.79309499999999999</v>
+      </c>
+      <c r="K35" s="7">
+        <f t="shared" si="2"/>
+        <v>0.20690500000000001</v>
+      </c>
+      <c r="L35" t="str">
+        <f t="shared" si="3"/>
+        <v>Guanyem</v>
+      </c>
+      <c r="M35" s="7">
+        <f t="shared" si="4"/>
+        <v>0.33309499999999997</v>
+      </c>
+      <c r="N35" s="7">
+        <f t="shared" si="5"/>
+        <v>0.46</v>
+      </c>
+      <c r="O35" s="7">
+        <f t="shared" si="6"/>
+        <v>0.54</v>
+      </c>
+      <c r="P35" t="str">
+        <f t="shared" si="7"/>
+        <v>DIALLO vs. ALTMAIER</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>105</v>
       </c>
@@ -2235,8 +6311,42 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H36" t="s">
+        <v>232</v>
+      </c>
+      <c r="I36">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J36" s="7">
+        <v>0.64820299999999997</v>
+      </c>
+      <c r="K36" s="7">
+        <f t="shared" si="2"/>
+        <v>0.35179700000000003</v>
+      </c>
+      <c r="L36" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M36" s="7">
+        <f t="shared" si="4"/>
+        <v>-4.8202999999999996E-2</v>
+      </c>
+      <c r="N36" s="7">
+        <f t="shared" si="5"/>
+        <v>0.6</v>
+      </c>
+      <c r="O36" s="7">
+        <f t="shared" si="6"/>
+        <v>0.4</v>
+      </c>
+      <c r="P36" t="str">
+        <f t="shared" si="7"/>
+        <v>ARNALDI vs. VAN DE ZANDSCHULP</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>108</v>
       </c>
@@ -2260,8 +6370,43 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H37" t="s">
+        <v>110</v>
+      </c>
+      <c r="I37">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J37" s="7">
+        <f>(1-0.738274)</f>
+        <v>0.26172600000000001</v>
+      </c>
+      <c r="K37" s="7">
+        <f t="shared" si="2"/>
+        <v>0.73827399999999999</v>
+      </c>
+      <c r="L37" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M37" s="7">
+        <f t="shared" si="4"/>
+        <v>7.8273999999999955E-2</v>
+      </c>
+      <c r="N37" s="7">
+        <f t="shared" si="5"/>
+        <v>0.34</v>
+      </c>
+      <c r="O37" s="7">
+        <f t="shared" si="6"/>
+        <v>0.66</v>
+      </c>
+      <c r="P37" t="str">
+        <f t="shared" si="7"/>
+        <v>HOLT vs. DAVIDOVICH FOKINA</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>111</v>
       </c>
@@ -2285,8 +6430,43 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H38" t="s">
+        <v>211</v>
+      </c>
+      <c r="I38">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="7">
+        <f>(1-0.246168)</f>
+        <v>0.75383200000000006</v>
+      </c>
+      <c r="K38" s="7">
+        <f t="shared" si="2"/>
+        <v>0.24616799999999994</v>
+      </c>
+      <c r="L38" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M38" s="7">
+        <f t="shared" si="4"/>
+        <v>6.1679999999999513E-3</v>
+      </c>
+      <c r="N38" s="7">
+        <f t="shared" si="5"/>
+        <v>0.76</v>
+      </c>
+      <c r="O38" s="7">
+        <f t="shared" si="6"/>
+        <v>0.24</v>
+      </c>
+      <c r="P38" t="str">
+        <f t="shared" si="7"/>
+        <v>POPYRIN vs. FERY</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>114</v>
       </c>
@@ -2310,8 +6490,42 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H39" t="s">
+        <v>221</v>
+      </c>
+      <c r="I39">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="7">
+        <v>0.21008499999999999</v>
+      </c>
+      <c r="K39" s="7">
+        <f t="shared" si="2"/>
+        <v>0.78991500000000003</v>
+      </c>
+      <c r="L39" t="str">
+        <f t="shared" si="3"/>
+        <v>Perdem</v>
+      </c>
+      <c r="M39" s="7">
+        <f t="shared" si="4"/>
+        <v>-0.34991500000000009</v>
+      </c>
+      <c r="N39" s="7">
+        <f t="shared" si="5"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="O39" s="7">
+        <f t="shared" si="6"/>
+        <v>0.44</v>
+      </c>
+      <c r="P39" t="str">
+        <f t="shared" si="7"/>
+        <v>DARDERI vs. SAFIULLIN</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>117</v>
       </c>
@@ -2335,8 +6549,42 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H40" t="s">
+        <v>119</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J40" s="7">
+        <v>0.22357099999999999</v>
+      </c>
+      <c r="K40" s="7">
+        <f t="shared" si="2"/>
+        <v>0.77642900000000004</v>
+      </c>
+      <c r="L40" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M40" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25642900000000002</v>
+      </c>
+      <c r="N40" s="7">
+        <f t="shared" si="5"/>
+        <v>0.48</v>
+      </c>
+      <c r="O40" s="7">
+        <f t="shared" si="6"/>
+        <v>0.52</v>
+      </c>
+      <c r="P40" t="str">
+        <f t="shared" si="7"/>
+        <v>KOPRIVA vs. THOMPSON</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>120</v>
       </c>
@@ -2360,8 +6608,42 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H41" t="s">
+        <v>212</v>
+      </c>
+      <c r="I41">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J41" s="7">
+        <v>9.2549999999999993E-3</v>
+      </c>
+      <c r="K41" s="7">
+        <f t="shared" si="2"/>
+        <v>0.99074499999999999</v>
+      </c>
+      <c r="L41" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M41" s="7">
+        <f t="shared" si="4"/>
+        <v>-0.23074499999999998</v>
+      </c>
+      <c r="N41" s="7">
+        <f t="shared" si="5"/>
+        <v>0.24</v>
+      </c>
+      <c r="O41" s="7">
+        <f t="shared" si="6"/>
+        <v>0.76</v>
+      </c>
+      <c r="P41" t="str">
+        <f t="shared" si="7"/>
+        <v>BONZI vs. MEDVEDEV</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>123</v>
       </c>
@@ -2385,8 +6667,43 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H42" t="s">
+        <v>220</v>
+      </c>
+      <c r="I42">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J42" s="7">
+        <f>(1-0.405323)</f>
+        <v>0.59467700000000001</v>
+      </c>
+      <c r="K42" s="7">
+        <f t="shared" si="2"/>
+        <v>0.40532299999999999</v>
+      </c>
+      <c r="L42" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M42" s="7">
+        <f t="shared" si="4"/>
+        <v>-1.4676999999999996E-2</v>
+      </c>
+      <c r="N42" s="7">
+        <f t="shared" si="5"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="O42" s="7">
+        <f t="shared" si="6"/>
+        <v>0.42</v>
+      </c>
+      <c r="P42" t="str">
+        <f t="shared" si="7"/>
+        <v>CERUNDOLO vs. BORGES</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>126</v>
       </c>
@@ -2410,8 +6727,42 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H43" t="s">
+        <v>128</v>
+      </c>
+      <c r="I43">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J43" s="7">
+        <v>0.76670000000000005</v>
+      </c>
+      <c r="K43" s="7">
+        <f t="shared" si="2"/>
+        <v>0.23329999999999995</v>
+      </c>
+      <c r="L43" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M43" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25670000000000004</v>
+      </c>
+      <c r="N43" s="7">
+        <f t="shared" si="5"/>
+        <v>0.51</v>
+      </c>
+      <c r="O43" s="7">
+        <f t="shared" si="6"/>
+        <v>0.49</v>
+      </c>
+      <c r="P43" t="str">
+        <f t="shared" si="7"/>
+        <v>HARRIS vs. LAJOVIC</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>129</v>
       </c>
@@ -2435,8 +6786,42 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H44" t="s">
+        <v>131</v>
+      </c>
+      <c r="I44">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J44" s="7">
+        <v>0.70935099999999995</v>
+      </c>
+      <c r="K44" s="7">
+        <f t="shared" si="2"/>
+        <v>0.29064900000000005</v>
+      </c>
+      <c r="L44" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M44" s="7">
+        <f t="shared" si="4"/>
+        <v>1.9351000000000007E-2</v>
+      </c>
+      <c r="N44" s="7">
+        <f t="shared" si="5"/>
+        <v>0.69</v>
+      </c>
+      <c r="O44" s="7">
+        <f t="shared" si="6"/>
+        <v>0.31</v>
+      </c>
+      <c r="P44" t="str">
+        <f t="shared" si="7"/>
+        <v>MOCHIZUKI vs. ZEPPIERI</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>132</v>
       </c>
@@ -2460,8 +6845,43 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H45" t="s">
+        <v>134</v>
+      </c>
+      <c r="I45">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J45" s="7">
+        <f>(1-0.561618)</f>
+        <v>0.43838200000000005</v>
+      </c>
+      <c r="K45" s="7">
+        <f t="shared" si="2"/>
+        <v>0.56161799999999995</v>
+      </c>
+      <c r="L45" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M45" s="7">
+        <f t="shared" si="4"/>
+        <v>-8.8382000000000072E-2</v>
+      </c>
+      <c r="N45" s="7">
+        <f t="shared" si="5"/>
+        <v>0.35</v>
+      </c>
+      <c r="O45" s="7">
+        <f t="shared" si="6"/>
+        <v>0.65</v>
+      </c>
+      <c r="P45" t="str">
+        <f t="shared" si="7"/>
+        <v>MCDONALD vs. KHACHANOV</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>135</v>
       </c>
@@ -2485,8 +6905,42 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H46" t="s">
+        <v>218</v>
+      </c>
+      <c r="I46">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J46" s="7">
+        <v>0.85499899999999995</v>
+      </c>
+      <c r="K46" s="7">
+        <f t="shared" si="2"/>
+        <v>0.14500100000000005</v>
+      </c>
+      <c r="L46" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M46" s="7">
+        <f t="shared" si="4"/>
+        <v>-0.21499899999999994</v>
+      </c>
+      <c r="N46" s="7">
+        <f t="shared" si="5"/>
+        <v>0.64</v>
+      </c>
+      <c r="O46" s="7">
+        <f t="shared" si="6"/>
+        <v>0.36</v>
+      </c>
+      <c r="P46" t="str">
+        <f t="shared" si="7"/>
+        <v>BERRETTINI vs. MAJCHRZAK</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>138</v>
       </c>
@@ -2510,8 +6964,42 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H47" t="s">
+        <v>140</v>
+      </c>
+      <c r="I47">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J47" s="7">
+        <v>0.74376900000000001</v>
+      </c>
+      <c r="K47" s="7">
+        <f t="shared" si="2"/>
+        <v>0.25623099999999999</v>
+      </c>
+      <c r="L47" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M47" s="7">
+        <f t="shared" si="4"/>
+        <v>-6.2309999999999865E-3</v>
+      </c>
+      <c r="N47" s="7">
+        <f t="shared" si="5"/>
+        <v>0.75</v>
+      </c>
+      <c r="O47" s="7">
+        <f t="shared" si="6"/>
+        <v>0.25</v>
+      </c>
+      <c r="P47" t="str">
+        <f t="shared" si="7"/>
+        <v>QUINN vs. SEARLE</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>141</v>
       </c>
@@ -2535,8 +7023,42 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H48" t="s">
+        <v>143</v>
+      </c>
+      <c r="I48">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J48" s="7">
+        <v>0.54134000000000004</v>
+      </c>
+      <c r="K48" s="7">
+        <f t="shared" si="2"/>
+        <v>0.45865999999999996</v>
+      </c>
+      <c r="L48" t="str">
+        <f t="shared" si="3"/>
+        <v>Guanyem</v>
+      </c>
+      <c r="M48" s="7">
+        <f t="shared" si="4"/>
+        <v>6.1340000000000061E-2</v>
+      </c>
+      <c r="N48" s="7">
+        <f t="shared" si="5"/>
+        <v>0.48</v>
+      </c>
+      <c r="O48" s="7">
+        <f t="shared" si="6"/>
+        <v>0.52</v>
+      </c>
+      <c r="P48" t="str">
+        <f t="shared" si="7"/>
+        <v>GARIN vs. RODESCH</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>144</v>
       </c>
@@ -2560,8 +7082,42 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H49" t="s">
+        <v>219</v>
+      </c>
+      <c r="I49">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J49" s="7">
+        <v>8.0236000000000002E-2</v>
+      </c>
+      <c r="K49" s="7">
+        <f t="shared" si="2"/>
+        <v>0.91976400000000003</v>
+      </c>
+      <c r="L49" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M49" s="7">
+        <f t="shared" si="4"/>
+        <v>-0.14976400000000001</v>
+      </c>
+      <c r="N49" s="7">
+        <f t="shared" si="5"/>
+        <v>0.23</v>
+      </c>
+      <c r="O49" s="7">
+        <f t="shared" si="6"/>
+        <v>0.77</v>
+      </c>
+      <c r="P49" t="str">
+        <f t="shared" si="7"/>
+        <v>RINDERKNECH vs. ZVEREV</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>147</v>
       </c>
@@ -2585,8 +7141,43 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H50" t="s">
+        <v>213</v>
+      </c>
+      <c r="I50">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J50" s="7">
+        <f>(1-0.21455)</f>
+        <v>0.78544999999999998</v>
+      </c>
+      <c r="K50" s="7">
+        <f t="shared" si="2"/>
+        <v>0.21455000000000002</v>
+      </c>
+      <c r="L50" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M50" s="7">
+        <f t="shared" si="4"/>
+        <v>8.4550000000000014E-2</v>
+      </c>
+      <c r="N50" s="7">
+        <f t="shared" si="5"/>
+        <v>0.87</v>
+      </c>
+      <c r="O50" s="7">
+        <f t="shared" si="6"/>
+        <v>0.13</v>
+      </c>
+      <c r="P50" t="str">
+        <f t="shared" si="7"/>
+        <v>RUNE vs. JARRY</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>150</v>
       </c>
@@ -2610,8 +7201,43 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H51" t="s">
+        <v>152</v>
+      </c>
+      <c r="I51">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J51" s="7">
+        <f>(1-0.261875)</f>
+        <v>0.73812499999999992</v>
+      </c>
+      <c r="K51" s="7">
+        <f t="shared" si="2"/>
+        <v>0.26187500000000008</v>
+      </c>
+      <c r="L51" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M51" s="7">
+        <f t="shared" si="4"/>
+        <v>0.13812499999999994</v>
+      </c>
+      <c r="N51" s="7">
+        <f t="shared" si="5"/>
+        <v>0.6</v>
+      </c>
+      <c r="O51" s="7">
+        <f t="shared" si="6"/>
+        <v>0.4</v>
+      </c>
+      <c r="P51" t="str">
+        <f t="shared" si="7"/>
+        <v>TIEN vs. BASAVAREDDY</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>153</v>
       </c>
@@ -2635,8 +7261,43 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H52" t="s">
+        <v>155</v>
+      </c>
+      <c r="I52">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J52" s="7">
+        <f>(0.379632)</f>
+        <v>0.37963200000000002</v>
+      </c>
+      <c r="K52" s="7">
+        <f t="shared" si="2"/>
+        <v>0.62036800000000003</v>
+      </c>
+      <c r="L52" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M52" s="7">
+        <f t="shared" si="4"/>
+        <v>-9.6319999999999739E-3</v>
+      </c>
+      <c r="N52" s="7">
+        <f t="shared" si="5"/>
+        <v>0.37</v>
+      </c>
+      <c r="O52" s="7">
+        <f t="shared" si="6"/>
+        <v>0.63</v>
+      </c>
+      <c r="P52" t="str">
+        <f t="shared" si="7"/>
+        <v>FEARNLEY vs. FONSECA</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>156</v>
       </c>
@@ -2660,8 +7321,42 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H53" t="s">
+        <v>214</v>
+      </c>
+      <c r="I53">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J53" s="7">
+        <v>0.29709400000000002</v>
+      </c>
+      <c r="K53" s="7">
+        <f t="shared" si="2"/>
+        <v>0.70290600000000003</v>
+      </c>
+      <c r="L53" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M53" s="7">
+        <f t="shared" si="4"/>
+        <v>-5.2905999999999953E-2</v>
+      </c>
+      <c r="N53" s="7">
+        <f t="shared" si="5"/>
+        <v>0.35</v>
+      </c>
+      <c r="O53" s="7">
+        <f t="shared" si="6"/>
+        <v>0.65</v>
+      </c>
+      <c r="P53" t="str">
+        <f t="shared" si="7"/>
+        <v>BROOKSBY vs. GRIEKSPOOR</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>159</v>
       </c>
@@ -2685,8 +7380,43 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H54" t="s">
+        <v>161</v>
+      </c>
+      <c r="I54">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J54" s="7">
+        <f>(1-0.005)</f>
+        <v>0.995</v>
+      </c>
+      <c r="K54" s="7">
+        <f t="shared" si="2"/>
+        <v>5.0000000000000044E-3</v>
+      </c>
+      <c r="L54" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M54" s="7">
+        <f t="shared" si="4"/>
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="N54" s="7">
+        <f t="shared" si="5"/>
+        <v>0.59</v>
+      </c>
+      <c r="O54" s="7">
+        <f t="shared" si="6"/>
+        <v>0.41</v>
+      </c>
+      <c r="P54" t="str">
+        <f t="shared" si="7"/>
+        <v>LEHECKA vs. DELLIEN</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>162</v>
       </c>
@@ -2710,8 +7440,42 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H55" t="s">
+        <v>164</v>
+      </c>
+      <c r="I55">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J55" s="7">
+        <v>0.63293999999999995</v>
+      </c>
+      <c r="K55" s="7">
+        <f t="shared" si="2"/>
+        <v>0.36706000000000005</v>
+      </c>
+      <c r="L55" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M55" s="7">
+        <f t="shared" si="4"/>
+        <v>-7.7060000000000017E-2</v>
+      </c>
+      <c r="N55" s="7">
+        <f t="shared" si="5"/>
+        <v>0.71</v>
+      </c>
+      <c r="O55" s="7">
+        <f t="shared" si="6"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="P55" t="str">
+        <f t="shared" si="7"/>
+        <v>BELLUCCI vs. CRAWFORD</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>165</v>
       </c>
@@ -2735,8 +7499,43 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H56" t="s">
+        <v>222</v>
+      </c>
+      <c r="I56">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="7">
+        <f>(1-0.596858)</f>
+        <v>0.403142</v>
+      </c>
+      <c r="K56" s="7">
+        <f t="shared" si="2"/>
+        <v>0.596858</v>
+      </c>
+      <c r="L56" t="str">
+        <f t="shared" si="3"/>
+        <v>Perdem</v>
+      </c>
+      <c r="M56" s="7">
+        <f t="shared" si="4"/>
+        <v>-0.13685800000000004</v>
+      </c>
+      <c r="N56" s="7">
+        <f t="shared" si="5"/>
+        <v>0.54</v>
+      </c>
+      <c r="O56" s="7">
+        <f t="shared" si="6"/>
+        <v>0.46</v>
+      </c>
+      <c r="P56" t="str">
+        <f t="shared" si="7"/>
+        <v>NORRIE vs. BAUTISTA AGUT</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>168</v>
       </c>
@@ -2760,8 +7559,42 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H57" t="s">
+        <v>170</v>
+      </c>
+      <c r="I57">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J57" s="7">
+        <v>3.1477999999999999E-2</v>
+      </c>
+      <c r="K57" s="7">
+        <f t="shared" si="2"/>
+        <v>0.96852199999999999</v>
+      </c>
+      <c r="L57" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M57" s="7">
+        <f t="shared" si="4"/>
+        <v>0.27852200000000005</v>
+      </c>
+      <c r="N57" s="7">
+        <f t="shared" si="5"/>
+        <v>0.31</v>
+      </c>
+      <c r="O57" s="7">
+        <f t="shared" si="6"/>
+        <v>0.69</v>
+      </c>
+      <c r="P57" t="str">
+        <f t="shared" si="7"/>
+        <v>MOLLER vs. TIAFOE</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>171</v>
       </c>
@@ -2785,8 +7618,43 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H58" t="s">
+        <v>173</v>
+      </c>
+      <c r="I58">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J58" s="7">
+        <f>(1-0.375822)</f>
+        <v>0.62417800000000001</v>
+      </c>
+      <c r="K58" s="7">
+        <f t="shared" si="2"/>
+        <v>0.37582199999999999</v>
+      </c>
+      <c r="L58" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M58" s="7">
+        <f t="shared" si="4"/>
+        <v>4.178000000000015E-3</v>
+      </c>
+      <c r="N58" s="7">
+        <f t="shared" si="5"/>
+        <v>0.62</v>
+      </c>
+      <c r="O58" s="7">
+        <f t="shared" si="6"/>
+        <v>0.38</v>
+      </c>
+      <c r="P58" t="str">
+        <f t="shared" si="7"/>
+        <v>RUBLEV vs. DJERE</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>174</v>
       </c>
@@ -2810,8 +7678,42 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H59" t="s">
+        <v>215</v>
+      </c>
+      <c r="I59">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J59" s="7">
+        <v>0.69083300000000003</v>
+      </c>
+      <c r="K59" s="7">
+        <f t="shared" si="2"/>
+        <v>0.30916699999999997</v>
+      </c>
+      <c r="L59" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M59" s="7">
+        <f t="shared" si="4"/>
+        <v>3.9166999999999952E-2</v>
+      </c>
+      <c r="N59" s="7">
+        <f t="shared" si="5"/>
+        <v>0.73</v>
+      </c>
+      <c r="O59" s="7">
+        <f t="shared" si="6"/>
+        <v>0.27</v>
+      </c>
+      <c r="P59" t="str">
+        <f t="shared" si="7"/>
+        <v>BERGS vs. HARRIS</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>176</v>
       </c>
@@ -2835,8 +7737,42 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H60" t="s">
+        <v>178</v>
+      </c>
+      <c r="I60">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J60" s="7">
+        <v>0.670242</v>
+      </c>
+      <c r="K60" s="7">
+        <f t="shared" si="2"/>
+        <v>0.329758</v>
+      </c>
+      <c r="L60" t="str">
+        <f t="shared" si="3"/>
+        <v>Guanyem</v>
+      </c>
+      <c r="M60" s="7">
+        <f t="shared" si="4"/>
+        <v>0.25024200000000002</v>
+      </c>
+      <c r="N60" s="7">
+        <f t="shared" si="5"/>
+        <v>0.42</v>
+      </c>
+      <c r="O60" s="7">
+        <f t="shared" si="6"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="P60" t="str">
+        <f t="shared" si="7"/>
+        <v>MANNARINO vs. O'CONNELL</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>179</v>
       </c>
@@ -2860,8 +7796,42 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H61" t="s">
+        <v>216</v>
+      </c>
+      <c r="I61">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J61" s="7">
+        <v>0.24232100000000001</v>
+      </c>
+      <c r="K61" s="7">
+        <f t="shared" si="2"/>
+        <v>0.75767899999999999</v>
+      </c>
+      <c r="L61" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M61" s="7">
+        <f t="shared" si="4"/>
+        <v>-0.137679</v>
+      </c>
+      <c r="N61" s="7">
+        <f t="shared" si="5"/>
+        <v>0.38</v>
+      </c>
+      <c r="O61" s="7">
+        <f t="shared" si="6"/>
+        <v>0.62</v>
+      </c>
+      <c r="P61" t="str">
+        <f t="shared" si="7"/>
+        <v>ROYER vs. TSITSIPAS</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>182</v>
       </c>
@@ -2885,8 +7855,42 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H62" t="s">
+        <v>184</v>
+      </c>
+      <c r="I62">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J62" s="7">
+        <v>0.70440599999999998</v>
+      </c>
+      <c r="K62" s="7">
+        <f t="shared" si="2"/>
+        <v>0.29559400000000002</v>
+      </c>
+      <c r="L62" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M62" s="7">
+        <f t="shared" si="4"/>
+        <v>1.440600000000003E-2</v>
+      </c>
+      <c r="N62" s="7">
+        <f t="shared" si="5"/>
+        <v>0.69</v>
+      </c>
+      <c r="O62" s="7">
+        <f t="shared" si="6"/>
+        <v>0.31</v>
+      </c>
+      <c r="P62" t="str">
+        <f t="shared" si="7"/>
+        <v>AUGER-ALIASSIME vs. DUCKWORTH</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>185</v>
       </c>
@@ -2910,8 +7914,43 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H63" t="s">
+        <v>187</v>
+      </c>
+      <c r="I63">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J63" s="7">
+        <f>(0.251329)</f>
+        <v>0.25132900000000002</v>
+      </c>
+      <c r="K63" s="7">
+        <f t="shared" si="2"/>
+        <v>0.74867099999999998</v>
+      </c>
+      <c r="L63" t="str">
+        <f t="shared" si="3"/>
+        <v>Guanyem</v>
+      </c>
+      <c r="M63" s="7">
+        <f t="shared" si="4"/>
+        <v>-0.16867099999999996</v>
+      </c>
+      <c r="N63" s="7">
+        <f t="shared" si="5"/>
+        <v>0.42</v>
+      </c>
+      <c r="O63" s="7">
+        <f t="shared" si="6"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="P63" t="str">
+        <f t="shared" si="7"/>
+        <v>STRUFF vs. MISOLIC</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>188</v>
       </c>
@@ -2935,8 +7974,43 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H64" t="s">
+        <v>217</v>
+      </c>
+      <c r="I64">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="J64" s="7">
+        <f>(1-0.57688)</f>
+        <v>0.42312000000000005</v>
+      </c>
+      <c r="K64" s="7">
+        <f t="shared" si="2"/>
+        <v>0.57687999999999995</v>
+      </c>
+      <c r="L64" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M64" s="7">
+        <f t="shared" si="4"/>
+        <v>-3.6879999999999968E-2</v>
+      </c>
+      <c r="N64" s="7">
+        <f t="shared" si="5"/>
+        <v>0.46</v>
+      </c>
+      <c r="O64" s="7">
+        <f t="shared" si="6"/>
+        <v>0.54</v>
+      </c>
+      <c r="P64" t="str">
+        <f t="shared" si="7"/>
+        <v>TARVET vs. RIEDI</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>191</v>
       </c>
@@ -2960,34 +8034,156 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
+      <c r="H65" t="s">
+        <v>193</v>
+      </c>
+      <c r="I65">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="J65" s="7">
+        <f>(1-0.928853)</f>
+        <v>7.114699999999996E-2</v>
+      </c>
+      <c r="K65" s="7">
+        <f t="shared" si="2"/>
+        <v>0.92885300000000004</v>
+      </c>
+      <c r="L65" t="str">
+        <f t="shared" si="3"/>
+        <v>Empat</v>
+      </c>
+      <c r="M65" s="7">
+        <f t="shared" si="4"/>
+        <v>5.8853000000000044E-2</v>
+      </c>
+      <c r="N65" s="7">
+        <f t="shared" si="5"/>
+        <v>0.13</v>
+      </c>
+      <c r="O65" s="7">
+        <f t="shared" si="6"/>
+        <v>0.87</v>
+      </c>
+      <c r="P65" t="str">
+        <f t="shared" si="7"/>
+        <v>FOGNINI vs. ALCARAZ</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G65" xr:uid="{733616C7-25F8-4522-B3D0-0114E321248B}"/>
-  <conditionalFormatting sqref="G1:G1048576">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+  <conditionalFormatting sqref="G1:G1048576 H1:P1">
+    <cfRule type="cellIs" dxfId="28" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="8" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I65">
+    <cfRule type="cellIs" dxfId="26" priority="5" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="6" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L65">
+    <cfRule type="containsText" dxfId="24" priority="2" operator="containsText" text="Perdem">
+      <formula>NOT(ISERROR(SEARCH("Perdem",L2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="23" priority="3" operator="containsText" text="Guanyem">
+      <formula>NOT(ISERROR(SEARCH("Guanyem",L2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="22" priority="4" operator="containsText" text="Empat">
+      <formula>NOT(ISERROR(SEARCH("Empat",L2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M65">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED167E1B-415B-4CDC-9B3B-B08FEDF0F2A1}">
+  <dimension ref="A3:B6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="28.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="B3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B4" s="16">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B5" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B6" s="16">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA468E2B-B98F-49D5-BB7C-817B60D20F6A}">
-  <dimension ref="A1:K33"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:V33"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="18.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7265625" customWidth="1"/>
+    <col min="10" max="11" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="39.453125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3007,10 +8203,37 @@
         <v>198</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+        <v>244</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>182</v>
       </c>
@@ -3027,15 +8250,55 @@
         <v>187</v>
       </c>
       <c r="F2" t="str">
-        <f t="shared" ref="F2:F33" si="0">LEFT(IF(C2&gt;D2, A2, B2), FIND(",", IF(C2&gt;D2, A2, B2)) - 1)</f>
+        <f t="shared" ref="F2:H33" si="0">LEFT(IF(C2&gt;D2, A2, B2), FIND(",", IF(C2&gt;D2, A2, B2)) - 1)</f>
         <v>AUGER-ALIASSIME</v>
       </c>
       <c r="G2">
         <f t="shared" ref="G2:G33" si="1">IF(F2=E2, 1, 0)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H2" t="s">
+        <v>184</v>
+      </c>
+      <c r="I2">
+        <f>IF(H2=E2, 1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="J2" s="7">
+        <v>0.69422300000000003</v>
+      </c>
+      <c r="K2" s="7">
+        <f>1-J2</f>
+        <v>0.30577699999999997</v>
+      </c>
+      <c r="L2" t="str">
+        <f>IF(G2=I2, "Empat", IF(I2=1, "Guanyem", "Perdem"))</f>
+        <v>Empat</v>
+      </c>
+      <c r="M2" s="7">
+        <f>IF(ISNUMBER(SEARCH(E2, A2)), J2-(C2/100), K2-(D2/100))</f>
+        <v>2.5776999999999939E-2</v>
+      </c>
+      <c r="N2" s="7">
+        <f t="shared" ref="N2:O33" si="2">C2/100</f>
+        <v>0.72</v>
+      </c>
+      <c r="O2" s="7">
+        <f t="shared" si="2"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="P2" t="str">
+        <f t="shared" ref="P2:P33" si="3">_xlfn.TEXTBEFORE(A2, ",") &amp; " vs. " &amp; _xlfn.TEXTBEFORE(B2, ",")</f>
+        <v>AUGER-ALIASSIME vs. STRUFF</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="V2" s="4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>124</v>
       </c>
@@ -3059,8 +8322,49 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I33" si="4">IF(H3=E3, 1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="J3" s="7">
+        <v>0.65856000000000003</v>
+      </c>
+      <c r="K3" s="7">
+        <f t="shared" ref="K3:K33" si="5">1-J3</f>
+        <v>0.34143999999999997</v>
+      </c>
+      <c r="L3" t="str">
+        <f t="shared" ref="L3:L33" si="6">IF(G3=I3, "Empat", IF(I3=1, "Guanyem", "Perdem"))</f>
+        <v>Empat</v>
+      </c>
+      <c r="M3" s="7">
+        <f t="shared" ref="M3:M33" si="7">IF(ISNUMBER(SEARCH(E3, A3)), J3-(C3/100), K3-(D3/100))</f>
+        <v>-1.4399999999999968E-3</v>
+      </c>
+      <c r="N3" s="7">
+        <f t="shared" si="2"/>
+        <v>0.66</v>
+      </c>
+      <c r="O3" s="7">
+        <f t="shared" si="2"/>
+        <v>0.34</v>
+      </c>
+      <c r="P3" t="str">
+        <f t="shared" si="3"/>
+        <v>BORGES vs. HARRIS</v>
+      </c>
+      <c r="U3" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="V3" s="6">
+        <f>22/32</f>
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>63</v>
       </c>
@@ -3084,14 +8388,49 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K4" s="4">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J4" s="7">
+        <v>0.74198200000000003</v>
+      </c>
+      <c r="K4" s="7">
+        <f t="shared" si="5"/>
+        <v>0.25801799999999997</v>
+      </c>
+      <c r="L4" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M4" s="7">
+        <f t="shared" si="7"/>
+        <v>-8.0179999999999696E-3</v>
+      </c>
+      <c r="N4" s="7">
+        <f t="shared" si="2"/>
+        <v>0.75</v>
+      </c>
+      <c r="O4" s="7">
+        <f t="shared" si="2"/>
+        <v>0.25</v>
+      </c>
+      <c r="P4" t="str">
+        <f t="shared" si="3"/>
+        <v>COBOLLI vs. PINNINGTON JONES</v>
+      </c>
+      <c r="U4" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="V4" s="6">
+        <f>27/32</f>
+        <v>0.84375</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>75</v>
       </c>
@@ -3115,15 +8454,50 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J5" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="K5" s="6">
-        <f>22/32</f>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H5" t="s">
+        <v>77</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J5" s="7">
+        <f>1-0.037538</f>
+        <v>0.96246200000000004</v>
+      </c>
+      <c r="K5" s="7">
+        <f t="shared" si="5"/>
+        <v>3.753799999999996E-2</v>
+      </c>
+      <c r="L5" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M5" s="7">
+        <f t="shared" si="7"/>
+        <v>0.28246199999999999</v>
+      </c>
+      <c r="N5" s="7">
+        <f t="shared" si="2"/>
+        <v>0.68</v>
+      </c>
+      <c r="O5" s="7">
+        <f t="shared" si="2"/>
+        <v>0.32</v>
+      </c>
+      <c r="P5" t="str">
+        <f t="shared" si="3"/>
+        <v>DE MINAUR vs. CAZAUX</v>
+      </c>
+      <c r="U5" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="V5" s="6">
+        <f>23/32</f>
+        <v>0.71875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -3147,15 +8521,49 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J6" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="K6" s="6">
-        <f>27/32</f>
-        <v>0.84375</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H6" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J6" s="7">
+        <v>0.63892800000000005</v>
+      </c>
+      <c r="K6" s="7">
+        <f t="shared" si="5"/>
+        <v>0.36107199999999995</v>
+      </c>
+      <c r="L6" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M6" s="7">
+        <f t="shared" si="7"/>
+        <v>0.10892800000000002</v>
+      </c>
+      <c r="N6" s="7">
+        <f t="shared" si="2"/>
+        <v>0.53</v>
+      </c>
+      <c r="O6" s="7">
+        <f t="shared" si="2"/>
+        <v>0.47</v>
+      </c>
+      <c r="P6" t="str">
+        <f t="shared" si="3"/>
+        <v>DIMITROV vs. MOUTET</v>
+      </c>
+      <c r="U6" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="V6" s="6">
+        <f>22/32</f>
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>51</v>
       </c>
@@ -3179,15 +8587,43 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="J7" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="K7" s="6">
-        <f>23/32</f>
-        <v>0.71875</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H7" t="s">
+        <v>53</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="7">
+        <f>(1-0.170706)</f>
+        <v>0.82929399999999998</v>
+      </c>
+      <c r="K7" s="7">
+        <f t="shared" si="5"/>
+        <v>0.17070600000000002</v>
+      </c>
+      <c r="L7" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M7" s="7">
+        <f t="shared" si="7"/>
+        <v>2.070600000000003E-2</v>
+      </c>
+      <c r="N7" s="7">
+        <f t="shared" si="2"/>
+        <v>0.85</v>
+      </c>
+      <c r="O7" s="7">
+        <f t="shared" si="2"/>
+        <v>0.15</v>
+      </c>
+      <c r="P7" t="str">
+        <f t="shared" si="3"/>
+        <v>DRAPER vs. CILIC</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>93</v>
       </c>
@@ -3211,15 +8647,43 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="J8" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="K8" s="6">
-        <f>22/32</f>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H8" t="s">
+        <v>98</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J8" s="7">
+        <f>1-0.930533</f>
+        <v>6.9466999999999945E-2</v>
+      </c>
+      <c r="K8" s="7">
+        <f t="shared" si="5"/>
+        <v>0.93053300000000005</v>
+      </c>
+      <c r="L8" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M8" s="7">
+        <f t="shared" si="7"/>
+        <v>6.0533000000000059E-2</v>
+      </c>
+      <c r="N8" s="7">
+        <f t="shared" si="2"/>
+        <v>0.13</v>
+      </c>
+      <c r="O8" s="7">
+        <f t="shared" si="2"/>
+        <v>0.87</v>
+      </c>
+      <c r="P8" t="str">
+        <f t="shared" si="3"/>
+        <v>EVANS vs. DJOKOVIC</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>112</v>
       </c>
@@ -3243,8 +8707,43 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H9" t="s">
+        <v>116</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J9" s="7">
+        <f>1-0.53091</f>
+        <v>0.46909000000000001</v>
+      </c>
+      <c r="K9" s="7">
+        <f t="shared" si="5"/>
+        <v>0.53090999999999999</v>
+      </c>
+      <c r="L9" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M9" s="7">
+        <f t="shared" si="7"/>
+        <v>-0.22909000000000002</v>
+      </c>
+      <c r="N9" s="7">
+        <f t="shared" si="2"/>
+        <v>0.24</v>
+      </c>
+      <c r="O9" s="7">
+        <f t="shared" si="2"/>
+        <v>0.76</v>
+      </c>
+      <c r="P9" t="str">
+        <f t="shared" si="3"/>
+        <v>FERY vs. DARDERI</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>154</v>
       </c>
@@ -3268,8 +8767,43 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H10" t="s">
+        <v>155</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J10" s="7">
+        <f>1-0.313855</f>
+        <v>0.686145</v>
+      </c>
+      <c r="K10" s="7">
+        <f t="shared" si="5"/>
+        <v>0.313855</v>
+      </c>
+      <c r="L10" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M10" s="7">
+        <f t="shared" si="7"/>
+        <v>5.6145E-2</v>
+      </c>
+      <c r="N10" s="7">
+        <f t="shared" si="2"/>
+        <v>0.63</v>
+      </c>
+      <c r="O10" s="7">
+        <f t="shared" si="2"/>
+        <v>0.37</v>
+      </c>
+      <c r="P10" t="str">
+        <f t="shared" si="3"/>
+        <v>FONSECA vs. BROOKSBY</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>99</v>
       </c>
@@ -3293,8 +8827,43 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H11" t="s">
+        <v>101</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J11" s="7">
+        <f>1-0.212849</f>
+        <v>0.78715099999999993</v>
+      </c>
+      <c r="K11" s="7">
+        <f t="shared" si="5"/>
+        <v>0.21284900000000007</v>
+      </c>
+      <c r="L11" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M11" s="7">
+        <f t="shared" si="7"/>
+        <v>6.7150999999999961E-2</v>
+      </c>
+      <c r="N11" s="7">
+        <f t="shared" si="2"/>
+        <v>0.72</v>
+      </c>
+      <c r="O11" s="7">
+        <f t="shared" si="2"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="P11" t="str">
+        <f t="shared" si="3"/>
+        <v>FRITZ vs. DIALLO</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -3318,8 +8887,42 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H12" t="s">
+        <v>35</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J12" s="7">
+        <v>0.53553099999999998</v>
+      </c>
+      <c r="K12" s="7">
+        <f t="shared" si="5"/>
+        <v>0.46446900000000002</v>
+      </c>
+      <c r="L12" t="str">
+        <f t="shared" si="6"/>
+        <v>Guanyem</v>
+      </c>
+      <c r="M12" s="7">
+        <f t="shared" si="7"/>
+        <v>0.16553099999999998</v>
+      </c>
+      <c r="N12" s="7">
+        <f t="shared" si="2"/>
+        <v>0.37</v>
+      </c>
+      <c r="O12" s="7">
+        <f t="shared" si="2"/>
+        <v>0.63</v>
+      </c>
+      <c r="P12" t="str">
+        <f t="shared" si="3"/>
+        <v>FUCSOVICS vs. MONFILS</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>141</v>
       </c>
@@ -3343,8 +8946,42 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H13" t="s">
+        <v>146</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J13" s="7">
+        <v>0.412935</v>
+      </c>
+      <c r="K13" s="7">
+        <f t="shared" si="5"/>
+        <v>0.58706499999999995</v>
+      </c>
+      <c r="L13" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M13" s="7">
+        <f t="shared" si="7"/>
+        <v>5.7064999999999921E-2</v>
+      </c>
+      <c r="N13" s="7">
+        <f t="shared" si="2"/>
+        <v>0.47</v>
+      </c>
+      <c r="O13" s="7">
+        <f t="shared" si="2"/>
+        <v>0.53</v>
+      </c>
+      <c r="P13" t="str">
+        <f t="shared" si="3"/>
+        <v>GARIN vs. RINDERKNECH</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>69</v>
       </c>
@@ -3368,8 +9005,42 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H14" t="s">
+        <v>74</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J14" s="7">
+        <v>0.41428300000000001</v>
+      </c>
+      <c r="K14" s="7">
+        <f t="shared" si="5"/>
+        <v>0.58571700000000004</v>
+      </c>
+      <c r="L14" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M14" s="7">
+        <f t="shared" si="7"/>
+        <v>-2.4282999999999944E-2</v>
+      </c>
+      <c r="N14" s="7">
+        <f t="shared" si="2"/>
+        <v>0.39</v>
+      </c>
+      <c r="O14" s="7">
+        <f t="shared" si="2"/>
+        <v>0.61</v>
+      </c>
+      <c r="P14" t="str">
+        <f t="shared" si="3"/>
+        <v>GIRON vs. MENSIK</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>82</v>
       </c>
@@ -3393,8 +9064,42 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H15" t="s">
+        <v>86</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J15" s="7">
+        <v>0.301927</v>
+      </c>
+      <c r="K15" s="7">
+        <f t="shared" si="5"/>
+        <v>0.69807299999999994</v>
+      </c>
+      <c r="L15" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M15" s="7">
+        <f t="shared" si="7"/>
+        <v>2.1926999999999974E-2</v>
+      </c>
+      <c r="N15" s="7">
+        <f t="shared" si="2"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="O15" s="7">
+        <f t="shared" si="2"/>
+        <v>0.72</v>
+      </c>
+      <c r="P15" t="str">
+        <f t="shared" si="3"/>
+        <v>HOLMGREN vs. MACHAC</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>148</v>
       </c>
@@ -3418,8 +9123,42 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H16" t="s">
+        <v>149</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J16" s="7">
+        <v>0.59473699999999996</v>
+      </c>
+      <c r="K16" s="7">
+        <f t="shared" si="5"/>
+        <v>0.40526300000000004</v>
+      </c>
+      <c r="L16" t="str">
+        <f t="shared" si="6"/>
+        <v>Guanyem</v>
+      </c>
+      <c r="M16" s="7">
+        <f t="shared" si="7"/>
+        <v>0.21473699999999996</v>
+      </c>
+      <c r="N16" s="7">
+        <f t="shared" si="2"/>
+        <v>0.38</v>
+      </c>
+      <c r="O16" s="7">
+        <f t="shared" si="2"/>
+        <v>0.62</v>
+      </c>
+      <c r="P16" t="str">
+        <f t="shared" si="3"/>
+        <v>JARRY vs. TIEN</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>88</v>
       </c>
@@ -3443,8 +9182,43 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H17" t="s">
+        <v>89</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J17" s="7">
+        <f>1-0.274561</f>
+        <v>0.72543899999999994</v>
+      </c>
+      <c r="K17" s="7">
+        <f t="shared" si="5"/>
+        <v>0.27456100000000006</v>
+      </c>
+      <c r="L17" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M17" s="7">
+        <f t="shared" si="7"/>
+        <v>0.10543899999999995</v>
+      </c>
+      <c r="N17" s="7">
+        <f t="shared" si="2"/>
+        <v>0.62</v>
+      </c>
+      <c r="O17" s="7">
+        <f t="shared" si="2"/>
+        <v>0.38</v>
+      </c>
+      <c r="P17" t="str">
+        <f t="shared" si="3"/>
+        <v>KECMANOVIC vs. DE JONG</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>159</v>
       </c>
@@ -3468,8 +9242,43 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H18" t="s">
+        <v>161</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="7">
+        <f>1-0.083545</f>
+        <v>0.91645500000000002</v>
+      </c>
+      <c r="K18" s="7">
+        <f t="shared" si="5"/>
+        <v>8.354499999999998E-2</v>
+      </c>
+      <c r="L18" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M18" s="7">
+        <f t="shared" si="7"/>
+        <v>-0.35645500000000002</v>
+      </c>
+      <c r="N18" s="7">
+        <f t="shared" si="2"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="O18" s="7">
+        <f t="shared" si="2"/>
+        <v>0.44</v>
+      </c>
+      <c r="P18" t="str">
+        <f t="shared" si="3"/>
+        <v>LEHECKA vs. BELLUCCI</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>136</v>
       </c>
@@ -3493,8 +9302,42 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H19" t="s">
+        <v>140</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J19" s="7">
+        <v>0.48952899999999999</v>
+      </c>
+      <c r="K19" s="7">
+        <f t="shared" si="5"/>
+        <v>0.51047100000000001</v>
+      </c>
+      <c r="L19" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M19" s="7">
+        <f t="shared" si="7"/>
+        <v>6.9529000000000007E-2</v>
+      </c>
+      <c r="N19" s="7">
+        <f t="shared" si="2"/>
+        <v>0.42</v>
+      </c>
+      <c r="O19" s="7">
+        <f t="shared" si="2"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="P19" t="str">
+        <f t="shared" si="3"/>
+        <v>MAJCHRZAK vs. QUINN</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>176</v>
       </c>
@@ -3518,8 +9361,42 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H20" t="s">
+        <v>178</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J20" s="7">
+        <v>0.69118900000000005</v>
+      </c>
+      <c r="K20" s="7">
+        <f t="shared" si="5"/>
+        <v>0.30881099999999995</v>
+      </c>
+      <c r="L20" t="str">
+        <f t="shared" si="6"/>
+        <v>Guanyem</v>
+      </c>
+      <c r="M20" s="7">
+        <f t="shared" si="7"/>
+        <v>0.27118900000000007</v>
+      </c>
+      <c r="N20" s="7">
+        <f t="shared" si="2"/>
+        <v>0.42</v>
+      </c>
+      <c r="O20" s="7">
+        <f t="shared" si="2"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="P20" t="str">
+        <f t="shared" si="3"/>
+        <v>MANNARINO vs. ROYER</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>58</v>
       </c>
@@ -3543,8 +9420,42 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H21" t="s">
+        <v>62</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J21" s="7">
+        <v>0.49672500000000003</v>
+      </c>
+      <c r="K21" s="7">
+        <f t="shared" si="5"/>
+        <v>0.50327499999999992</v>
+      </c>
+      <c r="L21" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M21" s="7">
+        <f t="shared" si="7"/>
+        <v>-7.6725000000000043E-2</v>
+      </c>
+      <c r="N21" s="7">
+        <f t="shared" si="2"/>
+        <v>0.42</v>
+      </c>
+      <c r="O21" s="7">
+        <f t="shared" si="2"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="P21" t="str">
+        <f t="shared" si="3"/>
+        <v>MAROZSAN vs. MUNAR</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -3568,8 +9479,42 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H22" t="s">
+        <v>14</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J22" s="7">
+        <v>0.41036899999999998</v>
+      </c>
+      <c r="K22" s="7">
+        <f t="shared" si="5"/>
+        <v>0.58963100000000002</v>
+      </c>
+      <c r="L22" t="str">
+        <f t="shared" si="6"/>
+        <v>Perdem</v>
+      </c>
+      <c r="M22" s="7">
+        <f t="shared" si="7"/>
+        <v>-0.13963100000000006</v>
+      </c>
+      <c r="N22" s="7">
+        <f t="shared" si="2"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="O22" s="7">
+        <f t="shared" si="2"/>
+        <v>0.45</v>
+      </c>
+      <c r="P22" t="str">
+        <f t="shared" si="3"/>
+        <v>MARTÍNEZ vs. NAVONE</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>129</v>
       </c>
@@ -3593,8 +9538,43 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H23" t="s">
+        <v>134</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J23" s="7">
+        <f>1-0.91519</f>
+        <v>8.4810000000000052E-2</v>
+      </c>
+      <c r="K23" s="7">
+        <f t="shared" si="5"/>
+        <v>0.91518999999999995</v>
+      </c>
+      <c r="L23" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M23" s="7">
+        <f t="shared" si="7"/>
+        <v>0.28518999999999994</v>
+      </c>
+      <c r="N23" s="7">
+        <f t="shared" si="2"/>
+        <v>0.37</v>
+      </c>
+      <c r="O23" s="7">
+        <f t="shared" si="2"/>
+        <v>0.63</v>
+      </c>
+      <c r="P23" t="str">
+        <f t="shared" si="3"/>
+        <v>MOCHIZUKI vs. KHACHANOV</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -3618,8 +9598,42 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H24" t="s">
+        <v>41</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J24" s="7">
+        <v>0.63892800000000005</v>
+      </c>
+      <c r="K24" s="7">
+        <f t="shared" si="5"/>
+        <v>0.36107199999999995</v>
+      </c>
+      <c r="L24" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M24" s="7">
+        <f t="shared" si="7"/>
+        <v>8.8928000000000007E-2</v>
+      </c>
+      <c r="N24" s="7">
+        <f t="shared" si="2"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="O24" s="7">
+        <f t="shared" si="2"/>
+        <v>0.45</v>
+      </c>
+      <c r="P24" t="str">
+        <f t="shared" si="3"/>
+        <v>NAKASHIMA vs. OPELKA</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>165</v>
       </c>
@@ -3643,8 +9657,42 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H25" t="s">
+        <v>170</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="7">
+        <v>0.44528000000000001</v>
+      </c>
+      <c r="K25" s="7">
+        <f t="shared" si="5"/>
+        <v>0.55471999999999999</v>
+      </c>
+      <c r="L25" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M25" s="7">
+        <f t="shared" si="7"/>
+        <v>6.5280000000000005E-2</v>
+      </c>
+      <c r="N25" s="7">
+        <f t="shared" si="2"/>
+        <v>0.38</v>
+      </c>
+      <c r="O25" s="7">
+        <f t="shared" si="2"/>
+        <v>0.63</v>
+      </c>
+      <c r="P25" t="str">
+        <f t="shared" si="3"/>
+        <v>NORRIE vs. TIAFOE</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>21</v>
       </c>
@@ -3668,8 +9716,42 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H26" t="s">
+        <v>26</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="7">
+        <v>0.160053</v>
+      </c>
+      <c r="K26" s="7">
+        <f t="shared" si="5"/>
+        <v>0.839947</v>
+      </c>
+      <c r="L26" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M26" s="7">
+        <f t="shared" si="7"/>
+        <v>-0.10994700000000002</v>
+      </c>
+      <c r="N26" s="7">
+        <f t="shared" si="2"/>
+        <v>0.27</v>
+      </c>
+      <c r="O26" s="7">
+        <f t="shared" si="2"/>
+        <v>0.73</v>
+      </c>
+      <c r="P26" t="str">
+        <f t="shared" si="3"/>
+        <v>OFNER vs. PAUL</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>171</v>
       </c>
@@ -3693,8 +9775,43 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H27" t="s">
+        <v>173</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J27" s="7">
+        <f>1-0.291186</f>
+        <v>0.70881400000000006</v>
+      </c>
+      <c r="K27" s="7">
+        <f t="shared" si="5"/>
+        <v>0.29118599999999994</v>
+      </c>
+      <c r="L27" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M27" s="7">
+        <f t="shared" si="7"/>
+        <v>-6.1185999999999963E-2</v>
+      </c>
+      <c r="N27" s="7">
+        <f t="shared" si="2"/>
+        <v>0.77</v>
+      </c>
+      <c r="O27" s="7">
+        <f t="shared" si="2"/>
+        <v>0.23</v>
+      </c>
+      <c r="P27" t="str">
+        <f t="shared" si="3"/>
+        <v>RUBLEV vs. HARRIS</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -3718,8 +9835,43 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H28" t="s">
+        <v>29</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J28" s="7">
+        <f>1-0.425766</f>
+        <v>0.57423400000000002</v>
+      </c>
+      <c r="K28" s="7">
+        <f t="shared" si="5"/>
+        <v>0.42576599999999998</v>
+      </c>
+      <c r="L28" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M28" s="7">
+        <f t="shared" si="7"/>
+        <v>-0.10576600000000003</v>
+      </c>
+      <c r="N28" s="7">
+        <f t="shared" si="2"/>
+        <v>0.68</v>
+      </c>
+      <c r="O28" s="7">
+        <f t="shared" si="2"/>
+        <v>0.32</v>
+      </c>
+      <c r="P28" t="str">
+        <f t="shared" si="3"/>
+        <v>SHELTON vs. HIJIKATA</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>3</v>
       </c>
@@ -3743,8 +9895,42 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H29" t="s">
+        <v>5</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J29" s="7">
+        <v>0.96193600000000001</v>
+      </c>
+      <c r="K29" s="7">
+        <f t="shared" si="5"/>
+        <v>3.8063999999999987E-2</v>
+      </c>
+      <c r="L29" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M29" s="7">
+        <f t="shared" si="7"/>
+        <v>6.1935999999999991E-2</v>
+      </c>
+      <c r="N29" s="7">
+        <f t="shared" si="2"/>
+        <v>0.9</v>
+      </c>
+      <c r="O29" s="7">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="P29" t="str">
+        <f t="shared" si="3"/>
+        <v>SINNER vs. VUKIC</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>46</v>
       </c>
@@ -3768,8 +9954,43 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H30" t="s">
+        <v>47</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J30" s="7">
+        <f>1-0.386971</f>
+        <v>0.61302900000000005</v>
+      </c>
+      <c r="K30" s="7">
+        <f t="shared" si="5"/>
+        <v>0.38697099999999995</v>
+      </c>
+      <c r="L30" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M30" s="7">
+        <f t="shared" si="7"/>
+        <v>-3.6970999999999976E-2</v>
+      </c>
+      <c r="N30" s="7">
+        <f t="shared" si="2"/>
+        <v>0.65</v>
+      </c>
+      <c r="O30" s="7">
+        <f t="shared" si="2"/>
+        <v>0.35</v>
+      </c>
+      <c r="P30" t="str">
+        <f t="shared" si="3"/>
+        <v>SONEGO vs. MUSETTI</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>188</v>
       </c>
@@ -3793,8 +10014,43 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H31" t="s">
+        <v>193</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J31" s="7">
+        <f>1-0.745963</f>
+        <v>0.25403699999999996</v>
+      </c>
+      <c r="K31" s="7">
+        <f t="shared" si="5"/>
+        <v>0.74596300000000004</v>
+      </c>
+      <c r="L31" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M31" s="7">
+        <f t="shared" si="7"/>
+        <v>-0.1940369999999999</v>
+      </c>
+      <c r="N31" s="7">
+        <f t="shared" si="2"/>
+        <v>0.06</v>
+      </c>
+      <c r="O31" s="7">
+        <f t="shared" si="2"/>
+        <v>0.94</v>
+      </c>
+      <c r="P31" t="str">
+        <f t="shared" si="3"/>
+        <v>TARVET vs. ALCARAZ</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>118</v>
       </c>
@@ -3818,8 +10074,43 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H32" t="s">
+        <v>122</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J32" s="7">
+        <f>(1-0.613034)</f>
+        <v>0.38696600000000003</v>
+      </c>
+      <c r="K32" s="7">
+        <f t="shared" si="5"/>
+        <v>0.61303399999999997</v>
+      </c>
+      <c r="L32" t="str">
+        <f t="shared" si="6"/>
+        <v>Perdem</v>
+      </c>
+      <c r="M32" s="7">
+        <f t="shared" si="7"/>
+        <v>-0.14303399999999999</v>
+      </c>
+      <c r="N32" s="7">
+        <f t="shared" si="2"/>
+        <v>0.53</v>
+      </c>
+      <c r="O32" s="7">
+        <f t="shared" si="2"/>
+        <v>0.47</v>
+      </c>
+      <c r="P32" t="str">
+        <f t="shared" si="3"/>
+        <v>THOMPSON vs. BONZI</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>106</v>
       </c>
@@ -3842,6 +10133,41 @@
       <c r="G33">
         <f t="shared" si="1"/>
         <v>1</v>
+      </c>
+      <c r="H33" t="s">
+        <v>110</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J33" s="7">
+        <f>1-0.763238</f>
+        <v>0.23676200000000003</v>
+      </c>
+      <c r="K33" s="7">
+        <f t="shared" si="5"/>
+        <v>0.76323799999999997</v>
+      </c>
+      <c r="L33" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M33" s="7">
+        <f t="shared" si="7"/>
+        <v>0.11323799999999995</v>
+      </c>
+      <c r="N33" s="7">
+        <f t="shared" si="2"/>
+        <v>0.35</v>
+      </c>
+      <c r="O33" s="7">
+        <f t="shared" si="2"/>
+        <v>0.65</v>
+      </c>
+      <c r="P33" t="str">
+        <f t="shared" si="3"/>
+        <v>VAN DE ZANDSCHULP vs. DAVIDOVICH FOKINA</v>
       </c>
     </row>
   </sheetData>
@@ -3851,32 +10177,78 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="G2:G33">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="9" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="10" operator="equal">
       <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J1:P1">
+    <cfRule type="cellIs" dxfId="19" priority="7" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="18" priority="8" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I33">
+    <cfRule type="cellIs" dxfId="17" priority="5" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="6" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L33">
+    <cfRule type="containsText" dxfId="15" priority="2" operator="containsText" text="Perdem">
+      <formula>NOT(ISERROR(SEARCH("Perdem",L2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="Guanyem">
+      <formula>NOT(ISERROR(SEARCH("Guanyem",L2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="13" priority="4" operator="containsText" text="Empat">
+      <formula>NOT(ISERROR(SEARCH("Empat",L2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M33">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACEA3751-FF78-4C3C-8ABE-F983B99484C6}">
-  <dimension ref="A1:K17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:T17"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3896,10 +10268,37 @@
         <v>198</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+        <v>244</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -3923,8 +10322,43 @@
         <f>IF(F2=E2, 1, 0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <f>IF(H2=E2, 1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="J2" s="7">
+        <f>1-0.035207</f>
+        <v>0.96479300000000001</v>
+      </c>
+      <c r="K2" s="7">
+        <f>1-J2</f>
+        <v>3.5206999999999988E-2</v>
+      </c>
+      <c r="L2" t="str">
+        <f>IF(G2=I2, "Empat", IF(I2=1, "Guanyem", "Perdem"))</f>
+        <v>Empat</v>
+      </c>
+      <c r="M2" s="7">
+        <f>IF(ISNUMBER(SEARCH(E2, A2)), J2-(C2/100), K2-(D2/100))</f>
+        <v>0.11479300000000003</v>
+      </c>
+      <c r="N2" s="7">
+        <f t="shared" ref="N2:O2" si="0">C2/100</f>
+        <v>0.85</v>
+      </c>
+      <c r="O2" s="7">
+        <f t="shared" si="0"/>
+        <v>0.15</v>
+      </c>
+      <c r="P2" t="str">
+        <f t="shared" ref="P2" si="1">_xlfn.TEXTBEFORE(A2, ",") &amp; " vs. " &amp; _xlfn.TEXTBEFORE(B2, ",")</f>
+        <v>SINNER vs. MARTÍNEZ</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -3941,15 +10375,55 @@
         <v>17</v>
       </c>
       <c r="F3" t="str">
-        <f t="shared" ref="F3:F17" si="0">LEFT(IF(C3&gt;D3, A3, B3), FIND(",", IF(C3&gt;D3, A3, B3)) - 1)</f>
+        <f t="shared" ref="F3:H17" si="2">LEFT(IF(C3&gt;D3, A3, B3), FIND(",", IF(C3&gt;D3, A3, B3)) - 1)</f>
         <v>DIMITROV</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G17" si="1">IF(F3=E3, 1, 0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+        <f t="shared" ref="G3:G17" si="3">IF(F3=E3, 1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I17" si="4">IF(H3=E3, 1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="J3" s="7">
+        <v>0.81166700000000003</v>
+      </c>
+      <c r="K3" s="7">
+        <f t="shared" ref="K3:K17" si="5">1-J3</f>
+        <v>0.18833299999999997</v>
+      </c>
+      <c r="L3" t="str">
+        <f t="shared" ref="L3:L17" si="6">IF(G3=I3, "Empat", IF(I3=1, "Guanyem", "Perdem"))</f>
+        <v>Empat</v>
+      </c>
+      <c r="M3" s="7">
+        <f t="shared" ref="M3:M17" si="7">IF(ISNUMBER(SEARCH(E3, A3)), J3-(C3/100), K3-(D3/100))</f>
+        <v>0.11166700000000007</v>
+      </c>
+      <c r="N3" s="7">
+        <f t="shared" ref="N3:N17" si="8">C3/100</f>
+        <v>0.7</v>
+      </c>
+      <c r="O3" s="7">
+        <f t="shared" ref="O3:O17" si="9">D3/100</f>
+        <v>0.3</v>
+      </c>
+      <c r="P3" t="str">
+        <f t="shared" ref="P3:P17" si="10">_xlfn.TEXTBEFORE(A3, ",") &amp; " vs. " &amp; _xlfn.TEXTBEFORE(B3, ",")</f>
+        <v>DIMITROV vs. OFNER</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="T3" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -3966,21 +10440,57 @@
         <v>29</v>
       </c>
       <c r="F4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>SHELTON</v>
       </c>
       <c r="G4">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K4" s="4">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J4" s="7">
+        <f>1-0.242251</f>
+        <v>0.75774900000000001</v>
+      </c>
+      <c r="K4" s="7">
+        <f t="shared" si="5"/>
+        <v>0.24225099999999999</v>
+      </c>
+      <c r="L4" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M4" s="7">
+        <f t="shared" si="7"/>
+        <v>7.7748999999999957E-2</v>
+      </c>
+      <c r="N4" s="7">
+        <f t="shared" si="8"/>
+        <v>0.68</v>
+      </c>
+      <c r="O4" s="7">
+        <f t="shared" si="9"/>
+        <v>0.32</v>
+      </c>
+      <c r="P4" t="str">
+        <f t="shared" si="10"/>
+        <v>SHELTON vs. FUCSOVICS</v>
+      </c>
+      <c r="S4" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="T4" s="6">
+        <f>11/16</f>
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -3988,31 +10498,65 @@
         <v>46</v>
       </c>
       <c r="C5">
+        <v>51</v>
+      </c>
+      <c r="D5">
         <v>49</v>
       </c>
-      <c r="D5">
-        <v>51</v>
-      </c>
       <c r="E5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="2"/>
+        <v>NAKASHIMA</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
         <v>41</v>
       </c>
-      <c r="F5" t="str">
-        <f t="shared" si="0"/>
-        <v>SONEGO</v>
-      </c>
-      <c r="G5">
-        <f t="shared" si="1"/>
+      <c r="I5">
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J5" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="K5" s="6">
-        <f>11/16</f>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="J5" s="7">
+        <v>0.69072900000000004</v>
+      </c>
+      <c r="K5" s="7">
+        <f t="shared" si="5"/>
+        <v>0.30927099999999996</v>
+      </c>
+      <c r="L5" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M5" s="7">
+        <f t="shared" si="7"/>
+        <v>-0.18072900000000003</v>
+      </c>
+      <c r="N5" s="7">
+        <f t="shared" si="8"/>
+        <v>0.51</v>
+      </c>
+      <c r="O5" s="7">
+        <f t="shared" si="9"/>
+        <v>0.49</v>
+      </c>
+      <c r="P5" t="str">
+        <f t="shared" si="10"/>
+        <v>NAKASHIMA vs. SONEGO</v>
+      </c>
+      <c r="S5" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="T5" s="6">
+        <f>15/16</f>
+        <v>0.9375</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>55</v>
       </c>
@@ -4029,22 +10573,56 @@
         <v>56</v>
       </c>
       <c r="F6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>MUNAR</v>
       </c>
       <c r="G6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J6" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="K6" s="6">
-        <f>15/16</f>
-        <v>0.9375</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="H6" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J6" s="7">
+        <v>0.662385</v>
+      </c>
+      <c r="K6" s="7">
+        <f t="shared" si="5"/>
+        <v>0.337615</v>
+      </c>
+      <c r="L6" t="str">
+        <f t="shared" si="6"/>
+        <v>Guanyem</v>
+      </c>
+      <c r="M6" s="7">
+        <f t="shared" si="7"/>
+        <v>0.23238500000000001</v>
+      </c>
+      <c r="N6" s="7">
+        <f t="shared" si="8"/>
+        <v>0.43</v>
+      </c>
+      <c r="O6" s="7">
+        <f t="shared" si="9"/>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="P6" t="str">
+        <f t="shared" si="10"/>
+        <v>CILIC vs. MUNAR</v>
+      </c>
+      <c r="S6" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="T6" s="6">
+        <f>12/16</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>63</v>
       </c>
@@ -4061,22 +10639,56 @@
         <v>65</v>
       </c>
       <c r="F7" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>MENSIK</v>
       </c>
       <c r="G7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="H7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="7">
+        <v>0.37805800000000001</v>
+      </c>
+      <c r="K7" s="7">
+        <f t="shared" si="5"/>
+        <v>0.62194199999999999</v>
+      </c>
+      <c r="L7" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M7" s="7">
+        <f t="shared" si="7"/>
+        <v>-4.1941999999999979E-2</v>
+      </c>
+      <c r="N7" s="7">
+        <f t="shared" si="8"/>
+        <v>0.42</v>
+      </c>
+      <c r="O7" s="7">
+        <f t="shared" si="9"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="P7" t="str">
+        <f t="shared" si="10"/>
+        <v>COBOLLI vs. MENSIK</v>
+      </c>
+      <c r="S7" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="K7" s="6">
+      <c r="T7" s="6">
         <f>12/16</f>
         <v>0.75</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>75</v>
       </c>
@@ -4093,22 +10705,49 @@
         <v>77</v>
       </c>
       <c r="F8" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>DE MINAUR</v>
       </c>
       <c r="G8">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="J8" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="K8" s="6">
-        <f>12/16</f>
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>77</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J8" s="7">
+        <v>0.89724199999999998</v>
+      </c>
+      <c r="K8" s="7">
+        <f t="shared" si="5"/>
+        <v>0.10275800000000002</v>
+      </c>
+      <c r="L8" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M8" s="7">
+        <f t="shared" si="7"/>
+        <v>0.17724200000000001</v>
+      </c>
+      <c r="N8" s="7">
+        <f t="shared" si="8"/>
+        <v>0.72</v>
+      </c>
+      <c r="O8" s="7">
+        <f t="shared" si="9"/>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="P8" t="str">
+        <f t="shared" si="10"/>
+        <v>DE MINAUR vs. HOLMGREN</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>88</v>
       </c>
@@ -4125,15 +10764,50 @@
         <v>98</v>
       </c>
       <c r="F9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>DJOKOVIC</v>
       </c>
       <c r="G9">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H9" t="s">
+        <v>98</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J9" s="7">
+        <f>1-0.988624</f>
+        <v>1.1376000000000053E-2</v>
+      </c>
+      <c r="K9" s="7">
+        <f t="shared" si="5"/>
+        <v>0.98862399999999995</v>
+      </c>
+      <c r="L9" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M9" s="7">
+        <f t="shared" si="7"/>
+        <v>0.21862399999999993</v>
+      </c>
+      <c r="N9" s="7">
+        <f t="shared" si="8"/>
+        <v>0.23</v>
+      </c>
+      <c r="O9" s="7">
+        <f t="shared" si="9"/>
+        <v>0.77</v>
+      </c>
+      <c r="P9" t="str">
+        <f t="shared" si="10"/>
+        <v>KECMANOVIC vs. DJOKOVIC</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>99</v>
       </c>
@@ -4150,15 +10824,50 @@
         <v>101</v>
       </c>
       <c r="F10" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>FRITZ</v>
       </c>
       <c r="G10">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>101</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J10" s="7">
+        <f>1-0.292478</f>
+        <v>0.70752199999999998</v>
+      </c>
+      <c r="K10" s="7">
+        <f t="shared" si="5"/>
+        <v>0.29247800000000002</v>
+      </c>
+      <c r="L10" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M10" s="7">
+        <f t="shared" si="7"/>
+        <v>5.7521999999999962E-2</v>
+      </c>
+      <c r="N10" s="7">
+        <f t="shared" si="8"/>
+        <v>0.65</v>
+      </c>
+      <c r="O10" s="7">
+        <f t="shared" si="9"/>
+        <v>0.35</v>
+      </c>
+      <c r="P10" t="str">
+        <f t="shared" si="10"/>
+        <v>FRITZ vs. DAVIDOVICH FOKINA</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>114</v>
       </c>
@@ -4172,18 +10881,52 @@
         <v>48</v>
       </c>
       <c r="E11" t="s">
-        <v>116</v>
+        <v>246</v>
       </c>
       <c r="F11" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>DARDERI</v>
       </c>
       <c r="G11">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>246</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J11" s="7">
+        <v>0.384932</v>
+      </c>
+      <c r="K11" s="7">
+        <f t="shared" si="5"/>
+        <v>0.61506799999999995</v>
+      </c>
+      <c r="L11" t="str">
+        <f t="shared" si="6"/>
+        <v>Guanyem</v>
+      </c>
+      <c r="M11" s="7">
+        <f t="shared" si="7"/>
+        <v>0.13506799999999997</v>
+      </c>
+      <c r="N11" s="7">
+        <f t="shared" si="8"/>
+        <v>0.52</v>
+      </c>
+      <c r="O11" s="7">
+        <f t="shared" si="9"/>
+        <v>0.48</v>
+      </c>
+      <c r="P11" t="str">
+        <f t="shared" si="10"/>
+        <v>DARDERI vs. THOMPSON</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>124</v>
       </c>
@@ -4200,15 +10943,49 @@
         <v>134</v>
       </c>
       <c r="F12" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>KHACHANOV</v>
       </c>
       <c r="G12">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H12" t="s">
+        <v>134</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J12" s="7">
+        <v>0.366365</v>
+      </c>
+      <c r="K12" s="7">
+        <f t="shared" si="5"/>
+        <v>0.63363499999999995</v>
+      </c>
+      <c r="L12" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M12" s="7">
+        <f t="shared" si="7"/>
+        <v>0.11363499999999993</v>
+      </c>
+      <c r="N12" s="7">
+        <f t="shared" si="8"/>
+        <v>0.48</v>
+      </c>
+      <c r="O12" s="7">
+        <f t="shared" si="9"/>
+        <v>0.52</v>
+      </c>
+      <c r="P12" t="str">
+        <f t="shared" si="10"/>
+        <v>BORGES vs. KHACHANOV</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>136</v>
       </c>
@@ -4225,15 +11002,50 @@
         <v>146</v>
       </c>
       <c r="F13" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>RINDERKNECH</v>
       </c>
       <c r="G13">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H13" t="s">
+        <v>137</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J13" s="7">
+        <f>1-0.445872</f>
+        <v>0.55412799999999995</v>
+      </c>
+      <c r="K13" s="7">
+        <f t="shared" si="5"/>
+        <v>0.44587200000000005</v>
+      </c>
+      <c r="L13" t="str">
+        <f t="shared" si="6"/>
+        <v>Perdem</v>
+      </c>
+      <c r="M13" s="7">
+        <f t="shared" si="7"/>
+        <v>-0.12412799999999991</v>
+      </c>
+      <c r="N13" s="7">
+        <f t="shared" si="8"/>
+        <v>0.43</v>
+      </c>
+      <c r="O13" s="7">
+        <f t="shared" si="9"/>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="P13" t="str">
+        <f t="shared" si="10"/>
+        <v>MAJCHRZAK vs. RINDERKNECH</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>148</v>
       </c>
@@ -4250,15 +11062,50 @@
         <v>149</v>
       </c>
       <c r="F14" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>FONSECA</v>
       </c>
       <c r="G14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H14" t="s">
+        <v>155</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="7">
+        <f>1-0.736691</f>
+        <v>0.26330900000000002</v>
+      </c>
+      <c r="K14" s="7">
+        <f t="shared" si="5"/>
+        <v>0.73669099999999998</v>
+      </c>
+      <c r="L14" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M14" s="7">
+        <f t="shared" si="7"/>
+        <v>-8.6690999999999963E-2</v>
+      </c>
+      <c r="N14" s="7">
+        <f t="shared" si="8"/>
+        <v>0.35</v>
+      </c>
+      <c r="O14" s="7">
+        <f t="shared" si="9"/>
+        <v>0.65</v>
+      </c>
+      <c r="P14" t="str">
+        <f t="shared" si="10"/>
+        <v>JARRY vs. FONSECA</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>162</v>
       </c>
@@ -4275,15 +11122,49 @@
         <v>167</v>
       </c>
       <c r="F15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>BELLUCCI</v>
       </c>
       <c r="G15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H15" t="s">
+        <v>167</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J15" s="7">
+        <v>0.30677500000000002</v>
+      </c>
+      <c r="K15" s="7">
+        <f t="shared" si="5"/>
+        <v>0.69322499999999998</v>
+      </c>
+      <c r="L15" t="str">
+        <f t="shared" si="6"/>
+        <v>Guanyem</v>
+      </c>
+      <c r="M15" s="7">
+        <f t="shared" si="7"/>
+        <v>0.25322499999999998</v>
+      </c>
+      <c r="N15" s="7">
+        <f t="shared" si="8"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="O15" s="7">
+        <f t="shared" si="9"/>
+        <v>0.44</v>
+      </c>
+      <c r="P15" t="str">
+        <f t="shared" si="10"/>
+        <v>BELLUCCI vs. NORRIE</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>171</v>
       </c>
@@ -4300,15 +11181,50 @@
         <v>173</v>
       </c>
       <c r="F16" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>RUBLEV</v>
       </c>
       <c r="G16">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H16" t="s">
+        <v>173</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J16" s="7">
+        <f>1-0.355816</f>
+        <v>0.64418399999999998</v>
+      </c>
+      <c r="K16" s="7">
+        <f t="shared" si="5"/>
+        <v>0.35581600000000002</v>
+      </c>
+      <c r="L16" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M16" s="7">
+        <f t="shared" si="7"/>
+        <v>-6.5815999999999986E-2</v>
+      </c>
+      <c r="N16" s="7">
+        <f t="shared" si="8"/>
+        <v>0.71</v>
+      </c>
+      <c r="O16" s="7">
+        <f t="shared" si="9"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="P16" t="str">
+        <f t="shared" si="10"/>
+        <v>RUBLEV vs. MANNARINO</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>185</v>
       </c>
@@ -4325,12 +11241,47 @@
         <v>193</v>
       </c>
       <c r="F17" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>ALCARAZ</v>
       </c>
       <c r="G17">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H17" t="s">
+        <v>193</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J17" s="7">
+        <f>1-0.950917</f>
+        <v>4.9082999999999988E-2</v>
+      </c>
+      <c r="K17" s="7">
+        <f t="shared" si="5"/>
+        <v>0.95091700000000001</v>
+      </c>
+      <c r="L17" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M17" s="7">
+        <f t="shared" si="7"/>
+        <v>6.0916999999999999E-2</v>
+      </c>
+      <c r="N17" s="7">
+        <f t="shared" si="8"/>
+        <v>0.11</v>
+      </c>
+      <c r="O17" s="7">
+        <f t="shared" si="9"/>
+        <v>0.89</v>
+      </c>
+      <c r="P17" t="str">
+        <f t="shared" si="10"/>
+        <v>STRUFF vs. ALCARAZ</v>
       </c>
     </row>
   </sheetData>
@@ -4340,292 +11291,50 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="G2:G17">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="9" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7B8FC45-B22C-4AD5-9F0B-B6BE598565A3}">
-  <dimension ref="A1:K9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.83203125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2">
-        <v>86</v>
-      </c>
-      <c r="D2">
-        <v>14</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="str">
-        <f>LEFT(IF(C2&gt;D2, A2, B2), FIND(",", IF(C2&gt;D2, A2, B2)) - 1)</f>
-        <v>SINNER</v>
-      </c>
-      <c r="G2">
-        <f>IF(F2=E2, 1, 0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3">
-        <v>63</v>
-      </c>
-      <c r="D3">
-        <v>37</v>
-      </c>
-      <c r="E3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" t="str">
-        <f t="shared" ref="F3:F9" si="0">LEFT(IF(C3&gt;D3, A3, B3), FIND(",", IF(C3&gt;D3, A3, B3)) - 1)</f>
-        <v>SHELTON</v>
-      </c>
-      <c r="G3">
-        <f t="shared" ref="G3:G9" si="1">IF(F3=E3, 1, 0)</f>
-        <v>1</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K3" s="4">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C4">
-        <v>32</v>
-      </c>
-      <c r="D4">
-        <v>68</v>
-      </c>
-      <c r="E4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" t="str">
-        <f t="shared" si="0"/>
-        <v>COBOLLI</v>
-      </c>
-      <c r="G4">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="K4" s="6">
-        <f>8/8</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>75</v>
-      </c>
-      <c r="B5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C5">
-        <v>29</v>
-      </c>
-      <c r="D5">
-        <v>71</v>
-      </c>
-      <c r="E5" t="s">
-        <v>98</v>
-      </c>
-      <c r="F5" t="str">
-        <f t="shared" si="0"/>
-        <v>DJOKOVIC</v>
-      </c>
-      <c r="G5">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="K5" s="6">
-        <f>7/8</f>
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>99</v>
-      </c>
-      <c r="B6" t="s">
-        <v>118</v>
-      </c>
-      <c r="C6">
-        <v>77</v>
-      </c>
-      <c r="D6">
-        <v>23</v>
-      </c>
-      <c r="E6" t="s">
-        <v>101</v>
-      </c>
-      <c r="F6" t="str">
-        <f t="shared" si="0"/>
-        <v>FRITZ</v>
-      </c>
-      <c r="G6">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="K6" s="6">
-        <f>6/8</f>
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>133</v>
-      </c>
-      <c r="B7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C7">
-        <v>68</v>
-      </c>
-      <c r="D7">
-        <v>32</v>
-      </c>
-      <c r="E7" t="s">
-        <v>134</v>
-      </c>
-      <c r="F7" t="str">
-        <f t="shared" si="0"/>
-        <v>KHACHANOV</v>
-      </c>
-      <c r="G7">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="J7" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="K7" s="6">
-        <f>7/8</f>
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>148</v>
-      </c>
-      <c r="B8" t="s">
-        <v>165</v>
-      </c>
-      <c r="C8">
-        <v>41</v>
-      </c>
-      <c r="D8">
-        <v>59</v>
-      </c>
-      <c r="E8" t="s">
-        <v>167</v>
-      </c>
-      <c r="F8" t="str">
-        <f t="shared" si="0"/>
-        <v>NORRIE</v>
-      </c>
-      <c r="G8">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>171</v>
-      </c>
-      <c r="B9" t="s">
-        <v>192</v>
-      </c>
-      <c r="C9">
-        <v>25</v>
-      </c>
-      <c r="D9">
-        <v>75</v>
-      </c>
-      <c r="E9" t="s">
-        <v>193</v>
-      </c>
-      <c r="F9" t="str">
-        <f t="shared" si="0"/>
-        <v>ALCARAZ</v>
-      </c>
-      <c r="G9">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="G2:G9">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+  <conditionalFormatting sqref="J1:P1">
+    <cfRule type="cellIs" dxfId="10" priority="7" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="8" operator="equal">
       <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I17">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L17">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Perdem">
+      <formula>NOT(ISERROR(SEARCH("Perdem",L2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="Guanyem">
+      <formula>NOT(ISERROR(SEARCH("Guanyem",L2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Empat">
+      <formula>NOT(ISERROR(SEARCH("Empat",L2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4633,20 +11342,20 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B426FC20-F2D4-42EE-B26E-57F7A91BDF6D}">
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7B8FC45-B22C-4AD5-9F0B-B6BE598565A3}">
+  <dimension ref="A1:K9"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4669,18 +11378,18 @@
         <v>197</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C2">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="D2">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4694,122 +11403,218 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3">
         <v>63</v>
       </c>
-      <c r="B3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C3">
-        <v>28</v>
-      </c>
       <c r="D3">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
-        <v>98</v>
+        <v>29</v>
       </c>
       <c r="F3" t="str">
-        <f>LEFT(IF(C3&gt;D3, A3, B3), FIND(",", IF(C3&gt;D3, A3, B3)) - 1)</f>
-        <v>DJOKOVIC</v>
+        <f t="shared" ref="F3:F9" si="0">LEFT(IF(C3&gt;D3, A3, B3), FIND(",", IF(C3&gt;D3, A3, B3)) - 1)</f>
+        <v>SHELTON</v>
       </c>
       <c r="G3">
-        <f>IF(F3=E3, 1, 0)</f>
+        <f t="shared" ref="G3:G9" si="1">IF(F3=E3, 1, 0)</f>
         <v>1</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>199</v>
       </c>
       <c r="K3" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>133</v>
+        <v>55</v>
       </c>
       <c r="B4" t="s">
-        <v>99</v>
+        <v>63</v>
       </c>
       <c r="C4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D4">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="F4" t="str">
-        <f>LEFT(IF(C4&gt;D4, A4, B4), FIND(",", IF(C4&gt;D4, A4, B4)) - 1)</f>
-        <v>FRITZ</v>
+        <f t="shared" si="0"/>
+        <v>COBOLLI</v>
       </c>
       <c r="G4">
-        <f>IF(F4=E4, 1, 0)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="J4" s="5" t="s">
         <v>200</v>
       </c>
       <c r="K4" s="6">
-        <f>4/4</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+        <f>8/8</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>192</v>
+        <v>75</v>
       </c>
       <c r="B5" t="s">
-        <v>165</v>
+        <v>97</v>
       </c>
       <c r="C5">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="D5">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
-        <v>193</v>
+        <v>98</v>
       </c>
       <c r="F5" t="str">
-        <f>LEFT(IF(C5&gt;D5, A5, B5), FIND(",", IF(C5&gt;D5, A5, B5)) - 1)</f>
-        <v>ALCARAZ</v>
+        <f t="shared" si="0"/>
+        <v>DJOKOVIC</v>
       </c>
       <c r="G5">
-        <f>IF(F5=E5, 1, 0)</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>201</v>
       </c>
       <c r="K5" s="6">
-        <f>4/4</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+        <f>7/8</f>
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B6" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6">
+        <v>77</v>
+      </c>
+      <c r="D6">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F6" t="str">
+        <f t="shared" si="0"/>
+        <v>FRITZ</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
       <c r="J6" s="5" t="s">
         <v>206</v>
       </c>
       <c r="K6" s="6">
-        <f>4/4</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+        <f>6/8</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C7">
+        <v>68</v>
+      </c>
+      <c r="D7">
+        <v>32</v>
+      </c>
+      <c r="E7" t="s">
+        <v>134</v>
+      </c>
+      <c r="F7" t="str">
+        <f t="shared" si="0"/>
+        <v>KHACHANOV</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
       <c r="J7" s="5" t="s">
         <v>208</v>
       </c>
       <c r="K7" s="6">
-        <f>4/4</f>
+        <f>7/8</f>
+        <v>0.875</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>148</v>
+      </c>
+      <c r="B8" t="s">
+        <v>165</v>
+      </c>
+      <c r="C8">
+        <v>41</v>
+      </c>
+      <c r="D8">
+        <v>59</v>
+      </c>
+      <c r="E8" t="s">
+        <v>167</v>
+      </c>
+      <c r="F8" t="str">
+        <f t="shared" si="0"/>
+        <v>NORRIE</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>171</v>
+      </c>
+      <c r="B9" t="s">
+        <v>192</v>
+      </c>
+      <c r="C9">
+        <v>25</v>
+      </c>
+      <c r="D9">
+        <v>75</v>
+      </c>
+      <c r="E9" t="s">
+        <v>193</v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" si="0"/>
+        <v>ALCARAZ</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:G5">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+  <conditionalFormatting sqref="G2:G9">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4818,20 +11623,20 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F3217C8-0180-4F68-B33D-869F44F7E5B7}">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B426FC20-F2D4-42EE-B26E-57F7A91BDF6D}">
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4854,18 +11659,18 @@
         <v>197</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>97</v>
-      </c>
       <c r="C2">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="D2">
-        <v>42</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4879,25 +11684,25 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>192</v>
+        <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C3">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="D3">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
-        <v>193</v>
+        <v>98</v>
       </c>
       <c r="F3" t="str">
         <f>LEFT(IF(C3&gt;D3, A3, B3), FIND(",", IF(C3&gt;D3, A3, B3)) - 1)</f>
-        <v>ALCARAZ</v>
+        <v>DJOKOVIC</v>
       </c>
       <c r="G3">
         <f>IF(F3=E3, 1, 0)</f>
@@ -4907,39 +11712,94 @@
         <v>199</v>
       </c>
       <c r="K3" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4">
+        <v>34</v>
+      </c>
+      <c r="D4">
+        <v>66</v>
+      </c>
+      <c r="E4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F4" t="str">
+        <f>LEFT(IF(C4&gt;D4, A4, B4), FIND(",", IF(C4&gt;D4, A4, B4)) - 1)</f>
+        <v>FRITZ</v>
+      </c>
+      <c r="G4">
+        <f>IF(F4=E4, 1, 0)</f>
+        <v>1</v>
+      </c>
       <c r="J4" s="5" t="s">
         <v>200</v>
       </c>
       <c r="K4" s="6">
-        <f>2/2</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+        <f>4/4</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C5">
+        <v>87</v>
+      </c>
+      <c r="D5">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>193</v>
+      </c>
+      <c r="F5" t="str">
+        <f>LEFT(IF(C5&gt;D5, A5, B5), FIND(",", IF(C5&gt;D5, A5, B5)) - 1)</f>
+        <v>ALCARAZ</v>
+      </c>
+      <c r="G5">
+        <f>IF(F5=E5, 1, 0)</f>
+        <v>1</v>
+      </c>
       <c r="J5" s="5" t="s">
         <v>201</v>
       </c>
       <c r="K5" s="6">
-        <f>2/2</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+        <f>4/4</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="J6" s="5" t="s">
         <v>206</v>
       </c>
       <c r="K6" s="6">
-        <f>2/2</f>
+        <f>4/4</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J7" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="K7" s="6">
+        <f>4/4</f>
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:G3">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+  <conditionalFormatting sqref="G2:G5">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4948,20 +11808,20 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{290BA5AE-209F-4B33-912E-0B335547B6EF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F3217C8-0180-4F68-B33D-869F44F7E5B7}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4984,18 +11844,18 @@
         <v>197</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>192</v>
+        <v>97</v>
       </c>
       <c r="C2">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D2">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5009,44 +11869,67 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>192</v>
+      </c>
+      <c r="B3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3">
+        <v>60</v>
+      </c>
+      <c r="D3">
+        <v>40</v>
+      </c>
+      <c r="E3" t="s">
+        <v>193</v>
+      </c>
+      <c r="F3" t="str">
+        <f>LEFT(IF(C3&gt;D3, A3, B3), FIND(",", IF(C3&gt;D3, A3, B3)) - 1)</f>
+        <v>ALCARAZ</v>
+      </c>
+      <c r="G3">
+        <f>IF(F3=E3, 1, 0)</f>
+        <v>1</v>
+      </c>
       <c r="J3" s="3" t="s">
         <v>199</v>
       </c>
       <c r="K3" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="J4" s="5" t="s">
         <v>200</v>
       </c>
       <c r="K4" s="6">
-        <f>1/1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+        <f>2/2</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="J5" s="5" t="s">
         <v>201</v>
       </c>
       <c r="K5" s="6">
-        <f>0/1</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+        <f>2/2</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="J6" s="5" t="s">
         <v>206</v>
       </c>
       <c r="K6" s="6">
-        <f>0/1</f>
-        <v>0</v>
+        <f>2/2</f>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="G2:G3">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5055,22 +11938,129 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{290BA5AE-209F-4B33-912E-0B335547B6EF}">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2">
+        <v>53</v>
+      </c>
+      <c r="D2">
+        <v>47</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="str">
+        <f>LEFT(IF(C2&gt;D2, A2, B2), FIND(",", IF(C2&gt;D2, A2, B2)) - 1)</f>
+        <v>SINNER</v>
+      </c>
+      <c r="G2">
+        <f>IF(F2=E2, 1, 0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J3" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="K3" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J4" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="K4" s="6">
+        <f>1/1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J5" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="K5" s="6">
+        <f>0/1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="J6" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="K6" s="6">
+        <f>0/1</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="G2">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03439C7F-BE26-46C4-AF78-BFBDE843F874}">
   <dimension ref="B1:J11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="8" max="8" width="7.83203125" customWidth="1"/>
-    <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.81640625" customWidth="1"/>
+    <col min="9" max="9" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B1" s="7"/>
     </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B2" s="7"/>
     </row>
-    <row r="8" spans="2:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="H8" s="8"/>
       <c r="I8" s="14" t="s">
         <v>204</v>
@@ -5079,7 +12069,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="9" spans="2:10" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:10" ht="15" thickTop="1" x14ac:dyDescent="0.35">
       <c r="H9" s="13" t="s">
         <v>202</v>
       </c>
@@ -5091,7 +12081,7 @@
         <v>0.6692913385826772</v>
       </c>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="H10" s="13" t="s">
         <v>203</v>
       </c>
@@ -5103,7 +12093,7 @@
         <v>0.88976377952755903</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="H11" s="13" t="s">
         <v>207</v>
       </c>

--- a/ResultatWimbeldon.xlsx
+++ b/ResultatWimbeldon.xlsx
@@ -8,30 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ikerr\Code\TFG\Program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EACAAD8-24BF-443E-AB6F-088A7576F703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0FF5199-3656-4F0A-AA04-74E5F4133A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25420" windowHeight="16300" activeTab="3" xr2:uid="{0ED45994-5EFE-4A4E-8BA9-C3AA32741888}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25420" windowHeight="16300" firstSheet="1" activeTab="8" xr2:uid="{0ED45994-5EFE-4A4E-8BA9-C3AA32741888}"/>
   </bookViews>
   <sheets>
     <sheet name="Ronda 1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet6" sheetId="14" r:id="rId2"/>
-    <sheet name="Ronda 2" sheetId="2" r:id="rId3"/>
-    <sheet name="Ronda 3" sheetId="3" r:id="rId4"/>
-    <sheet name="Ronda 4" sheetId="4" r:id="rId5"/>
-    <sheet name="Quarts" sheetId="5" r:id="rId6"/>
-    <sheet name="Semi" sheetId="6" r:id="rId7"/>
-    <sheet name="Final" sheetId="7" r:id="rId8"/>
-    <sheet name="Resultats" sheetId="8" r:id="rId9"/>
+    <sheet name="Ronda 2" sheetId="2" r:id="rId2"/>
+    <sheet name="Ronda 3" sheetId="3" r:id="rId3"/>
+    <sheet name="Ronda 4" sheetId="4" r:id="rId4"/>
+    <sheet name="Quarts" sheetId="5" r:id="rId5"/>
+    <sheet name="Semi" sheetId="6" r:id="rId6"/>
+    <sheet name="Final" sheetId="7" r:id="rId7"/>
+    <sheet name="Resultats" sheetId="8" r:id="rId8"/>
+    <sheet name="Grafics" sheetId="17" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ronda 1'!$A$1:$G$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Ronda 2'!$A$1:$G$33</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Ronda 3'!$A$1:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Ronda 2'!$A$1:$G$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Ronda 3'!$A$1:$G$17</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <pivotCaches>
-    <pivotCache cacheId="87" r:id="rId10"/>
-  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -52,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="261">
   <si>
     <t>Jugador 1</t>
   </si>
@@ -759,18 +756,6 @@
     <t>Qui prediu millor</t>
   </si>
   <si>
-    <t>Count of Guanyador de les prediccions</t>
-  </si>
-  <si>
-    <t>Empat</t>
-  </si>
-  <si>
-    <t>Guanyem</t>
-  </si>
-  <si>
-    <t>Perdem</t>
-  </si>
-  <si>
     <t>Probabilitat A Model Propi</t>
   </si>
   <si>
@@ -793,13 +778,67 @@
   </si>
   <si>
     <t>THOMSON</t>
+  </si>
+  <si>
+    <t>Ronda</t>
+  </si>
+  <si>
+    <t>Ronda 1</t>
+  </si>
+  <si>
+    <t>Ronda 2</t>
+  </si>
+  <si>
+    <t>Ronda 3</t>
+  </si>
+  <si>
+    <t>Ronda 4</t>
+  </si>
+  <si>
+    <t>Quarts de Final</t>
+  </si>
+  <si>
+    <t>Final</t>
+  </si>
+  <si>
+    <t>Encerts IBM</t>
+  </si>
+  <si>
+    <t>Encerts Model Propi</t>
+  </si>
+  <si>
+    <t>Semi Final</t>
+  </si>
+  <si>
+    <t>Accuracy IBM</t>
+  </si>
+  <si>
+    <t>Accuracy Model Propi</t>
+  </si>
+  <si>
+    <t>Brier Score Model Propi</t>
+  </si>
+  <si>
+    <t>Prob IBM Guanyador</t>
+  </si>
+  <si>
+    <t>(p - o)^2</t>
+  </si>
+  <si>
+    <t>Brier Score IBM</t>
+  </si>
+  <si>
+    <t>Brier Score IBM:</t>
+  </si>
+  <si>
+    <t>Brier Score Iker:</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -821,6 +860,19 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1000,14 +1052,56 @@
     <xf numFmtId="10" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="29">
+  <dxfs count="71">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -1055,7 +1149,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF92D050"/>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1067,9 +1168,125 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1095,9 +1312,174 @@
       </fill>
     </dxf>
     <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1490,10 +1872,6 @@
       <c:style val="2"/>
     </mc:Fallback>
   </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[ResultatWimbeldon.xlsx]Sheet6!PivotTable48</c:name>
-    <c:fmtId val="0"/>
-  </c:pivotSource>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1516,7 +1894,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Count of Guanyador de les prediccions</a:t>
+              <a:t>Accuracy per rondes</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1551,64 +1929,6 @@
       </c:txPr>
     </c:title>
     <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
       <c:barChart>
@@ -1620,11 +1940,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet6!$B$3</c:f>
+              <c:f>Grafics!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Total</c:v>
+                  <c:v>Encerts IBM</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1641,42 +1961,155 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet6!$A$4:$A$6</c:f>
+              <c:f>Grafics!$A$2:$A$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>Empat</c:v>
+                  <c:v>Ronda 1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Guanyem</c:v>
+                  <c:v>Ronda 2</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>Perdem</c:v>
+                  <c:v>Ronda 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Ronda 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Quarts de Final</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Semi Final</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Final</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet6!$B$4:$B$6</c:f>
+              <c:f>Grafics!$B$2:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>27</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3</c:v>
+                  <c:v>22</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-79AD-4526-905E-86909A91E942}"/>
+              <c16:uniqueId val="{00000000-24A6-477B-BFA7-E4863E9B20BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Grafics!$C$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Encerts Model Propi</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Grafics!$A$2:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Ronda 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Ronda 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Ronda 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Ronda 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Quarts de Final</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Semi Final</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Final</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Grafics!$C$2:$C$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-24A6-477B-BFA7-E4863E9B20BE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1690,11 +2123,217 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="693352096"/>
-        <c:axId val="693361216"/>
+        <c:axId val="693378016"/>
+        <c:axId val="693379456"/>
       </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Grafics!$D$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Accuracy IBM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Grafics!$A$2:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Ronda 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Ronda 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Ronda 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Ronda 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Quarts de Final</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Semi Final</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Final</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Grafics!$D$2:$D$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0.578125</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.6875</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.6875</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-24A6-477B-BFA7-E4863E9B20BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Grafics!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Accuracy Model Propi</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Grafics!$A$2:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Ronda 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Ronda 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Ronda 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Ronda 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Quarts de Final</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Semi Final</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Final</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Grafics!$E$2:$E$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.00%</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0.65625</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.71875</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-24A6-477B-BFA7-E4863E9B20BE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="693383776"/>
+        <c:axId val="693383296"/>
+      </c:lineChart>
       <c:catAx>
-        <c:axId val="693352096"/>
+        <c:axId val="693378016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1737,7 +2376,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="693361216"/>
+        <c:crossAx val="693379456"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1745,7 +2384,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="693361216"/>
+        <c:axId val="693379456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1796,10 +2435,70 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="693352096"/>
+        <c:crossAx val="693378016"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:valAx>
+        <c:axId val="693383296"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="0.00%" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="693383776"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="693383776"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="693383296"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -1808,9 +2507,47 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1842,21 +2579,497 @@
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Brier</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Score per rondes</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Grafics!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Brier Score IBM</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Grafics!$A$2:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Ronda 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Ronda 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Ronda 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Ronda 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Quarts de Final</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Semi Final</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Final</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Grafics!$F$2:$F$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0.2387</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.22245312499999995</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.18175624999999995</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.1112499999999999E-2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6.3750000000000001E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.16820000000000002</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.22089999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1139-4F60-8FA5-21AEF496C141}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Grafics!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Brier Score Model Propi</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Grafics!$A$2:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>Ronda 1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Ronda 2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Ronda 3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Ronda 4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Quarts de Final</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Semi Final</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Final</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Grafics!$G$2:$G$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0.2387</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.2185</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.1578</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.13400000000000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3.8399999999999997E-2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.1293</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.32269999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1139-4F60-8FA5-21AEF496C141}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="693332896"/>
+        <c:axId val="693329056"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="693332896"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="693329056"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="693329056"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="693332896"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
@@ -1901,6 +3114,46 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -2946,6 +4199,509 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -2991,23 +4747,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1978025</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>146050</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>790575</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>127000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>555625</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1133475</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>107950</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1">
+        <xdr:cNvPr id="6" name="Chart 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AED3CA1E-E103-9FDE-21CE-3957D8440473}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CB005372-7906-526C-5A49-0C49976FDC61}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3025,820 +4781,43 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>70347</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>172322</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>184896</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>114051</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Chart 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FFF7CC93-BE9A-F2EE-20BC-1381315DC9A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Iker Ruiz" refreshedDate="46026.953020949077" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="32" xr:uid="{71E54D72-922A-494A-9371-400A1EE1345E}">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A1:P33" sheet="Ronda 2"/>
-  </cacheSource>
-  <cacheFields count="16">
-    <cacheField name="Jugador 1" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Jugador 2" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Probabilitat 1" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="6" maxValue="90"/>
-    </cacheField>
-    <cacheField name="Probabilitat 2" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="10" maxValue="94"/>
-    </cacheField>
-    <cacheField name="Ganador" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="IBM Winner" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Acert IBM" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
-    </cacheField>
-    <cacheField name="Iker Winner" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-    <cacheField name="Acert Iker" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
-    </cacheField>
-    <cacheField name="Probabilitat A Model Propi" numFmtId="10">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="6.9466999999999945E-2" maxValue="0.96246200000000004"/>
-    </cacheField>
-    <cacheField name="Probabilitat B Model Propi" numFmtId="10">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="3.753799999999996E-2" maxValue="0.93053300000000005"/>
-    </cacheField>
-    <cacheField name="Guanyador de les prediccions" numFmtId="0">
-      <sharedItems count="3">
-        <s v="Empat"/>
-        <s v="Guanyem"/>
-        <s v="Perdem"/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Qui prediu millor" numFmtId="10">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="-0.35645500000000002" maxValue="0.28518999999999994"/>
-    </cacheField>
-    <cacheField name="Probabilitat A IBM" numFmtId="10">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.06" maxValue="0.9"/>
-    </cacheField>
-    <cacheField name="Probabilitat B IBM" numFmtId="10">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.1" maxValue="0.94"/>
-    </cacheField>
-    <cacheField name="Partit" numFmtId="0">
-      <sharedItems/>
-    </cacheField>
-  </cacheFields>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="32">
-  <r>
-    <s v="AUGER-ALIASSIME, Felix"/>
-    <s v="STRUFF, Jan-Lennard"/>
-    <n v="72"/>
-    <n v="28"/>
-    <s v="STRUFF"/>
-    <s v="AUGER-ALIASSIME"/>
-    <n v="0"/>
-    <s v="AUGER-ALIASSIME"/>
-    <n v="0"/>
-    <n v="0.69422300000000003"/>
-    <n v="0.30577699999999997"/>
-    <x v="0"/>
-    <n v="2.5776999999999939E-2"/>
-    <n v="0.72"/>
-    <n v="0.28000000000000003"/>
-    <s v="AUGER-ALIASSIME vs. STRUFF"/>
-  </r>
-  <r>
-    <s v="BORGES, Nuno"/>
-    <s v="HARRIS, Billy"/>
-    <n v="66"/>
-    <n v="34"/>
-    <s v="BORGES"/>
-    <s v="BORGES"/>
-    <n v="1"/>
-    <s v="BORGES"/>
-    <n v="1"/>
-    <n v="0.65856000000000003"/>
-    <n v="0.34143999999999997"/>
-    <x v="0"/>
-    <n v="-1.4399999999999968E-3"/>
-    <n v="0.66"/>
-    <n v="0.34"/>
-    <s v="BORGES vs. HARRIS"/>
-  </r>
-  <r>
-    <s v="COBOLLI, Flavio"/>
-    <s v="PINNINGTON JONES, Jack"/>
-    <n v="75"/>
-    <n v="25"/>
-    <s v="COBOLLI"/>
-    <s v="COBOLLI"/>
-    <n v="1"/>
-    <s v="COBOLLI"/>
-    <n v="1"/>
-    <n v="0.74198200000000003"/>
-    <n v="0.25801799999999997"/>
-    <x v="0"/>
-    <n v="-8.0179999999999696E-3"/>
-    <n v="0.75"/>
-    <n v="0.25"/>
-    <s v="COBOLLI vs. PINNINGTON JONES"/>
-  </r>
-  <r>
-    <s v="DE MINAUR, Alex"/>
-    <s v="CAZAUX, Arthur"/>
-    <n v="68"/>
-    <n v="32"/>
-    <s v="DE MINAUR"/>
-    <s v="DE MINAUR"/>
-    <n v="1"/>
-    <s v="DE MINAUR"/>
-    <n v="1"/>
-    <n v="0.96246200000000004"/>
-    <n v="3.753799999999996E-2"/>
-    <x v="0"/>
-    <n v="0.28246199999999999"/>
-    <n v="0.68"/>
-    <n v="0.32"/>
-    <s v="DE MINAUR vs. CAZAUX"/>
-  </r>
-  <r>
-    <s v="DIMITROV, Grigor"/>
-    <s v="MOUTET, Corentin"/>
-    <n v="53"/>
-    <n v="47"/>
-    <s v="DIMITROV"/>
-    <s v="DIMITROV"/>
-    <n v="1"/>
-    <s v="DIMITROV"/>
-    <n v="1"/>
-    <n v="0.63892800000000005"/>
-    <n v="0.36107199999999995"/>
-    <x v="0"/>
-    <n v="0.10892800000000002"/>
-    <n v="0.53"/>
-    <n v="0.47"/>
-    <s v="DIMITROV vs. MOUTET"/>
-  </r>
-  <r>
-    <s v="DRAPER, Jack"/>
-    <s v="CILIC, Marin"/>
-    <n v="85"/>
-    <n v="15"/>
-    <s v="CILIC"/>
-    <s v="DRAPER"/>
-    <n v="0"/>
-    <s v="DRAPER"/>
-    <n v="0"/>
-    <n v="0.82929399999999998"/>
-    <n v="0.17070600000000002"/>
-    <x v="0"/>
-    <n v="2.070600000000003E-2"/>
-    <n v="0.85"/>
-    <n v="0.15"/>
-    <s v="DRAPER vs. CILIC"/>
-  </r>
-  <r>
-    <s v="EVANS, Daniel"/>
-    <s v="DJOKOVIC, Novak"/>
-    <n v="13"/>
-    <n v="87"/>
-    <s v="DJOKOVIC"/>
-    <s v="DJOKOVIC"/>
-    <n v="1"/>
-    <s v="DJOKOVIC"/>
-    <n v="1"/>
-    <n v="6.9466999999999945E-2"/>
-    <n v="0.93053300000000005"/>
-    <x v="0"/>
-    <n v="6.0533000000000059E-2"/>
-    <n v="0.13"/>
-    <n v="0.87"/>
-    <s v="EVANS vs. DJOKOVIC"/>
-  </r>
-  <r>
-    <s v="FERY, Arthur"/>
-    <s v="DARDERI, Luciano"/>
-    <n v="24"/>
-    <n v="76"/>
-    <s v="DARDERI"/>
-    <s v="DARDERI"/>
-    <n v="1"/>
-    <s v="DARDERI"/>
-    <n v="1"/>
-    <n v="0.46909000000000001"/>
-    <n v="0.53090999999999999"/>
-    <x v="0"/>
-    <n v="-0.22909000000000002"/>
-    <n v="0.24"/>
-    <n v="0.76"/>
-    <s v="FERY vs. DARDERI"/>
-  </r>
-  <r>
-    <s v="FONSECA, Joao"/>
-    <s v="BROOKSBY, Jenson"/>
-    <n v="63"/>
-    <n v="37"/>
-    <s v="FONSECA"/>
-    <s v="FONSECA"/>
-    <n v="1"/>
-    <s v="FONSECA"/>
-    <n v="1"/>
-    <n v="0.686145"/>
-    <n v="0.313855"/>
-    <x v="0"/>
-    <n v="5.6145E-2"/>
-    <n v="0.63"/>
-    <n v="0.37"/>
-    <s v="FONSECA vs. BROOKSBY"/>
-  </r>
-  <r>
-    <s v="FRITZ, Taylor"/>
-    <s v="DIALLO, Gabriel"/>
-    <n v="72"/>
-    <n v="28"/>
-    <s v="FRITZ"/>
-    <s v="FRITZ"/>
-    <n v="1"/>
-    <s v="FRITZ"/>
-    <n v="1"/>
-    <n v="0.78715099999999993"/>
-    <n v="0.21284900000000007"/>
-    <x v="0"/>
-    <n v="6.7150999999999961E-2"/>
-    <n v="0.72"/>
-    <n v="0.28000000000000003"/>
-    <s v="FRITZ vs. DIALLO"/>
-  </r>
-  <r>
-    <s v="FUCSOVICS, Marton"/>
-    <s v="MONFILS, Gael"/>
-    <n v="37"/>
-    <n v="63"/>
-    <s v="FUCSOVICS"/>
-    <s v="MONFILS"/>
-    <n v="0"/>
-    <s v="FUCSOVICS"/>
-    <n v="1"/>
-    <n v="0.53553099999999998"/>
-    <n v="0.46446900000000002"/>
-    <x v="1"/>
-    <n v="0.16553099999999998"/>
-    <n v="0.37"/>
-    <n v="0.63"/>
-    <s v="FUCSOVICS vs. MONFILS"/>
-  </r>
-  <r>
-    <s v="GARIN, Cristian"/>
-    <s v="RINDERKNECH, Arthur"/>
-    <n v="47"/>
-    <n v="53"/>
-    <s v="RINDERKNECH"/>
-    <s v="RINDERKNECH"/>
-    <n v="1"/>
-    <s v="RINDERKNECH"/>
-    <n v="1"/>
-    <n v="0.412935"/>
-    <n v="0.58706499999999995"/>
-    <x v="0"/>
-    <n v="5.7064999999999921E-2"/>
-    <n v="0.47"/>
-    <n v="0.53"/>
-    <s v="GARIN vs. RINDERKNECH"/>
-  </r>
-  <r>
-    <s v="GIRON, Marcos"/>
-    <s v="MENSIK, Jakub"/>
-    <n v="39"/>
-    <n v="61"/>
-    <s v="MENSIK"/>
-    <s v="MENSIK"/>
-    <n v="1"/>
-    <s v="MENSIK"/>
-    <n v="1"/>
-    <n v="0.41428300000000001"/>
-    <n v="0.58571700000000004"/>
-    <x v="0"/>
-    <n v="-2.4282999999999944E-2"/>
-    <n v="0.39"/>
-    <n v="0.61"/>
-    <s v="GIRON vs. MENSIK"/>
-  </r>
-  <r>
-    <s v="HOLMGREN, August"/>
-    <s v="MACHAC, Tomas"/>
-    <n v="28"/>
-    <n v="72"/>
-    <s v="HOLMGREN"/>
-    <s v="MACHAC"/>
-    <n v="0"/>
-    <s v="MACHAC"/>
-    <n v="0"/>
-    <n v="0.301927"/>
-    <n v="0.69807299999999994"/>
-    <x v="0"/>
-    <n v="2.1926999999999974E-2"/>
-    <n v="0.28000000000000003"/>
-    <n v="0.72"/>
-    <s v="HOLMGREN vs. MACHAC"/>
-  </r>
-  <r>
-    <s v="JARRY, Nicolas"/>
-    <s v="TIEN, Learner"/>
-    <n v="38"/>
-    <n v="62"/>
-    <s v="JARRY"/>
-    <s v="TIEN"/>
-    <n v="0"/>
-    <s v="JARRY"/>
-    <n v="1"/>
-    <n v="0.59473699999999996"/>
-    <n v="0.40526300000000004"/>
-    <x v="1"/>
-    <n v="0.21473699999999996"/>
-    <n v="0.38"/>
-    <n v="0.62"/>
-    <s v="JARRY vs. TIEN"/>
-  </r>
-  <r>
-    <s v="KECMANOVIC, Miomir"/>
-    <s v="DE JONG, Jesper"/>
-    <n v="62"/>
-    <n v="38"/>
-    <s v="KECMANOVIC"/>
-    <s v="KECMANOVIC"/>
-    <n v="1"/>
-    <s v="KECMANOVIC"/>
-    <n v="1"/>
-    <n v="0.72543899999999994"/>
-    <n v="0.27456100000000006"/>
-    <x v="0"/>
-    <n v="0.10543899999999995"/>
-    <n v="0.62"/>
-    <n v="0.38"/>
-    <s v="KECMANOVIC vs. DE JONG"/>
-  </r>
-  <r>
-    <s v="LEHECKA, Jiri"/>
-    <s v="BELLUCCI, Mattia"/>
-    <n v="56"/>
-    <n v="44"/>
-    <s v="BELLUCCI"/>
-    <s v="LEHECKA"/>
-    <n v="0"/>
-    <s v="LEHECKA"/>
-    <n v="0"/>
-    <n v="0.91645500000000002"/>
-    <n v="8.354499999999998E-2"/>
-    <x v="0"/>
-    <n v="-0.35645500000000002"/>
-    <n v="0.56000000000000005"/>
-    <n v="0.44"/>
-    <s v="LEHECKA vs. BELLUCCI"/>
-  </r>
-  <r>
-    <s v="MAJCHRZAK, Kamil"/>
-    <s v="QUINN, Ethan"/>
-    <n v="42"/>
-    <n v="58"/>
-    <s v="MAJCHRZAK"/>
-    <s v="QUINN"/>
-    <n v="0"/>
-    <s v="QUINN"/>
-    <n v="0"/>
-    <n v="0.48952899999999999"/>
-    <n v="0.51047100000000001"/>
-    <x v="0"/>
-    <n v="6.9529000000000007E-2"/>
-    <n v="0.42"/>
-    <n v="0.57999999999999996"/>
-    <s v="MAJCHRZAK vs. QUINN"/>
-  </r>
-  <r>
-    <s v="MANNARINO, Adrian"/>
-    <s v="ROYER, Valentin"/>
-    <n v="42"/>
-    <n v="58"/>
-    <s v="MANNARINO"/>
-    <s v="ROYER"/>
-    <n v="0"/>
-    <s v="MANNARINO"/>
-    <n v="1"/>
-    <n v="0.69118900000000005"/>
-    <n v="0.30881099999999995"/>
-    <x v="1"/>
-    <n v="0.27118900000000007"/>
-    <n v="0.42"/>
-    <n v="0.57999999999999996"/>
-    <s v="MANNARINO vs. ROYER"/>
-  </r>
-  <r>
-    <s v="MAROZSAN, Fabian"/>
-    <s v="MUNAR, Jaume"/>
-    <n v="42"/>
-    <n v="58"/>
-    <s v="MUNAR"/>
-    <s v="MUNAR"/>
-    <n v="1"/>
-    <s v="MUNAR"/>
-    <n v="1"/>
-    <n v="0.49672500000000003"/>
-    <n v="0.50327499999999992"/>
-    <x v="0"/>
-    <n v="-7.6725000000000043E-2"/>
-    <n v="0.42"/>
-    <n v="0.57999999999999996"/>
-    <s v="MAROZSAN vs. MUNAR"/>
-  </r>
-  <r>
-    <s v="MARTÍNEZ, Pedro"/>
-    <s v="NAVONE, Mariano"/>
-    <n v="55"/>
-    <n v="45"/>
-    <s v="MARTÍNEZ"/>
-    <s v="MARTÍNEZ"/>
-    <n v="1"/>
-    <s v="NAVONE"/>
-    <n v="0"/>
-    <n v="0.41036899999999998"/>
-    <n v="0.58963100000000002"/>
-    <x v="2"/>
-    <n v="-0.13963100000000006"/>
-    <n v="0.55000000000000004"/>
-    <n v="0.45"/>
-    <s v="MARTÍNEZ vs. NAVONE"/>
-  </r>
-  <r>
-    <s v="MOCHIZUKI, Shintaro"/>
-    <s v="KHACHANOV, Karen"/>
-    <n v="37"/>
-    <n v="63"/>
-    <s v="KHACHANOV"/>
-    <s v="KHACHANOV"/>
-    <n v="1"/>
-    <s v="KHACHANOV"/>
-    <n v="1"/>
-    <n v="8.4810000000000052E-2"/>
-    <n v="0.91518999999999995"/>
-    <x v="0"/>
-    <n v="0.28518999999999994"/>
-    <n v="0.37"/>
-    <n v="0.63"/>
-    <s v="MOCHIZUKI vs. KHACHANOV"/>
-  </r>
-  <r>
-    <s v="NAKASHIMA, Brandon"/>
-    <s v="OPELKA, Reilly"/>
-    <n v="55"/>
-    <n v="45"/>
-    <s v="NAKASHIMA"/>
-    <s v="NAKASHIMA"/>
-    <n v="1"/>
-    <s v="NAKASHIMA"/>
-    <n v="1"/>
-    <n v="0.63892800000000005"/>
-    <n v="0.36107199999999995"/>
-    <x v="0"/>
-    <n v="8.8928000000000007E-2"/>
-    <n v="0.55000000000000004"/>
-    <n v="0.45"/>
-    <s v="NAKASHIMA vs. OPELKA"/>
-  </r>
-  <r>
-    <s v="NORRIE, Cameron"/>
-    <s v="TIAFOE, Frances"/>
-    <n v="38"/>
-    <n v="63"/>
-    <s v="NORRIE"/>
-    <s v="TIAFOE"/>
-    <n v="0"/>
-    <s v="TIAFOE"/>
-    <n v="0"/>
-    <n v="0.44528000000000001"/>
-    <n v="0.55471999999999999"/>
-    <x v="0"/>
-    <n v="6.5280000000000005E-2"/>
-    <n v="0.38"/>
-    <n v="0.63"/>
-    <s v="NORRIE vs. TIAFOE"/>
-  </r>
-  <r>
-    <s v="OFNER, Sebastian"/>
-    <s v="PAUL, Tommy"/>
-    <n v="27"/>
-    <n v="73"/>
-    <s v="OFNER"/>
-    <s v="PAUL"/>
-    <n v="0"/>
-    <s v="PAUL"/>
-    <n v="0"/>
-    <n v="0.160053"/>
-    <n v="0.839947"/>
-    <x v="0"/>
-    <n v="-0.10994700000000002"/>
-    <n v="0.27"/>
-    <n v="0.73"/>
-    <s v="OFNER vs. PAUL"/>
-  </r>
-  <r>
-    <s v="RUBLEV, Andrey"/>
-    <s v="HARRIS, Lloyd"/>
-    <n v="77"/>
-    <n v="23"/>
-    <s v="RUBLEV"/>
-    <s v="RUBLEV"/>
-    <n v="1"/>
-    <s v="RUBLEV"/>
-    <n v="1"/>
-    <n v="0.70881400000000006"/>
-    <n v="0.29118599999999994"/>
-    <x v="0"/>
-    <n v="-6.1185999999999963E-2"/>
-    <n v="0.77"/>
-    <n v="0.23"/>
-    <s v="RUBLEV vs. HARRIS"/>
-  </r>
-  <r>
-    <s v="SHELTON, Ben"/>
-    <s v="HIJIKATA, Rinky"/>
-    <n v="68"/>
-    <n v="32"/>
-    <s v="SHELTON"/>
-    <s v="SHELTON"/>
-    <n v="1"/>
-    <s v="SHELTON"/>
-    <n v="1"/>
-    <n v="0.57423400000000002"/>
-    <n v="0.42576599999999998"/>
-    <x v="0"/>
-    <n v="-0.10576600000000003"/>
-    <n v="0.68"/>
-    <n v="0.32"/>
-    <s v="SHELTON vs. HIJIKATA"/>
-  </r>
-  <r>
-    <s v="SINNER, Jannik"/>
-    <s v="VUKIC, Aleksandar"/>
-    <n v="90"/>
-    <n v="10"/>
-    <s v="SINNER"/>
-    <s v="SINNER"/>
-    <n v="1"/>
-    <s v="SINNER"/>
-    <n v="1"/>
-    <n v="0.96193600000000001"/>
-    <n v="3.8063999999999987E-2"/>
-    <x v="0"/>
-    <n v="6.1935999999999991E-2"/>
-    <n v="0.9"/>
-    <n v="0.1"/>
-    <s v="SINNER vs. VUKIC"/>
-  </r>
-  <r>
-    <s v="SONEGO, Lorenzo"/>
-    <s v="MUSETTI, Lorenzo"/>
-    <n v="65"/>
-    <n v="35"/>
-    <s v="SONEGO"/>
-    <s v="SONEGO"/>
-    <n v="1"/>
-    <s v="SONEGO"/>
-    <n v="1"/>
-    <n v="0.61302900000000005"/>
-    <n v="0.38697099999999995"/>
-    <x v="0"/>
-    <n v="-3.6970999999999976E-2"/>
-    <n v="0.65"/>
-    <n v="0.35"/>
-    <s v="SONEGO vs. MUSETTI"/>
-  </r>
-  <r>
-    <s v="TARVET, Oliver"/>
-    <s v="ALCARAZ, Carlos"/>
-    <n v="6"/>
-    <n v="94"/>
-    <s v="ALCARAZ"/>
-    <s v="ALCARAZ"/>
-    <n v="1"/>
-    <s v="ALCARAZ"/>
-    <n v="1"/>
-    <n v="0.25403699999999996"/>
-    <n v="0.74596300000000004"/>
-    <x v="0"/>
-    <n v="-0.1940369999999999"/>
-    <n v="0.06"/>
-    <n v="0.94"/>
-    <s v="TARVET vs. ALCARAZ"/>
-  </r>
-  <r>
-    <s v="THOMPSON, Jordan"/>
-    <s v="BONZI, Benjamin"/>
-    <n v="53"/>
-    <n v="47"/>
-    <s v="THOMPSON"/>
-    <s v="THOMPSON"/>
-    <n v="1"/>
-    <s v="BONZI"/>
-    <n v="0"/>
-    <n v="0.38696600000000003"/>
-    <n v="0.61303399999999997"/>
-    <x v="2"/>
-    <n v="-0.14303399999999999"/>
-    <n v="0.53"/>
-    <n v="0.47"/>
-    <s v="THOMPSON vs. BONZI"/>
-  </r>
-  <r>
-    <s v="VAN DE ZANDSCHULP, Botic"/>
-    <s v="DAVIDOVICH FOKINA, Alejandro"/>
-    <n v="35"/>
-    <n v="65"/>
-    <s v="DAVIDOVICH FOKINA"/>
-    <s v="DAVIDOVICH FOKINA"/>
-    <n v="1"/>
-    <s v="DAVIDOVICH FOKINA"/>
-    <n v="1"/>
-    <n v="0.23676200000000003"/>
-    <n v="0.76323799999999997"/>
-    <x v="0"/>
-    <n v="0.11323799999999995"/>
-    <n v="0.35"/>
-    <n v="0.65"/>
-    <s v="VAN DE ZANDSCHULP vs. DAVIDOVICH FOKINA"/>
-  </r>
-</pivotCacheRecords>
-</file>
-
-<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4E558E51-84D4-45E2-ABAD-64FB8739C946}" name="PivotTable48" cacheId="87" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="1">
-  <location ref="A3:B6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="16">
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-    <pivotField compact="0" numFmtId="10" outline="0" showAll="0" defaultSubtotal="0">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-    <pivotField compact="0" numFmtId="10" outline="0" showAll="0" defaultSubtotal="0">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-    <pivotField axis="axisRow" dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-      </items>
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-    <pivotField compact="0" numFmtId="10" outline="0" showAll="0" defaultSubtotal="0">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-    <pivotField compact="0" numFmtId="10" outline="0" showAll="0" defaultSubtotal="0">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-    <pivotField compact="0" numFmtId="10" outline="0" showAll="0" defaultSubtotal="0">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0">
-      <extLst>
-        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{2946ED86-A175-432a-8AC1-64E0C546D7DE}">
-          <x14:pivotField fillDownLabels="1"/>
-        </ext>
-      </extLst>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="11"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Guanyador de les prediccions" fld="11" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" fillDownLabelsDefault="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4158,7 +5137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{733616C7-25F8-4522-B3D0-0114E321248B}">
-  <dimension ref="A1:S65"/>
+  <dimension ref="A1:V65"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.90625" bestFit="1" customWidth="1"/>
@@ -4174,11 +5153,13 @@
     <col min="13" max="13" width="14.90625" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="15.81640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="48.36328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.453125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4207,10 +5188,10 @@
         <v>210</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>233</v>
@@ -4219,16 +5200,22 @@
         <v>234</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+        <v>239</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="R1" s="15" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -4287,8 +5274,16 @@
         <f>_xlfn.TEXTBEFORE(A2, ",") &amp; " vs. " &amp; _xlfn.TEXTBEFORE(B2, ",")</f>
         <v>SINNER vs. NARDI</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="Q2" s="7">
+        <f>IF(N2&gt;O2, N2, O2)</f>
+        <v>0.79</v>
+      </c>
+      <c r="R2">
+        <f>(Q2-G2)^2</f>
+        <v>4.4099999999999986E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -4346,8 +5341,16 @@
         <f t="shared" ref="P3:P65" si="7">_xlfn.TEXTBEFORE(A3, ",") &amp; " vs. " &amp; _xlfn.TEXTBEFORE(B3, ",")</f>
         <v>TSENG vs. VUKIC</v>
       </c>
-    </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="Q3" s="7">
+        <f t="shared" ref="Q3:Q65" si="8">IF(N3&gt;O3, N3, O3)</f>
+        <v>0.53</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R65" si="9">(Q3-G3)^2</f>
+        <v>0.28090000000000004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -4375,7 +5378,7 @@
         <v>225</v>
       </c>
       <c r="I4">
-        <f t="shared" ref="I4:I65" si="8">IF(H4=E4, 1, 0)</f>
+        <f t="shared" ref="I4:I65" si="10">IF(H4=E4, 1, 0)</f>
         <v>0</v>
       </c>
       <c r="J4" s="7">
@@ -4406,14 +5409,22 @@
         <f t="shared" si="7"/>
         <v>MARTÍNEZ vs. LOFFHAGEN</v>
       </c>
-      <c r="R4" s="3" t="s">
+      <c r="Q4" s="7">
+        <f t="shared" si="8"/>
+        <v>0.7</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="9"/>
+        <v>9.0000000000000024E-2</v>
+      </c>
+      <c r="U4" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="S4" s="4">
+      <c r="V4" s="4">
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -4441,7 +5452,7 @@
         <v>226</v>
       </c>
       <c r="I5">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J5" s="7">
@@ -4471,15 +5482,23 @@
         <f t="shared" si="7"/>
         <v>NAVONE vs. SHAPOVALOV</v>
       </c>
-      <c r="R5" s="5" t="s">
+      <c r="Q5" s="7">
+        <f t="shared" si="8"/>
+        <v>0.59</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="9"/>
+        <v>0.34809999999999997</v>
+      </c>
+      <c r="U5" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="S5" s="6">
+      <c r="V5" s="6">
         <f>37/64</f>
         <v>0.578125</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -4507,7 +5526,7 @@
         <v>17</v>
       </c>
       <c r="I6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J6" s="7">
@@ -4537,15 +5556,23 @@
         <f t="shared" si="7"/>
         <v>DIMITROV vs. NISHIOKA</v>
       </c>
-      <c r="R6" s="5" t="s">
+      <c r="Q6" s="7">
+        <f t="shared" si="8"/>
+        <v>0.67</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="9"/>
+        <v>0.10889999999999997</v>
+      </c>
+      <c r="U6" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="S6" s="6">
+      <c r="V6" s="6">
         <f>58/64</f>
         <v>0.90625</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -4573,7 +5600,7 @@
         <v>20</v>
       </c>
       <c r="I7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J7" s="7">
@@ -4603,15 +5630,23 @@
         <f t="shared" si="7"/>
         <v>COMESANA vs. MOUTET</v>
       </c>
-      <c r="R7" s="5" t="s">
+      <c r="Q7" s="7">
+        <f t="shared" si="8"/>
+        <v>0.54</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="9"/>
+        <v>0.21159999999999995</v>
+      </c>
+      <c r="U7" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="S7" s="6">
+      <c r="V7" s="6">
         <f>42/64</f>
         <v>0.65625</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -4639,7 +5674,7 @@
         <v>227</v>
       </c>
       <c r="I8">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J8" s="7">
@@ -4670,15 +5705,23 @@
         <f t="shared" si="7"/>
         <v>OFNER vs. MEDJEDOVIC</v>
       </c>
-      <c r="R8" s="5" t="s">
+      <c r="Q8" s="7">
+        <f t="shared" si="8"/>
+        <v>0.66</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="9"/>
+        <v>0.43560000000000004</v>
+      </c>
+      <c r="U8" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="S8" s="6">
+      <c r="V8" s="6">
         <f>41/64</f>
         <v>0.640625</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -4706,7 +5749,7 @@
         <v>26</v>
       </c>
       <c r="I9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J9" s="7">
@@ -4736,8 +5779,16 @@
         <f t="shared" si="7"/>
         <v>MONDAY vs. PAUL</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="Q9" s="7">
+        <f t="shared" si="8"/>
+        <v>0.71</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="9"/>
+        <v>8.4100000000000022E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -4765,7 +5816,7 @@
         <v>29</v>
       </c>
       <c r="I10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J10" s="7">
@@ -4796,8 +5847,23 @@
         <f t="shared" si="7"/>
         <v>SHELTON vs. BOLT</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="Q10" s="7">
+        <f t="shared" si="8"/>
+        <v>0.72</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="9"/>
+        <v>7.8400000000000011E-2</v>
+      </c>
+      <c r="U10" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="V10" s="4">
+        <f>AVERAGE(R2:R65)</f>
+        <v>0.24228281249999994</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -4825,7 +5891,7 @@
         <v>32</v>
       </c>
       <c r="I11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J11" s="7">
@@ -4856,8 +5922,22 @@
         <f t="shared" si="7"/>
         <v>HIJIKATA vs. GOFFIN</v>
       </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="Q11" s="7">
+        <f t="shared" si="8"/>
+        <v>0.53</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="9"/>
+        <v>0.28090000000000004</v>
+      </c>
+      <c r="U11" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="V11" s="16">
+        <v>0.2387</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -4885,7 +5965,7 @@
         <v>35</v>
       </c>
       <c r="I12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J12" s="7">
@@ -4916,8 +5996,16 @@
         <f t="shared" si="7"/>
         <v>KOVACEVIC vs. FUCSOVICS</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="Q12" s="7">
+        <f t="shared" si="8"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="9"/>
+        <v>0.31360000000000005</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -4945,7 +6033,7 @@
         <v>228</v>
       </c>
       <c r="I13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J13" s="7">
@@ -4976,8 +6064,23 @@
         <f t="shared" si="7"/>
         <v>MONFILS vs. HUMBERT</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="Q13" s="7">
+        <f t="shared" si="8"/>
+        <v>0.53</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="9"/>
+        <v>0.28090000000000004</v>
+      </c>
+      <c r="U13">
+        <f>(42/64)*100</f>
+        <v>65.625</v>
+      </c>
+      <c r="V13">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -5005,7 +6108,7 @@
         <v>41</v>
       </c>
       <c r="I14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J14" s="7">
@@ -5036,8 +6139,16 @@
         <f t="shared" si="7"/>
         <v>NAKASHIMA vs. BU</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="Q14" s="7">
+        <f t="shared" si="8"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="9"/>
+        <v>0.17640000000000003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -5065,7 +6176,7 @@
         <v>44</v>
       </c>
       <c r="I15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J15" s="7">
@@ -5096,8 +6207,16 @@
         <f t="shared" si="7"/>
         <v>SHEVCHENKO vs. OPELKA</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="Q15" s="7">
+        <f t="shared" si="8"/>
+        <v>0.6</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="9"/>
+        <v>0.16000000000000003</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -5125,7 +6244,7 @@
         <v>47</v>
       </c>
       <c r="I16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J16" s="7">
@@ -5155,8 +6274,16 @@
         <f t="shared" si="7"/>
         <v>FARIA vs. SONEGO</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q16" s="7">
+        <f t="shared" si="8"/>
+        <v>0.61</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="9"/>
+        <v>0.15210000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -5184,7 +6311,7 @@
         <v>230</v>
       </c>
       <c r="I17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J17" s="7">
@@ -5215,8 +6342,16 @@
         <f t="shared" si="7"/>
         <v>BASILASHVILI vs. MUSETTI</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q17" s="7">
+        <f t="shared" si="8"/>
+        <v>0.84</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="9"/>
+        <v>2.5600000000000012E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>51</v>
       </c>
@@ -5244,7 +6379,7 @@
         <v>53</v>
       </c>
       <c r="I18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J18" s="7">
@@ -5275,8 +6410,16 @@
         <f t="shared" si="7"/>
         <v>DRAPER vs. BAEZ</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q18" s="7">
+        <f t="shared" si="8"/>
+        <v>0.8</v>
+      </c>
+      <c r="R18">
+        <f t="shared" si="9"/>
+        <v>3.999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>54</v>
       </c>
@@ -5304,7 +6447,7 @@
         <v>56</v>
       </c>
       <c r="I19">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J19" s="7">
@@ -5335,8 +6478,16 @@
         <f t="shared" si="7"/>
         <v>COLLIGNON vs. CILIC</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q19" s="7">
+        <f t="shared" si="8"/>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="9"/>
+        <v>0.32489999999999997</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>57</v>
       </c>
@@ -5364,7 +6515,7 @@
         <v>59</v>
       </c>
       <c r="I20">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J20" s="7">
@@ -5395,8 +6546,16 @@
         <f t="shared" si="7"/>
         <v>MCCABE vs. MAROZSAN</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q20" s="7">
+        <f t="shared" si="8"/>
+        <v>0.63</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="9"/>
+        <v>0.13689999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>60</v>
       </c>
@@ -5424,7 +6583,7 @@
         <v>229</v>
       </c>
       <c r="I21">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J21" s="7">
@@ -5455,8 +6614,16 @@
         <f t="shared" si="7"/>
         <v>MUNAR vs. BUBLIK</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q21" s="7">
+        <f t="shared" si="8"/>
+        <v>0.52</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="9"/>
+        <v>0.27040000000000003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>63</v>
       </c>
@@ -5484,7 +6651,7 @@
         <v>65</v>
       </c>
       <c r="I22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J22" s="7">
@@ -5514,8 +6681,16 @@
         <f t="shared" si="7"/>
         <v>COBOLLI vs. ZHUKAYEV</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q22" s="7">
+        <f t="shared" si="8"/>
+        <v>0.69</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="9"/>
+        <v>9.6100000000000033E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>66</v>
       </c>
@@ -5543,7 +6718,7 @@
         <v>223</v>
       </c>
       <c r="I23">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J23" s="7">
@@ -5573,8 +6748,16 @@
         <f t="shared" si="7"/>
         <v>ETCHEVERRY vs. PINNINGTON JONES</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q23" s="7">
+        <f t="shared" si="8"/>
+        <v>0.73</v>
+      </c>
+      <c r="R23">
+        <f t="shared" si="9"/>
+        <v>0.53289999999999993</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>69</v>
       </c>
@@ -5602,7 +6785,7 @@
         <v>71</v>
       </c>
       <c r="I24">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J24" s="7">
@@ -5632,8 +6815,16 @@
         <f t="shared" si="7"/>
         <v>GIRON vs. UGO CARABELLI</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q24" s="7">
+        <f t="shared" si="8"/>
+        <v>0.53</v>
+      </c>
+      <c r="R24">
+        <f t="shared" si="9"/>
+        <v>0.22089999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>72</v>
       </c>
@@ -5661,7 +6852,7 @@
         <v>74</v>
       </c>
       <c r="I25">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J25" s="7">
@@ -5691,8 +6882,16 @@
         <f t="shared" si="7"/>
         <v>GASTON vs. MENSIK</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q25" s="7">
+        <f t="shared" si="8"/>
+        <v>0.65</v>
+      </c>
+      <c r="R25">
+        <f t="shared" si="9"/>
+        <v>0.12249999999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>75</v>
       </c>
@@ -5720,7 +6919,7 @@
         <v>77</v>
       </c>
       <c r="I26">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J26" s="7">
@@ -5751,8 +6950,16 @@
         <f t="shared" si="7"/>
         <v>DE MINAUR vs. CARBALLES BAENA</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q26" s="7">
+        <f t="shared" si="8"/>
+        <v>0.65</v>
+      </c>
+      <c r="R26">
+        <f t="shared" si="9"/>
+        <v>0.12249999999999998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -5780,7 +6987,7 @@
         <v>80</v>
       </c>
       <c r="I27">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J27" s="7">
@@ -5810,8 +7017,16 @@
         <f t="shared" si="7"/>
         <v>CAZAUX vs. WALTON</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q27" s="7">
+        <f t="shared" si="8"/>
+        <v>0.54</v>
+      </c>
+      <c r="R27">
+        <f t="shared" si="9"/>
+        <v>0.21159999999999995</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>81</v>
       </c>
@@ -5839,7 +7054,7 @@
         <v>224</v>
       </c>
       <c r="I28">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J28" s="7">
@@ -5869,8 +7084,16 @@
         <f t="shared" si="7"/>
         <v>HALYS vs. HOLMGREN</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q28" s="7">
+        <f t="shared" si="8"/>
+        <v>0.69</v>
+      </c>
+      <c r="R28">
+        <f t="shared" si="9"/>
+        <v>0.47609999999999991</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>84</v>
       </c>
@@ -5898,7 +7121,7 @@
         <v>86</v>
       </c>
       <c r="I29">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J29" s="7">
@@ -5928,8 +7151,16 @@
         <f t="shared" si="7"/>
         <v>DZUMHUR vs. MACHAC</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q29" s="7">
+        <f t="shared" si="8"/>
+        <v>0.63</v>
+      </c>
+      <c r="R29">
+        <f t="shared" si="9"/>
+        <v>0.13689999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>87</v>
       </c>
@@ -5957,7 +7188,7 @@
         <v>231</v>
       </c>
       <c r="I30">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J30" s="7">
@@ -5988,8 +7219,16 @@
         <f t="shared" si="7"/>
         <v>MICHELSEN vs. KECMANOVIC</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q30" s="7">
+        <f t="shared" si="8"/>
+        <v>0.51</v>
+      </c>
+      <c r="R30">
+        <f t="shared" si="9"/>
+        <v>0.2601</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>90</v>
       </c>
@@ -6017,7 +7256,7 @@
         <v>92</v>
       </c>
       <c r="I31">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J31" s="7">
@@ -6047,8 +7286,16 @@
         <f t="shared" si="7"/>
         <v>DE JONG vs. EUBANKS</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q31" s="7">
+        <f t="shared" si="8"/>
+        <v>0.52</v>
+      </c>
+      <c r="R31">
+        <f t="shared" si="9"/>
+        <v>0.27040000000000003</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>93</v>
       </c>
@@ -6076,7 +7323,7 @@
         <v>95</v>
       </c>
       <c r="I32">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J32" s="7">
@@ -6107,8 +7354,16 @@
         <f t="shared" si="7"/>
         <v>EVANS vs. CLARKE</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q32" s="7">
+        <f t="shared" si="8"/>
+        <v>0.52</v>
+      </c>
+      <c r="R32">
+        <f t="shared" si="9"/>
+        <v>0.23039999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>96</v>
       </c>
@@ -6136,7 +7391,7 @@
         <v>98</v>
       </c>
       <c r="I33">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J33" s="7">
@@ -6167,8 +7422,16 @@
         <f t="shared" si="7"/>
         <v>MULLER vs. DJOKOVIC</v>
       </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q33" s="7">
+        <f t="shared" si="8"/>
+        <v>0.7</v>
+      </c>
+      <c r="R33">
+        <f t="shared" si="9"/>
+        <v>9.0000000000000024E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>99</v>
       </c>
@@ -6196,7 +7459,7 @@
         <v>101</v>
       </c>
       <c r="I34">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J34" s="7">
@@ -6226,8 +7489,16 @@
         <f t="shared" si="7"/>
         <v>FRITZ vs. MPETSHI PERRICARD</v>
       </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q34" s="7">
+        <f t="shared" si="8"/>
+        <v>0.51</v>
+      </c>
+      <c r="R34">
+        <f t="shared" si="9"/>
+        <v>0.24009999999999998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>102</v>
       </c>
@@ -6255,7 +7526,7 @@
         <v>104</v>
       </c>
       <c r="I35">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J35" s="7">
@@ -6286,8 +7557,16 @@
         <f t="shared" si="7"/>
         <v>DIALLO vs. ALTMAIER</v>
       </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q35" s="7">
+        <f t="shared" si="8"/>
+        <v>0.54</v>
+      </c>
+      <c r="R35">
+        <f t="shared" si="9"/>
+        <v>0.29160000000000003</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>105</v>
       </c>
@@ -6315,7 +7594,7 @@
         <v>232</v>
       </c>
       <c r="I36">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J36" s="7">
@@ -6345,8 +7624,16 @@
         <f t="shared" si="7"/>
         <v>ARNALDI vs. VAN DE ZANDSCHULP</v>
       </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q36" s="7">
+        <f t="shared" si="8"/>
+        <v>0.6</v>
+      </c>
+      <c r="R36">
+        <f t="shared" si="9"/>
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>108</v>
       </c>
@@ -6374,7 +7661,7 @@
         <v>110</v>
       </c>
       <c r="I37">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J37" s="7">
@@ -6405,8 +7692,16 @@
         <f t="shared" si="7"/>
         <v>HOLT vs. DAVIDOVICH FOKINA</v>
       </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q37" s="7">
+        <f t="shared" si="8"/>
+        <v>0.66</v>
+      </c>
+      <c r="R37">
+        <f t="shared" si="9"/>
+        <v>0.11559999999999998</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>111</v>
       </c>
@@ -6434,7 +7729,7 @@
         <v>211</v>
       </c>
       <c r="I38">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J38" s="7">
@@ -6465,8 +7760,16 @@
         <f t="shared" si="7"/>
         <v>POPYRIN vs. FERY</v>
       </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q38" s="7">
+        <f t="shared" si="8"/>
+        <v>0.76</v>
+      </c>
+      <c r="R38">
+        <f t="shared" si="9"/>
+        <v>0.5776</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>114</v>
       </c>
@@ -6494,7 +7797,7 @@
         <v>221</v>
       </c>
       <c r="I39">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J39" s="7">
@@ -6524,8 +7827,16 @@
         <f t="shared" si="7"/>
         <v>DARDERI vs. SAFIULLIN</v>
       </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q39" s="7">
+        <f t="shared" si="8"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="R39">
+        <f t="shared" si="9"/>
+        <v>0.19359999999999997</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>117</v>
       </c>
@@ -6553,7 +7864,7 @@
         <v>119</v>
       </c>
       <c r="I40">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J40" s="7">
@@ -6583,8 +7894,16 @@
         <f t="shared" si="7"/>
         <v>KOPRIVA vs. THOMPSON</v>
       </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q40" s="7">
+        <f t="shared" si="8"/>
+        <v>0.52</v>
+      </c>
+      <c r="R40">
+        <f t="shared" si="9"/>
+        <v>0.23039999999999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>120</v>
       </c>
@@ -6612,7 +7931,7 @@
         <v>212</v>
       </c>
       <c r="I41">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J41" s="7">
@@ -6642,8 +7961,16 @@
         <f t="shared" si="7"/>
         <v>BONZI vs. MEDVEDEV</v>
       </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q41" s="7">
+        <f t="shared" si="8"/>
+        <v>0.76</v>
+      </c>
+      <c r="R41">
+        <f t="shared" si="9"/>
+        <v>0.5776</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>123</v>
       </c>
@@ -6671,7 +7998,7 @@
         <v>220</v>
       </c>
       <c r="I42">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J42" s="7">
@@ -6702,8 +8029,16 @@
         <f t="shared" si="7"/>
         <v>CERUNDOLO vs. BORGES</v>
       </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q42" s="7">
+        <f t="shared" si="8"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="R42">
+        <f t="shared" si="9"/>
+        <v>0.33639999999999998</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>126</v>
       </c>
@@ -6731,7 +8066,7 @@
         <v>128</v>
       </c>
       <c r="I43">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J43" s="7">
@@ -6761,8 +8096,16 @@
         <f t="shared" si="7"/>
         <v>HARRIS vs. LAJOVIC</v>
       </c>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q43" s="7">
+        <f t="shared" si="8"/>
+        <v>0.51</v>
+      </c>
+      <c r="R43">
+        <f t="shared" si="9"/>
+        <v>0.24009999999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>129</v>
       </c>
@@ -6790,7 +8133,7 @@
         <v>131</v>
       </c>
       <c r="I44">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J44" s="7">
@@ -6820,8 +8163,16 @@
         <f t="shared" si="7"/>
         <v>MOCHIZUKI vs. ZEPPIERI</v>
       </c>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q44" s="7">
+        <f t="shared" si="8"/>
+        <v>0.69</v>
+      </c>
+      <c r="R44">
+        <f t="shared" si="9"/>
+        <v>9.6100000000000033E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>132</v>
       </c>
@@ -6849,7 +8200,7 @@
         <v>134</v>
       </c>
       <c r="I45">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J45" s="7">
@@ -6880,8 +8231,16 @@
         <f t="shared" si="7"/>
         <v>MCDONALD vs. KHACHANOV</v>
       </c>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q45" s="7">
+        <f t="shared" si="8"/>
+        <v>0.65</v>
+      </c>
+      <c r="R45">
+        <f t="shared" si="9"/>
+        <v>0.12249999999999998</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>135</v>
       </c>
@@ -6909,7 +8268,7 @@
         <v>218</v>
       </c>
       <c r="I46">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J46" s="7">
@@ -6939,8 +8298,16 @@
         <f t="shared" si="7"/>
         <v>BERRETTINI vs. MAJCHRZAK</v>
       </c>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q46" s="7">
+        <f t="shared" si="8"/>
+        <v>0.64</v>
+      </c>
+      <c r="R46">
+        <f t="shared" si="9"/>
+        <v>0.40960000000000002</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>138</v>
       </c>
@@ -6968,7 +8335,7 @@
         <v>140</v>
       </c>
       <c r="I47">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J47" s="7">
@@ -6998,8 +8365,16 @@
         <f t="shared" si="7"/>
         <v>QUINN vs. SEARLE</v>
       </c>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q47" s="7">
+        <f t="shared" si="8"/>
+        <v>0.75</v>
+      </c>
+      <c r="R47">
+        <f t="shared" si="9"/>
+        <v>6.25E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>141</v>
       </c>
@@ -7027,7 +8402,7 @@
         <v>143</v>
       </c>
       <c r="I48">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J48" s="7">
@@ -7057,8 +8432,16 @@
         <f t="shared" si="7"/>
         <v>GARIN vs. RODESCH</v>
       </c>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q48" s="7">
+        <f t="shared" si="8"/>
+        <v>0.52</v>
+      </c>
+      <c r="R48">
+        <f t="shared" si="9"/>
+        <v>0.27040000000000003</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>144</v>
       </c>
@@ -7086,7 +8469,7 @@
         <v>219</v>
       </c>
       <c r="I49">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J49" s="7">
@@ -7116,8 +8499,16 @@
         <f t="shared" si="7"/>
         <v>RINDERKNECH vs. ZVEREV</v>
       </c>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q49" s="7">
+        <f t="shared" si="8"/>
+        <v>0.77</v>
+      </c>
+      <c r="R49">
+        <f t="shared" si="9"/>
+        <v>0.59289999999999998</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>147</v>
       </c>
@@ -7145,7 +8536,7 @@
         <v>213</v>
       </c>
       <c r="I50">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J50" s="7">
@@ -7176,8 +8567,16 @@
         <f t="shared" si="7"/>
         <v>RUNE vs. JARRY</v>
       </c>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q50" s="7">
+        <f t="shared" si="8"/>
+        <v>0.87</v>
+      </c>
+      <c r="R50">
+        <f t="shared" si="9"/>
+        <v>0.75690000000000002</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>150</v>
       </c>
@@ -7205,7 +8604,7 @@
         <v>152</v>
       </c>
       <c r="I51">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J51" s="7">
@@ -7236,8 +8635,16 @@
         <f t="shared" si="7"/>
         <v>TIEN vs. BASAVAREDDY</v>
       </c>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q51" s="7">
+        <f t="shared" si="8"/>
+        <v>0.6</v>
+      </c>
+      <c r="R51">
+        <f t="shared" si="9"/>
+        <v>0.16000000000000003</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>153</v>
       </c>
@@ -7265,7 +8672,7 @@
         <v>155</v>
       </c>
       <c r="I52">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J52" s="7">
@@ -7296,8 +8703,16 @@
         <f t="shared" si="7"/>
         <v>FEARNLEY vs. FONSECA</v>
       </c>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q52" s="7">
+        <f t="shared" si="8"/>
+        <v>0.63</v>
+      </c>
+      <c r="R52">
+        <f t="shared" si="9"/>
+        <v>0.13689999999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>156</v>
       </c>
@@ -7325,7 +8740,7 @@
         <v>214</v>
       </c>
       <c r="I53">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J53" s="7">
@@ -7355,8 +8770,16 @@
         <f t="shared" si="7"/>
         <v>BROOKSBY vs. GRIEKSPOOR</v>
       </c>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q53" s="7">
+        <f t="shared" si="8"/>
+        <v>0.65</v>
+      </c>
+      <c r="R53">
+        <f t="shared" si="9"/>
+        <v>0.42250000000000004</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>159</v>
       </c>
@@ -7384,7 +8807,7 @@
         <v>161</v>
       </c>
       <c r="I54">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J54" s="7">
@@ -7415,8 +8838,16 @@
         <f t="shared" si="7"/>
         <v>LEHECKA vs. DELLIEN</v>
       </c>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q54" s="7">
+        <f t="shared" si="8"/>
+        <v>0.59</v>
+      </c>
+      <c r="R54">
+        <f t="shared" si="9"/>
+        <v>0.16810000000000003</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>162</v>
       </c>
@@ -7444,7 +8875,7 @@
         <v>164</v>
       </c>
       <c r="I55">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J55" s="7">
@@ -7474,8 +8905,16 @@
         <f t="shared" si="7"/>
         <v>BELLUCCI vs. CRAWFORD</v>
       </c>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q55" s="7">
+        <f t="shared" si="8"/>
+        <v>0.71</v>
+      </c>
+      <c r="R55">
+        <f t="shared" si="9"/>
+        <v>8.4100000000000022E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>165</v>
       </c>
@@ -7503,7 +8942,7 @@
         <v>222</v>
       </c>
       <c r="I56">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J56" s="7">
@@ -7534,8 +8973,16 @@
         <f t="shared" si="7"/>
         <v>NORRIE vs. BAUTISTA AGUT</v>
       </c>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q56" s="7">
+        <f t="shared" si="8"/>
+        <v>0.54</v>
+      </c>
+      <c r="R56">
+        <f t="shared" si="9"/>
+        <v>0.21159999999999995</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>168</v>
       </c>
@@ -7563,7 +9010,7 @@
         <v>170</v>
       </c>
       <c r="I57">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J57" s="7">
@@ -7593,8 +9040,16 @@
         <f t="shared" si="7"/>
         <v>MOLLER vs. TIAFOE</v>
       </c>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q57" s="7">
+        <f t="shared" si="8"/>
+        <v>0.69</v>
+      </c>
+      <c r="R57">
+        <f t="shared" si="9"/>
+        <v>9.6100000000000033E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>171</v>
       </c>
@@ -7622,7 +9077,7 @@
         <v>173</v>
       </c>
       <c r="I58">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J58" s="7">
@@ -7653,8 +9108,16 @@
         <f t="shared" si="7"/>
         <v>RUBLEV vs. DJERE</v>
       </c>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q58" s="7">
+        <f t="shared" si="8"/>
+        <v>0.62</v>
+      </c>
+      <c r="R58">
+        <f t="shared" si="9"/>
+        <v>0.1444</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>174</v>
       </c>
@@ -7682,7 +9145,7 @@
         <v>215</v>
       </c>
       <c r="I59">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J59" s="7">
@@ -7712,8 +9175,16 @@
         <f t="shared" si="7"/>
         <v>BERGS vs. HARRIS</v>
       </c>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q59" s="7">
+        <f t="shared" si="8"/>
+        <v>0.73</v>
+      </c>
+      <c r="R59">
+        <f t="shared" si="9"/>
+        <v>0.53289999999999993</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>176</v>
       </c>
@@ -7741,7 +9212,7 @@
         <v>178</v>
       </c>
       <c r="I60">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J60" s="7">
@@ -7771,8 +9242,16 @@
         <f t="shared" si="7"/>
         <v>MANNARINO vs. O'CONNELL</v>
       </c>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q60" s="7">
+        <f t="shared" si="8"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="R60">
+        <f t="shared" si="9"/>
+        <v>0.33639999999999998</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>179</v>
       </c>
@@ -7800,7 +9279,7 @@
         <v>216</v>
       </c>
       <c r="I61">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J61" s="7">
@@ -7830,8 +9309,16 @@
         <f t="shared" si="7"/>
         <v>ROYER vs. TSITSIPAS</v>
       </c>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q61" s="7">
+        <f t="shared" si="8"/>
+        <v>0.62</v>
+      </c>
+      <c r="R61">
+        <f t="shared" si="9"/>
+        <v>0.38440000000000002</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>182</v>
       </c>
@@ -7859,7 +9346,7 @@
         <v>184</v>
       </c>
       <c r="I62">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J62" s="7">
@@ -7889,8 +9376,16 @@
         <f t="shared" si="7"/>
         <v>AUGER-ALIASSIME vs. DUCKWORTH</v>
       </c>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q62" s="7">
+        <f t="shared" si="8"/>
+        <v>0.69</v>
+      </c>
+      <c r="R62">
+        <f t="shared" si="9"/>
+        <v>9.6100000000000033E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>185</v>
       </c>
@@ -7918,7 +9413,7 @@
         <v>187</v>
       </c>
       <c r="I63">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J63" s="7">
@@ -7949,8 +9444,16 @@
         <f t="shared" si="7"/>
         <v>STRUFF vs. MISOLIC</v>
       </c>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q63" s="7">
+        <f t="shared" si="8"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="R63">
+        <f t="shared" si="9"/>
+        <v>0.33639999999999998</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>188</v>
       </c>
@@ -7978,7 +9481,7 @@
         <v>217</v>
       </c>
       <c r="I64">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="J64" s="7">
@@ -8009,8 +9512,16 @@
         <f t="shared" si="7"/>
         <v>TARVET vs. RIEDI</v>
       </c>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q64" s="7">
+        <f t="shared" si="8"/>
+        <v>0.54</v>
+      </c>
+      <c r="R64">
+        <f t="shared" si="9"/>
+        <v>0.29160000000000003</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>191</v>
       </c>
@@ -8038,7 +9549,7 @@
         <v>193</v>
       </c>
       <c r="I65">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>1</v>
       </c>
       <c r="J65" s="7">
@@ -8069,33 +9580,41 @@
         <f t="shared" si="7"/>
         <v>FOGNINI vs. ALCARAZ</v>
       </c>
+      <c r="Q65" s="7">
+        <f t="shared" si="8"/>
+        <v>0.87</v>
+      </c>
+      <c r="R65">
+        <f t="shared" si="9"/>
+        <v>1.6900000000000002E-2</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G65" xr:uid="{733616C7-25F8-4522-B3D0-0114E321248B}"/>
-  <conditionalFormatting sqref="G1:G1048576 H1:P1">
-    <cfRule type="cellIs" dxfId="28" priority="7" operator="equal">
+  <conditionalFormatting sqref="G1:G1048576 H1:Q1">
+    <cfRule type="cellIs" dxfId="70" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="69" priority="8" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I65">
-    <cfRule type="cellIs" dxfId="26" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="68" priority="5" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="67" priority="6" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L65">
-    <cfRule type="containsText" dxfId="24" priority="2" operator="containsText" text="Perdem">
+    <cfRule type="containsText" dxfId="66" priority="2" operator="containsText" text="Perdem">
       <formula>NOT(ISERROR(SEARCH("Perdem",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="23" priority="3" operator="containsText" text="Guanyem">
+    <cfRule type="containsText" dxfId="65" priority="3" operator="containsText" text="Guanyem">
       <formula>NOT(ISERROR(SEARCH("Guanyem",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="4" operator="containsText" text="Empat">
+    <cfRule type="containsText" dxfId="64" priority="4" operator="containsText" text="Empat">
       <formula>NOT(ISERROR(SEARCH("Empat",L2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8117,53 +9636,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED167E1B-415B-4CDC-9B3B-B08FEDF0F2A1}">
-  <dimension ref="A3:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="28.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.453125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="15" t="s">
-        <v>233</v>
-      </c>
-      <c r="B3" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>236</v>
-      </c>
-      <c r="B4" s="16">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>237</v>
-      </c>
-      <c r="B5" s="16">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>238</v>
-      </c>
-      <c r="B6" s="16">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA468E2B-B98F-49D5-BB7C-817B60D20F6A}">
   <dimension ref="A1:V33"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -8203,19 +9675,19 @@
         <v>198</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>209</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>233</v>
@@ -8224,13 +9696,19 @@
         <v>234</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="R1" s="15" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.35">
@@ -8291,6 +9769,14 @@
         <f t="shared" ref="P2:P33" si="3">_xlfn.TEXTBEFORE(A2, ",") &amp; " vs. " &amp; _xlfn.TEXTBEFORE(B2, ",")</f>
         <v>AUGER-ALIASSIME vs. STRUFF</v>
       </c>
+      <c r="Q2" s="7">
+        <f>IF(N2&gt;O2, N2, O2)</f>
+        <v>0.72</v>
+      </c>
+      <c r="R2">
+        <f>(Q2-G2)^2</f>
+        <v>0.51839999999999997</v>
+      </c>
       <c r="U2" s="3" t="s">
         <v>199</v>
       </c>
@@ -8356,6 +9842,14 @@
         <f t="shared" si="3"/>
         <v>BORGES vs. HARRIS</v>
       </c>
+      <c r="Q3" s="7">
+        <f t="shared" ref="Q3:Q33" si="8">IF(N3&gt;O3, N3, O3)</f>
+        <v>0.66</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R33" si="9">(Q3-G3)^2</f>
+        <v>0.11559999999999998</v>
+      </c>
       <c r="U3" s="5" t="s">
         <v>200</v>
       </c>
@@ -8422,6 +9916,14 @@
         <f t="shared" si="3"/>
         <v>COBOLLI vs. PINNINGTON JONES</v>
       </c>
+      <c r="Q4" s="7">
+        <f t="shared" si="8"/>
+        <v>0.75</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="9"/>
+        <v>6.25E-2</v>
+      </c>
       <c r="U4" s="5" t="s">
         <v>201</v>
       </c>
@@ -8489,6 +9991,14 @@
         <f t="shared" si="3"/>
         <v>DE MINAUR vs. CAZAUX</v>
       </c>
+      <c r="Q5" s="7">
+        <f t="shared" si="8"/>
+        <v>0.68</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="9"/>
+        <v>0.10239999999999996</v>
+      </c>
       <c r="U5" s="5" t="s">
         <v>206</v>
       </c>
@@ -8555,6 +10065,14 @@
         <f t="shared" si="3"/>
         <v>DIMITROV vs. MOUTET</v>
       </c>
+      <c r="Q6" s="7">
+        <f t="shared" si="8"/>
+        <v>0.53</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="9"/>
+        <v>0.22089999999999999</v>
+      </c>
       <c r="U6" s="5" t="s">
         <v>208</v>
       </c>
@@ -8622,8 +10140,16 @@
         <f t="shared" si="3"/>
         <v>DRAPER vs. CILIC</v>
       </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="Q7" s="7">
+        <f t="shared" si="8"/>
+        <v>0.85</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="9"/>
+        <v>0.72249999999999992</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>93</v>
       </c>
@@ -8682,6 +10208,14 @@
         <f t="shared" si="3"/>
         <v>EVANS vs. DJOKOVIC</v>
       </c>
+      <c r="Q8" s="7">
+        <f t="shared" si="8"/>
+        <v>0.87</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="9"/>
+        <v>1.6900000000000002E-2</v>
+      </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
@@ -8742,8 +10276,23 @@
         <f t="shared" si="3"/>
         <v>FERY vs. DARDERI</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="Q9" s="7">
+        <f t="shared" si="8"/>
+        <v>0.76</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="9"/>
+        <v>5.7599999999999998E-2</v>
+      </c>
+      <c r="U9" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="V9" s="4">
+        <f>AVERAGE(R2:R33)</f>
+        <v>0.22245312499999995</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>154</v>
       </c>
@@ -8802,6 +10351,20 @@
         <f t="shared" si="3"/>
         <v>FONSECA vs. BROOKSBY</v>
       </c>
+      <c r="Q10" s="7">
+        <f t="shared" si="8"/>
+        <v>0.63</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="9"/>
+        <v>0.13689999999999999</v>
+      </c>
+      <c r="U10" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="V10" s="16">
+        <v>0.2387</v>
+      </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
@@ -8862,6 +10425,14 @@
         <f t="shared" si="3"/>
         <v>FRITZ vs. DIALLO</v>
       </c>
+      <c r="Q11" s="7">
+        <f t="shared" si="8"/>
+        <v>0.72</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="9"/>
+        <v>7.8400000000000011E-2</v>
+      </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
@@ -8921,6 +10492,14 @@
         <f t="shared" si="3"/>
         <v>FUCSOVICS vs. MONFILS</v>
       </c>
+      <c r="Q12" s="7">
+        <f t="shared" si="8"/>
+        <v>0.63</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="9"/>
+        <v>0.39690000000000003</v>
+      </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
@@ -8980,6 +10559,14 @@
         <f t="shared" si="3"/>
         <v>GARIN vs. RINDERKNECH</v>
       </c>
+      <c r="Q13" s="7">
+        <f t="shared" si="8"/>
+        <v>0.53</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="9"/>
+        <v>0.22089999999999999</v>
+      </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
@@ -9039,6 +10626,14 @@
         <f t="shared" si="3"/>
         <v>GIRON vs. MENSIK</v>
       </c>
+      <c r="Q14" s="7">
+        <f t="shared" si="8"/>
+        <v>0.61</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="9"/>
+        <v>0.15210000000000001</v>
+      </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
@@ -9098,6 +10693,14 @@
         <f t="shared" si="3"/>
         <v>HOLMGREN vs. MACHAC</v>
       </c>
+      <c r="Q15" s="7">
+        <f t="shared" si="8"/>
+        <v>0.72</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="9"/>
+        <v>0.51839999999999997</v>
+      </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
@@ -9157,8 +10760,16 @@
         <f t="shared" si="3"/>
         <v>JARRY vs. TIEN</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q16" s="7">
+        <f t="shared" si="8"/>
+        <v>0.62</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="9"/>
+        <v>0.38440000000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>88</v>
       </c>
@@ -9217,8 +10828,16 @@
         <f t="shared" si="3"/>
         <v>KECMANOVIC vs. DE JONG</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q17" s="7">
+        <f t="shared" si="8"/>
+        <v>0.62</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="9"/>
+        <v>0.1444</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>159</v>
       </c>
@@ -9277,8 +10896,16 @@
         <f t="shared" si="3"/>
         <v>LEHECKA vs. BELLUCCI</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q18" s="7">
+        <f t="shared" si="8"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="R18">
+        <f t="shared" si="9"/>
+        <v>0.31360000000000005</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>136</v>
       </c>
@@ -9336,8 +10963,16 @@
         <f t="shared" si="3"/>
         <v>MAJCHRZAK vs. QUINN</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q19" s="7">
+        <f t="shared" si="8"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="R19">
+        <f t="shared" si="9"/>
+        <v>0.33639999999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>176</v>
       </c>
@@ -9395,8 +11030,16 @@
         <f t="shared" si="3"/>
         <v>MANNARINO vs. ROYER</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q20" s="7">
+        <f t="shared" si="8"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="R20">
+        <f t="shared" si="9"/>
+        <v>0.33639999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>58</v>
       </c>
@@ -9454,8 +11097,16 @@
         <f t="shared" si="3"/>
         <v>MAROZSAN vs. MUNAR</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q21" s="7">
+        <f t="shared" si="8"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="R21">
+        <f t="shared" si="9"/>
+        <v>0.17640000000000003</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -9513,8 +11164,16 @@
         <f t="shared" si="3"/>
         <v>MARTÍNEZ vs. NAVONE</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q22" s="7">
+        <f t="shared" si="8"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="R22">
+        <f t="shared" si="9"/>
+        <v>0.20249999999999996</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>129</v>
       </c>
@@ -9573,8 +11232,16 @@
         <f t="shared" si="3"/>
         <v>MOCHIZUKI vs. KHACHANOV</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q23" s="7">
+        <f t="shared" si="8"/>
+        <v>0.63</v>
+      </c>
+      <c r="R23">
+        <f t="shared" si="9"/>
+        <v>0.13689999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -9632,8 +11299,16 @@
         <f t="shared" si="3"/>
         <v>NAKASHIMA vs. OPELKA</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q24" s="7">
+        <f t="shared" si="8"/>
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="R24">
+        <f t="shared" si="9"/>
+        <v>0.20249999999999996</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>165</v>
       </c>
@@ -9691,8 +11366,16 @@
         <f t="shared" si="3"/>
         <v>NORRIE vs. TIAFOE</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q25" s="7">
+        <f t="shared" si="8"/>
+        <v>0.63</v>
+      </c>
+      <c r="R25">
+        <f t="shared" si="9"/>
+        <v>0.39690000000000003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>21</v>
       </c>
@@ -9750,8 +11433,16 @@
         <f t="shared" si="3"/>
         <v>OFNER vs. PAUL</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q26" s="7">
+        <f t="shared" si="8"/>
+        <v>0.73</v>
+      </c>
+      <c r="R26">
+        <f t="shared" si="9"/>
+        <v>0.53289999999999993</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>171</v>
       </c>
@@ -9810,8 +11501,16 @@
         <f t="shared" si="3"/>
         <v>RUBLEV vs. HARRIS</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q27" s="7">
+        <f t="shared" si="8"/>
+        <v>0.77</v>
+      </c>
+      <c r="R27">
+        <f t="shared" si="9"/>
+        <v>5.2899999999999989E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -9870,8 +11569,16 @@
         <f t="shared" si="3"/>
         <v>SHELTON vs. HIJIKATA</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q28" s="7">
+        <f t="shared" si="8"/>
+        <v>0.68</v>
+      </c>
+      <c r="R28">
+        <f t="shared" si="9"/>
+        <v>0.10239999999999996</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>3</v>
       </c>
@@ -9929,8 +11636,16 @@
         <f t="shared" si="3"/>
         <v>SINNER vs. VUKIC</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q29" s="7">
+        <f t="shared" si="8"/>
+        <v>0.9</v>
+      </c>
+      <c r="R29">
+        <f t="shared" si="9"/>
+        <v>9.999999999999995E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>46</v>
       </c>
@@ -9989,8 +11704,16 @@
         <f t="shared" si="3"/>
         <v>SONEGO vs. MUSETTI</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q30" s="7">
+        <f t="shared" si="8"/>
+        <v>0.65</v>
+      </c>
+      <c r="R30">
+        <f t="shared" si="9"/>
+        <v>0.12249999999999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>188</v>
       </c>
@@ -10049,8 +11772,16 @@
         <f t="shared" si="3"/>
         <v>TARVET vs. ALCARAZ</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q31" s="7">
+        <f t="shared" si="8"/>
+        <v>0.94</v>
+      </c>
+      <c r="R31">
+        <f t="shared" si="9"/>
+        <v>3.6000000000000064E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>118</v>
       </c>
@@ -10109,8 +11840,16 @@
         <f t="shared" si="3"/>
         <v>THOMPSON vs. BONZI</v>
       </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q32" s="7">
+        <f t="shared" si="8"/>
+        <v>0.53</v>
+      </c>
+      <c r="R32">
+        <f t="shared" si="9"/>
+        <v>0.22089999999999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>106</v>
       </c>
@@ -10168,6 +11907,14 @@
       <c r="P33" t="str">
         <f t="shared" si="3"/>
         <v>VAN DE ZANDSCHULP vs. DAVIDOVICH FOKINA</v>
+      </c>
+      <c r="Q33" s="7">
+        <f t="shared" si="8"/>
+        <v>0.65</v>
+      </c>
+      <c r="R33">
+        <f t="shared" si="9"/>
+        <v>0.12249999999999998</v>
       </c>
     </row>
   </sheetData>
@@ -10177,42 +11924,42 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="G2:G33">
-    <cfRule type="cellIs" dxfId="21" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="63" priority="11" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="62" priority="12" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:P1">
-    <cfRule type="cellIs" dxfId="19" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="61" priority="9" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="60" priority="10" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I33">
-    <cfRule type="cellIs" dxfId="17" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="59" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="58" priority="8" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L33">
-    <cfRule type="containsText" dxfId="15" priority="2" operator="containsText" text="Perdem">
+    <cfRule type="containsText" dxfId="57" priority="4" operator="containsText" text="Perdem">
       <formula>NOT(ISERROR(SEARCH("Perdem",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="Guanyem">
+    <cfRule type="containsText" dxfId="56" priority="5" operator="containsText" text="Guanyem">
       <formula>NOT(ISERROR(SEARCH("Guanyem",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="13" priority="4" operator="containsText" text="Empat">
+    <cfRule type="containsText" dxfId="55" priority="6" operator="containsText" text="Empat">
       <formula>NOT(ISERROR(SEARCH("Empat",L2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M33">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -10223,13 +11970,21 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="Q1">
+    <cfRule type="cellIs" dxfId="52" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="51" priority="2" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACEA3751-FF78-4C3C-8ABE-F983B99484C6}">
-  <dimension ref="A1:T17"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.7265625" bestFit="1" customWidth="1"/>
@@ -10243,12 +11998,13 @@
     <col min="12" max="12" width="25.81640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.90625" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="15.6328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="26" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="13.81640625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="6.90625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10268,19 +12024,19 @@
         <v>198</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>209</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>233</v>
@@ -10289,16 +12045,22 @@
         <v>234</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>239</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="R1" s="15" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -10357,8 +12119,16 @@
         <f t="shared" ref="P2" si="1">_xlfn.TEXTBEFORE(A2, ",") &amp; " vs. " &amp; _xlfn.TEXTBEFORE(B2, ",")</f>
         <v>SINNER vs. MARTÍNEZ</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="Q2" s="7">
+        <f>IF(N2&gt;O2, N2, O2)</f>
+        <v>0.85</v>
+      </c>
+      <c r="R2">
+        <f>(Q2-G2)^2</f>
+        <v>2.2500000000000006E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -10416,14 +12186,16 @@
         <f t="shared" ref="P3:P17" si="10">_xlfn.TEXTBEFORE(A3, ",") &amp; " vs. " &amp; _xlfn.TEXTBEFORE(B3, ",")</f>
         <v>DIMITROV vs. OFNER</v>
       </c>
-      <c r="S3" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="T3" s="4">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="Q3" s="7">
+        <f t="shared" ref="Q3:Q17" si="11">IF(N3&gt;O3, N3, O3)</f>
+        <v>0.7</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R17" si="12">(Q3-G3)^2</f>
+        <v>9.0000000000000024E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -10482,15 +12254,16 @@
         <f t="shared" si="10"/>
         <v>SHELTON vs. FUCSOVICS</v>
       </c>
-      <c r="S4" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="T4" s="6">
-        <f>11/16</f>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="Q4" s="7">
+        <f t="shared" si="11"/>
+        <v>0.68</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="12"/>
+        <v>0.10239999999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -10548,15 +12321,22 @@
         <f t="shared" si="10"/>
         <v>NAKASHIMA vs. SONEGO</v>
       </c>
-      <c r="S5" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="T5" s="6">
-        <f>15/16</f>
-        <v>0.9375</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="Q5" s="7">
+        <f t="shared" si="11"/>
+        <v>0.51</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="12"/>
+        <v>0.2601</v>
+      </c>
+      <c r="X5" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="Y5" s="4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>55</v>
       </c>
@@ -10614,15 +12394,23 @@
         <f t="shared" si="10"/>
         <v>CILIC vs. MUNAR</v>
       </c>
-      <c r="S6" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="T6" s="6">
-        <f>12/16</f>
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="Q6" s="7">
+        <f t="shared" si="11"/>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="12"/>
+        <v>0.32489999999999997</v>
+      </c>
+      <c r="X6" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="Y6" s="6">
+        <f>11/16</f>
+        <v>0.6875</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>63</v>
       </c>
@@ -10680,15 +12468,23 @@
         <f t="shared" si="10"/>
         <v>COBOLLI vs. MENSIK</v>
       </c>
-      <c r="S7" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="T7" s="6">
-        <f>12/16</f>
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="Q7" s="7">
+        <f t="shared" si="11"/>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="12"/>
+        <v>0.33639999999999998</v>
+      </c>
+      <c r="X7" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y7" s="6">
+        <f>15/16</f>
+        <v>0.9375</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>75</v>
       </c>
@@ -10746,8 +12542,23 @@
         <f t="shared" si="10"/>
         <v>DE MINAUR vs. HOLMGREN</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="Q8" s="7">
+        <f t="shared" si="11"/>
+        <v>0.72</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="12"/>
+        <v>7.8400000000000011E-2</v>
+      </c>
+      <c r="X8" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="Y8" s="6">
+        <f>12/16</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>88</v>
       </c>
@@ -10806,8 +12617,23 @@
         <f t="shared" si="10"/>
         <v>KECMANOVIC vs. DJOKOVIC</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="Q9" s="7">
+        <f t="shared" si="11"/>
+        <v>0.77</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="12"/>
+        <v>5.2899999999999989E-2</v>
+      </c>
+      <c r="X9" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="Y9" s="6">
+        <f>12/16</f>
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>99</v>
       </c>
@@ -10866,8 +12692,16 @@
         <f t="shared" si="10"/>
         <v>FRITZ vs. DAVIDOVICH FOKINA</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="Q10" s="7">
+        <f t="shared" si="11"/>
+        <v>0.65</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="12"/>
+        <v>0.12249999999999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>114</v>
       </c>
@@ -10881,7 +12715,7 @@
         <v>48</v>
       </c>
       <c r="E11" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F11" t="str">
         <f t="shared" si="2"/>
@@ -10892,7 +12726,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="I11">
         <f t="shared" si="4"/>
@@ -10925,8 +12759,23 @@
         <f t="shared" si="10"/>
         <v>DARDERI vs. THOMPSON</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="Q11" s="7">
+        <f t="shared" si="11"/>
+        <v>0.52</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="12"/>
+        <v>0.27040000000000003</v>
+      </c>
+      <c r="X11" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="Y11" s="4">
+        <f>AVERAGE(R2:R17)</f>
+        <v>0.18175624999999995</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>124</v>
       </c>
@@ -10984,8 +12833,22 @@
         <f t="shared" si="10"/>
         <v>BORGES vs. KHACHANOV</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="Q12" s="7">
+        <f t="shared" si="11"/>
+        <v>0.52</v>
+      </c>
+      <c r="R12">
+        <f t="shared" si="12"/>
+        <v>0.23039999999999999</v>
+      </c>
+      <c r="X12" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="Y12" s="16">
+        <v>0.2387</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>136</v>
       </c>
@@ -11044,8 +12907,16 @@
         <f t="shared" si="10"/>
         <v>MAJCHRZAK vs. RINDERKNECH</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="Q13" s="7">
+        <f t="shared" si="11"/>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="R13">
+        <f t="shared" si="12"/>
+        <v>0.18490000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>148</v>
       </c>
@@ -11104,8 +12975,16 @@
         <f t="shared" si="10"/>
         <v>JARRY vs. FONSECA</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="Q14" s="7">
+        <f t="shared" si="11"/>
+        <v>0.65</v>
+      </c>
+      <c r="R14">
+        <f t="shared" si="12"/>
+        <v>0.42250000000000004</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>162</v>
       </c>
@@ -11163,8 +13042,16 @@
         <f t="shared" si="10"/>
         <v>BELLUCCI vs. NORRIE</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="Q15" s="7">
+        <f t="shared" si="11"/>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="R15">
+        <f t="shared" si="12"/>
+        <v>0.31360000000000005</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>171</v>
       </c>
@@ -11223,8 +13110,16 @@
         <f t="shared" si="10"/>
         <v>RUBLEV vs. MANNARINO</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q16" s="7">
+        <f t="shared" si="11"/>
+        <v>0.71</v>
+      </c>
+      <c r="R16">
+        <f t="shared" si="12"/>
+        <v>8.4100000000000022E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>185</v>
       </c>
@@ -11282,6 +13177,14 @@
       <c r="P17" t="str">
         <f t="shared" si="10"/>
         <v>STRUFF vs. ALCARAZ</v>
+      </c>
+      <c r="Q17" s="7">
+        <f t="shared" si="11"/>
+        <v>0.89</v>
+      </c>
+      <c r="R17">
+        <f t="shared" si="12"/>
+        <v>1.2099999999999998E-2</v>
       </c>
     </row>
   </sheetData>
@@ -11291,42 +13194,42 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="G2:G17">
-    <cfRule type="cellIs" dxfId="12" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="50" priority="11" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="12" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:P1">
-    <cfRule type="cellIs" dxfId="10" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="9" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="10" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I17">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="45" priority="8" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L17">
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Perdem">
+    <cfRule type="containsText" dxfId="44" priority="4" operator="containsText" text="Perdem">
       <formula>NOT(ISERROR(SEARCH("Perdem",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="Guanyem">
+    <cfRule type="containsText" dxfId="43" priority="5" operator="containsText" text="Guanyem">
       <formula>NOT(ISERROR(SEARCH("Guanyem",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Empat">
+    <cfRule type="containsText" dxfId="42" priority="6" operator="containsText" text="Empat">
       <formula>NOT(ISERROR(SEARCH("Empat",L2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M2:M17">
-    <cfRule type="colorScale" priority="1">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -11337,13 +13240,21 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="Q1">
+    <cfRule type="cellIs" dxfId="41" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="40" priority="2" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7B8FC45-B22C-4AD5-9F0B-B6BE598565A3}">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.36328125" bestFit="1" customWidth="1"/>
@@ -11352,10 +13263,14 @@
     <col min="5" max="5" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.36328125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.54296875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.6328125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11377,8 +13292,41 @@
       <c r="G1" s="1" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H1" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="R1" s="15" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -11402,8 +13350,51 @@
         <f>IF(F2=E2, 1, 0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="H2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <f>IF(H2=E2, 1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="J2" s="7">
+        <f>1-0.063651</f>
+        <v>0.93634899999999999</v>
+      </c>
+      <c r="K2" s="7">
+        <f>1-J2</f>
+        <v>6.3651000000000013E-2</v>
+      </c>
+      <c r="L2" t="str">
+        <f>IF(G2=I2, "Empat", IF(I2=1, "Guanyem", "Perdem"))</f>
+        <v>Empat</v>
+      </c>
+      <c r="M2" s="7">
+        <f>IF(ISNUMBER(SEARCH(E2, A2)), J2-(C2/100), K2-(D2/100))</f>
+        <v>7.6349E-2</v>
+      </c>
+      <c r="N2" s="7">
+        <f t="shared" ref="N2:O2" si="0">C2/100</f>
+        <v>0.86</v>
+      </c>
+      <c r="O2" s="7">
+        <f t="shared" si="0"/>
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="P2" t="str">
+        <f t="shared" ref="P2" si="1">_xlfn.TEXTBEFORE(A2, ",") &amp; " vs. " &amp; _xlfn.TEXTBEFORE(B2, ",")</f>
+        <v>SINNER vs. DIMITROV</v>
+      </c>
+      <c r="Q2" s="7">
+        <f>IF(N2&gt;O2, N2, O2)</f>
+        <v>0.86</v>
+      </c>
+      <c r="R2">
+        <f>(Q2-G2)^2</f>
+        <v>1.9600000000000003E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -11420,21 +13411,63 @@
         <v>29</v>
       </c>
       <c r="F3" t="str">
-        <f t="shared" ref="F3:F9" si="0">LEFT(IF(C3&gt;D3, A3, B3), FIND(",", IF(C3&gt;D3, A3, B3)) - 1)</f>
+        <f t="shared" ref="F3:F9" si="2">LEFT(IF(C3&gt;D3, A3, B3), FIND(",", IF(C3&gt;D3, A3, B3)) - 1)</f>
         <v>SHELTON</v>
       </c>
       <c r="G3">
-        <f t="shared" ref="G3:G9" si="1">IF(F3=E3, 1, 0)</f>
-        <v>1</v>
-      </c>
-      <c r="J3" s="3" t="s">
+        <f t="shared" ref="G3:G9" si="3">IF(F3=E3, 1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I9" si="4">IF(H3=E3, 1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="J3" s="7">
+        <v>0.63477600000000001</v>
+      </c>
+      <c r="K3" s="7">
+        <f t="shared" ref="K3:K9" si="5">1-J3</f>
+        <v>0.36522399999999999</v>
+      </c>
+      <c r="L3" t="str">
+        <f t="shared" ref="L3:L9" si="6">IF(G3=I3, "Empat", IF(I3=1, "Guanyem", "Perdem"))</f>
+        <v>Empat</v>
+      </c>
+      <c r="M3" s="7">
+        <f t="shared" ref="M3:M9" si="7">IF(ISNUMBER(SEARCH(E3, A3)), J3-(C3/100), K3-(D3/100))</f>
+        <v>4.7760000000000025E-3</v>
+      </c>
+      <c r="N3" s="7">
+        <f t="shared" ref="N3:N9" si="8">C3/100</f>
+        <v>0.63</v>
+      </c>
+      <c r="O3" s="7">
+        <f t="shared" ref="O3:O9" si="9">D3/100</f>
+        <v>0.37</v>
+      </c>
+      <c r="P3" t="str">
+        <f t="shared" ref="P3:P9" si="10">_xlfn.TEXTBEFORE(A3, ",") &amp; " vs. " &amp; _xlfn.TEXTBEFORE(B3, ",")</f>
+        <v>SHELTON vs. SONEGO</v>
+      </c>
+      <c r="Q3" s="7">
+        <f t="shared" ref="Q3:Q9" si="11">IF(N3&gt;O3, N3, O3)</f>
+        <v>0.63</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R9" si="12">(Q3-G3)^2</f>
+        <v>0.13689999999999999</v>
+      </c>
+      <c r="V3" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="K3" s="4">
+      <c r="W3" s="4">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>55</v>
       </c>
@@ -11451,22 +13484,64 @@
         <v>65</v>
       </c>
       <c r="F4" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>COBOLLI</v>
       </c>
       <c r="G4">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="J4" s="5" t="s">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J4" s="7">
+        <v>0.67331799999999997</v>
+      </c>
+      <c r="K4" s="7">
+        <f t="shared" si="5"/>
+        <v>0.32668200000000003</v>
+      </c>
+      <c r="L4" t="str">
+        <f t="shared" si="6"/>
+        <v>Perdem</v>
+      </c>
+      <c r="M4" s="7">
+        <f t="shared" si="7"/>
+        <v>-0.35331800000000002</v>
+      </c>
+      <c r="N4" s="7">
+        <f t="shared" si="8"/>
+        <v>0.32</v>
+      </c>
+      <c r="O4" s="7">
+        <f t="shared" si="9"/>
+        <v>0.68</v>
+      </c>
+      <c r="P4" t="str">
+        <f t="shared" si="10"/>
+        <v>CILIC vs. COBOLLI</v>
+      </c>
+      <c r="Q4" s="7">
+        <f t="shared" si="11"/>
+        <v>0.68</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="12"/>
+        <v>0.10239999999999996</v>
+      </c>
+      <c r="V4" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="K4" s="6">
+      <c r="W4" s="6">
         <f>8/8</f>
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>75</v>
       </c>
@@ -11483,22 +13558,64 @@
         <v>98</v>
       </c>
       <c r="F5" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>DJOKOVIC</v>
       </c>
       <c r="G5">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="J5" s="5" t="s">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>98</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J5" s="7">
+        <v>0.29965999999999998</v>
+      </c>
+      <c r="K5" s="7">
+        <f t="shared" si="5"/>
+        <v>0.70033999999999996</v>
+      </c>
+      <c r="L5" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M5" s="7">
+        <f t="shared" si="7"/>
+        <v>-9.6600000000000019E-3</v>
+      </c>
+      <c r="N5" s="7">
+        <f t="shared" si="8"/>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="O5" s="7">
+        <f t="shared" si="9"/>
+        <v>0.71</v>
+      </c>
+      <c r="P5" t="str">
+        <f t="shared" si="10"/>
+        <v>DE MINAUR vs. DJOKOVIC</v>
+      </c>
+      <c r="Q5" s="7">
+        <f t="shared" si="11"/>
+        <v>0.71</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="12"/>
+        <v>8.4100000000000022E-2</v>
+      </c>
+      <c r="V5" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="K5" s="6">
+      <c r="W5" s="6">
         <f>7/8</f>
         <v>0.875</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>99</v>
       </c>
@@ -11515,22 +13632,64 @@
         <v>101</v>
       </c>
       <c r="F6" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>FRITZ</v>
       </c>
       <c r="G6">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="J6" s="5" t="s">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H6" t="s">
+        <v>101</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J6" s="7">
+        <v>0.94166899999999998</v>
+      </c>
+      <c r="K6" s="7">
+        <f t="shared" si="5"/>
+        <v>5.8331000000000022E-2</v>
+      </c>
+      <c r="L6" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M6" s="7">
+        <f t="shared" si="7"/>
+        <v>0.17166899999999996</v>
+      </c>
+      <c r="N6" s="7">
+        <f t="shared" si="8"/>
+        <v>0.77</v>
+      </c>
+      <c r="O6" s="7">
+        <f t="shared" si="9"/>
+        <v>0.23</v>
+      </c>
+      <c r="P6" t="str">
+        <f t="shared" si="10"/>
+        <v>FRITZ vs. THOMPSON</v>
+      </c>
+      <c r="Q6" s="7">
+        <f t="shared" si="11"/>
+        <v>0.77</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="12"/>
+        <v>5.2899999999999989E-2</v>
+      </c>
+      <c r="V6" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="K6" s="6">
+      <c r="W6" s="6">
         <f>6/8</f>
         <v>0.75</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>133</v>
       </c>
@@ -11547,22 +13706,64 @@
         <v>134</v>
       </c>
       <c r="F7" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>KHACHANOV</v>
       </c>
       <c r="G7">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="J7" s="5" t="s">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>134</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J7" s="7">
+        <v>0.668462</v>
+      </c>
+      <c r="K7" s="7">
+        <f t="shared" si="5"/>
+        <v>0.331538</v>
+      </c>
+      <c r="L7" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M7" s="7">
+        <f t="shared" si="7"/>
+        <v>-1.1538000000000048E-2</v>
+      </c>
+      <c r="N7" s="7">
+        <f t="shared" si="8"/>
+        <v>0.68</v>
+      </c>
+      <c r="O7" s="7">
+        <f t="shared" si="9"/>
+        <v>0.32</v>
+      </c>
+      <c r="P7" t="str">
+        <f t="shared" si="10"/>
+        <v>KHACHANOV vs. MAJCHRZAK</v>
+      </c>
+      <c r="Q7" s="7">
+        <f t="shared" si="11"/>
+        <v>0.68</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="12"/>
+        <v>0.10239999999999996</v>
+      </c>
+      <c r="V7" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="K7" s="6">
+      <c r="W7" s="6">
         <f>7/8</f>
         <v>0.875</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>148</v>
       </c>
@@ -11579,15 +13780,57 @@
         <v>167</v>
       </c>
       <c r="F8" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>NORRIE</v>
       </c>
       <c r="G8">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>149</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="7">
+        <v>0.52766400000000002</v>
+      </c>
+      <c r="K8" s="7">
+        <f t="shared" si="5"/>
+        <v>0.47233599999999998</v>
+      </c>
+      <c r="L8" t="str">
+        <f t="shared" si="6"/>
+        <v>Perdem</v>
+      </c>
+      <c r="M8" s="7">
+        <f t="shared" si="7"/>
+        <v>-0.11766399999999999</v>
+      </c>
+      <c r="N8" s="7">
+        <f t="shared" si="8"/>
+        <v>0.41</v>
+      </c>
+      <c r="O8" s="7">
+        <f t="shared" si="9"/>
+        <v>0.59</v>
+      </c>
+      <c r="P8" t="str">
+        <f t="shared" si="10"/>
+        <v>JARRY vs. NORRIE</v>
+      </c>
+      <c r="Q8" s="7">
+        <f t="shared" si="11"/>
+        <v>0.59</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="12"/>
+        <v>0.16810000000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>171</v>
       </c>
@@ -11604,17 +13847,585 @@
         <v>193</v>
       </c>
       <c r="F9" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>ALCARAZ</v>
       </c>
       <c r="G9">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="H9" t="s">
+        <v>193</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="J9" s="7">
+        <f>1-0.994118</f>
+        <v>5.8820000000000539E-3</v>
+      </c>
+      <c r="K9" s="7">
+        <f t="shared" si="5"/>
+        <v>0.99411799999999995</v>
+      </c>
+      <c r="L9" t="str">
+        <f t="shared" si="6"/>
+        <v>Empat</v>
+      </c>
+      <c r="M9" s="7">
+        <f t="shared" si="7"/>
+        <v>0.24411799999999995</v>
+      </c>
+      <c r="N9" s="7">
+        <f t="shared" si="8"/>
+        <v>0.25</v>
+      </c>
+      <c r="O9" s="7">
+        <f t="shared" si="9"/>
+        <v>0.75</v>
+      </c>
+      <c r="P9" t="str">
+        <f t="shared" si="10"/>
+        <v>RUBLEV vs. ALCARAZ</v>
+      </c>
+      <c r="Q9" s="7">
+        <f t="shared" si="11"/>
+        <v>0.75</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="12"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="W9" s="4">
+        <f>AVERAGE(R2:R9)</f>
+        <v>9.1112499999999999E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="V10" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="W10" s="16">
+        <v>0.2387</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G9">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="11" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J1:P1">
+    <cfRule type="cellIs" dxfId="38" priority="9" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="10" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I9">
+    <cfRule type="cellIs" dxfId="36" priority="7" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="35" priority="8" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L9">
+    <cfRule type="containsText" dxfId="34" priority="4" operator="containsText" text="Perdem">
+      <formula>NOT(ISERROR(SEARCH("Perdem",L2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="33" priority="5" operator="containsText" text="Guanyem">
+      <formula>NOT(ISERROR(SEARCH("Guanyem",L2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="32" priority="6" operator="containsText" text="Empat">
+      <formula>NOT(ISERROR(SEARCH("Empat",L2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M9">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q1">
+    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="2" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B426FC20-F2D4-42EE-B26E-57F7A91BDF6D}">
+  <dimension ref="A1:X11"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="R1" s="15" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>21</v>
+      </c>
+      <c r="D2">
+        <v>79</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="str">
+        <f>LEFT(IF(C2&gt;D2, A2, B2), FIND(",", IF(C2&gt;D2, A2, B2)) - 1)</f>
+        <v>SINNER</v>
+      </c>
+      <c r="G2">
+        <f>IF(F2=E2, 1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <f>IF(H2=E2, 1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="J2" s="7">
+        <v>0.25052200000000002</v>
+      </c>
+      <c r="K2" s="7">
+        <f>1-J2</f>
+        <v>0.74947799999999998</v>
+      </c>
+      <c r="L2" t="str">
+        <f>IF(G2=I2, "Empat", IF(I2=1, "Guanyem", "Perdem"))</f>
+        <v>Empat</v>
+      </c>
+      <c r="M2" s="7">
+        <f>IF(ISNUMBER(SEARCH(E2, A2)), J2-(C2/100), K2-(D2/100))</f>
+        <v>-4.0522000000000058E-2</v>
+      </c>
+      <c r="N2" s="7">
+        <f t="shared" ref="N2:O2" si="0">C2/100</f>
+        <v>0.21</v>
+      </c>
+      <c r="O2" s="7">
+        <f t="shared" si="0"/>
+        <v>0.79</v>
+      </c>
+      <c r="P2" t="str">
+        <f t="shared" ref="P2" si="1">_xlfn.TEXTBEFORE(A2, ",") &amp; " vs. " &amp; _xlfn.TEXTBEFORE(B2, ",")</f>
+        <v>SHELTON vs. SINNER</v>
+      </c>
+      <c r="Q2" s="7">
+        <f>IF(N2&gt;O2, N2, O2)</f>
+        <v>0.79</v>
+      </c>
+      <c r="R2">
+        <f>(Q2-G2)^2</f>
+        <v>4.4099999999999986E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C3">
+        <v>28</v>
+      </c>
+      <c r="D3">
+        <v>72</v>
+      </c>
+      <c r="E3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F3" t="str">
+        <f>LEFT(IF(C3&gt;D3, A3, B3), FIND(",", IF(C3&gt;D3, A3, B3)) - 1)</f>
+        <v>DJOKOVIC</v>
+      </c>
+      <c r="G3">
+        <f>IF(F3=E3, 1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I3">
+        <f t="shared" ref="I3:I5" si="2">IF(H3=E3, 1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="J3" s="7">
+        <v>0.118141</v>
+      </c>
+      <c r="K3" s="7">
+        <f t="shared" ref="K3:K5" si="3">1-J3</f>
+        <v>0.88185899999999995</v>
+      </c>
+      <c r="L3" t="str">
+        <f t="shared" ref="L3:L5" si="4">IF(G3=I3, "Empat", IF(I3=1, "Guanyem", "Perdem"))</f>
+        <v>Empat</v>
+      </c>
+      <c r="M3" s="7">
+        <f t="shared" ref="M3:M5" si="5">IF(ISNUMBER(SEARCH(E3, A3)), J3-(C3/100), K3-(D3/100))</f>
+        <v>0.16185899999999998</v>
+      </c>
+      <c r="N3" s="7">
+        <f t="shared" ref="N3:N5" si="6">C3/100</f>
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="O3" s="7">
+        <f t="shared" ref="O3:O5" si="7">D3/100</f>
+        <v>0.72</v>
+      </c>
+      <c r="P3" t="str">
+        <f t="shared" ref="P3:P5" si="8">_xlfn.TEXTBEFORE(A3, ",") &amp; " vs. " &amp; _xlfn.TEXTBEFORE(B3, ",")</f>
+        <v>COBOLLI vs. DJOKOVIC</v>
+      </c>
+      <c r="Q3" s="7">
+        <f t="shared" ref="Q3:Q5" si="9">IF(N3&gt;O3, N3, O3)</f>
+        <v>0.72</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R5" si="10">(Q3-G3)^2</f>
+        <v>7.8400000000000011E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C4">
+        <v>34</v>
+      </c>
+      <c r="D4">
+        <v>66</v>
+      </c>
+      <c r="E4" t="s">
+        <v>101</v>
+      </c>
+      <c r="F4" t="str">
+        <f>LEFT(IF(C4&gt;D4, A4, B4), FIND(",", IF(C4&gt;D4, A4, B4)) - 1)</f>
+        <v>FRITZ</v>
+      </c>
+      <c r="G4">
+        <f>IF(F4=E4, 1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J4" s="7">
+        <f>1-0.732573</f>
+        <v>0.26742699999999997</v>
+      </c>
+      <c r="K4" s="7">
+        <f t="shared" si="3"/>
+        <v>0.73257300000000003</v>
+      </c>
+      <c r="L4" t="str">
+        <f t="shared" si="4"/>
+        <v>Empat</v>
+      </c>
+      <c r="M4" s="7">
+        <f t="shared" si="5"/>
+        <v>7.2572999999999999E-2</v>
+      </c>
+      <c r="N4" s="7">
+        <f t="shared" si="6"/>
+        <v>0.34</v>
+      </c>
+      <c r="O4" s="7">
+        <f t="shared" si="7"/>
+        <v>0.66</v>
+      </c>
+      <c r="P4" t="str">
+        <f t="shared" si="8"/>
+        <v>KHACHANOV vs. FRITZ</v>
+      </c>
+      <c r="Q4" s="7">
+        <f t="shared" si="9"/>
+        <v>0.66</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="10"/>
+        <v>0.11559999999999998</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="X4" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>192</v>
+      </c>
+      <c r="B5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C5">
+        <v>87</v>
+      </c>
+      <c r="D5">
+        <v>13</v>
+      </c>
+      <c r="E5" t="s">
+        <v>193</v>
+      </c>
+      <c r="F5" t="str">
+        <f>LEFT(IF(C5&gt;D5, A5, B5), FIND(",", IF(C5&gt;D5, A5, B5)) - 1)</f>
+        <v>ALCARAZ</v>
+      </c>
+      <c r="G5">
+        <f>IF(F5=E5, 1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>193</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J5" s="7">
+        <v>0.925485</v>
+      </c>
+      <c r="K5" s="7">
+        <f t="shared" si="3"/>
+        <v>7.4514999999999998E-2</v>
+      </c>
+      <c r="L5" t="str">
+        <f t="shared" si="4"/>
+        <v>Empat</v>
+      </c>
+      <c r="M5" s="7">
+        <f t="shared" si="5"/>
+        <v>5.5485000000000007E-2</v>
+      </c>
+      <c r="N5" s="7">
+        <f t="shared" si="6"/>
+        <v>0.87</v>
+      </c>
+      <c r="O5" s="7">
+        <f t="shared" si="7"/>
+        <v>0.13</v>
+      </c>
+      <c r="P5" t="str">
+        <f t="shared" si="8"/>
+        <v>ALCARAZ vs. NORRIE</v>
+      </c>
+      <c r="Q5" s="7">
+        <f t="shared" si="9"/>
+        <v>0.87</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="10"/>
+        <v>1.6900000000000002E-2</v>
+      </c>
+      <c r="W5" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="X5" s="6">
+        <f>4/4</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="W6" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="X6" s="6">
+        <f>4/4</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="W7" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="X7" s="6">
+        <f>4/4</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="W8" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="X8" s="6">
+        <f>4/4</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="W10" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="X10" s="4">
+        <f>AVERAGE(R2:R5)</f>
+        <v>6.3750000000000001E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="W11" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="X11" s="16">
+        <v>0.2387</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="G2:G5">
+    <cfRule type="cellIs" dxfId="29" priority="11" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J1:P1">
+    <cfRule type="cellIs" dxfId="28" priority="9" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="27" priority="10" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I5">
+    <cfRule type="cellIs" dxfId="26" priority="7" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="25" priority="8" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L5">
+    <cfRule type="containsText" dxfId="24" priority="4" operator="containsText" text="Perdem">
+      <formula>NOT(ISERROR(SEARCH("Perdem",L2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="23" priority="5" operator="containsText" text="Guanyem">
+      <formula>NOT(ISERROR(SEARCH("Guanyem",L2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="22" priority="6" operator="containsText" text="Empat">
+      <formula>NOT(ISERROR(SEARCH("Empat",L2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M5">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q1">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11623,193 +14434,8 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B426FC20-F2D4-42EE-B26E-57F7A91BDF6D}">
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>21</v>
-      </c>
-      <c r="D2">
-        <v>79</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="str">
-        <f>LEFT(IF(C2&gt;D2, A2, B2), FIND(",", IF(C2&gt;D2, A2, B2)) - 1)</f>
-        <v>SINNER</v>
-      </c>
-      <c r="G2">
-        <f>IF(F2=E2, 1, 0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C3">
-        <v>28</v>
-      </c>
-      <c r="D3">
-        <v>72</v>
-      </c>
-      <c r="E3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F3" t="str">
-        <f>LEFT(IF(C3&gt;D3, A3, B3), FIND(",", IF(C3&gt;D3, A3, B3)) - 1)</f>
-        <v>DJOKOVIC</v>
-      </c>
-      <c r="G3">
-        <f>IF(F3=E3, 1, 0)</f>
-        <v>1</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K3" s="4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C4">
-        <v>34</v>
-      </c>
-      <c r="D4">
-        <v>66</v>
-      </c>
-      <c r="E4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F4" t="str">
-        <f>LEFT(IF(C4&gt;D4, A4, B4), FIND(",", IF(C4&gt;D4, A4, B4)) - 1)</f>
-        <v>FRITZ</v>
-      </c>
-      <c r="G4">
-        <f>IF(F4=E4, 1, 0)</f>
-        <v>1</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="K4" s="6">
-        <f>4/4</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>192</v>
-      </c>
-      <c r="B5" t="s">
-        <v>165</v>
-      </c>
-      <c r="C5">
-        <v>87</v>
-      </c>
-      <c r="D5">
-        <v>13</v>
-      </c>
-      <c r="E5" t="s">
-        <v>193</v>
-      </c>
-      <c r="F5" t="str">
-        <f>LEFT(IF(C5&gt;D5, A5, B5), FIND(",", IF(C5&gt;D5, A5, B5)) - 1)</f>
-        <v>ALCARAZ</v>
-      </c>
-      <c r="G5">
-        <f>IF(F5=E5, 1, 0)</f>
-        <v>1</v>
-      </c>
-      <c r="J5" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="K5" s="6">
-        <f>4/4</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="J6" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="K6" s="6">
-        <f>4/4</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="J7" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="K7" s="6">
-        <f>4/4</f>
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="G2:G5">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F3217C8-0180-4F68-B33D-869F44F7E5B7}">
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
@@ -11819,9 +14445,12 @@
     <col min="6" max="6" width="10.36328125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.1796875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11843,8 +14472,41 @@
       <c r="G1" s="1" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="H1" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="R1" s="15" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -11868,8 +14530,51 @@
         <f>IF(F2=E2, 1, 0)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="H2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2">
+        <f>IF(H2=E2, 1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <f>1-0.468072</f>
+        <v>0.53192799999999996</v>
+      </c>
+      <c r="K2">
+        <f>1-J2</f>
+        <v>0.46807200000000004</v>
+      </c>
+      <c r="L2" t="str">
+        <f>IF(G2=I2, "Empat", IF(I2=1, "Guanyem", "Perdem"))</f>
+        <v>Empat</v>
+      </c>
+      <c r="M2" s="7">
+        <f>IF(ISNUMBER(SEARCH(E2, A2)), J2-(C2/100), K2-(D2/100))</f>
+        <v>-4.8072000000000004E-2</v>
+      </c>
+      <c r="N2" s="7">
+        <f t="shared" ref="N2:O2" si="0">C2/100</f>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="O2" s="7">
+        <f t="shared" si="0"/>
+        <v>0.42</v>
+      </c>
+      <c r="P2" t="str">
+        <f t="shared" ref="P2" si="1">_xlfn.TEXTBEFORE(A2, ",") &amp; " vs. " &amp; _xlfn.TEXTBEFORE(B2, ",")</f>
+        <v>SINNER vs. DJOKOVIC</v>
+      </c>
+      <c r="Q2" s="7">
+        <f>IF(N2&gt;O2, N2, O2)</f>
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="R2">
+        <f>(Q2-G2)^2</f>
+        <v>0.17640000000000003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>192</v>
       </c>
@@ -11893,43 +14598,411 @@
         <f>IF(F3=E3, 1, 0)</f>
         <v>1</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="H3" t="s">
+        <v>193</v>
+      </c>
+      <c r="I3">
+        <f>IF(H3=E3, 1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>0.80112700000000003</v>
+      </c>
+      <c r="K3">
+        <f>1-J3</f>
+        <v>0.19887299999999997</v>
+      </c>
+      <c r="L3" t="str">
+        <f>IF(G3=I3, "Empat", IF(I3=1, "Guanyem", "Perdem"))</f>
+        <v>Empat</v>
+      </c>
+      <c r="M3" s="7">
+        <f>IF(ISNUMBER(SEARCH(E3, A3)), J3-(C3/100), K3-(D3/100))</f>
+        <v>0.20112700000000006</v>
+      </c>
+      <c r="N3" s="7">
+        <f t="shared" ref="N3" si="2">C3/100</f>
+        <v>0.6</v>
+      </c>
+      <c r="O3" s="7">
+        <f t="shared" ref="O3" si="3">D3/100</f>
+        <v>0.4</v>
+      </c>
+      <c r="P3" t="str">
+        <f t="shared" ref="P3" si="4">_xlfn.TEXTBEFORE(A3, ",") &amp; " vs. " &amp; _xlfn.TEXTBEFORE(B3, ",")</f>
+        <v>ALCARAZ vs. FRITZ</v>
+      </c>
+      <c r="Q3" s="7">
+        <f>IF(N3&gt;O3, N3, O3)</f>
+        <v>0.6</v>
+      </c>
+      <c r="R3">
+        <f>(Q3-G3)^2</f>
+        <v>0.16000000000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="U7" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="K3" s="4">
+      <c r="V7" s="4">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="J4" s="5" t="s">
+    <row r="8" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="U8" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="K4" s="6">
+      <c r="V8" s="6">
         <f>2/2</f>
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="J5" s="5" t="s">
+    <row r="9" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="U9" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="K5" s="6">
+      <c r="V9" s="6">
         <f>2/2</f>
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="J6" s="5" t="s">
+    <row r="10" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="U10" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="K6" s="6">
+      <c r="V10" s="6">
         <f>2/2</f>
         <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="U12" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="V12" s="4">
+        <f>AVERAGE(R2:R3)</f>
+        <v>0.16820000000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="U13" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="V13" s="16">
+        <v>0.2387</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G3">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="11" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J1:P1">
+    <cfRule type="cellIs" dxfId="20" priority="9" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="10" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I3">
+    <cfRule type="cellIs" dxfId="18" priority="7" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="17" priority="8" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2:L3">
+    <cfRule type="containsText" dxfId="16" priority="4" operator="containsText" text="Perdem">
+      <formula>NOT(ISERROR(SEARCH("Perdem",L2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="15" priority="5" operator="containsText" text="Guanyem">
+      <formula>NOT(ISERROR(SEARCH("Guanyem",L2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="14" priority="6" operator="containsText" text="Empat">
+      <formula>NOT(ISERROR(SEARCH("Empat",L2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2:M3">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q1">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{290BA5AE-209F-4B33-912E-0B335547B6EF}">
+  <dimension ref="A1:W10"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.54296875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.90625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="R1" s="15" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2">
+        <v>53</v>
+      </c>
+      <c r="D2">
+        <v>47</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" t="str">
+        <f>LEFT(IF(C2&gt;D2, A2, B2), FIND(",", IF(C2&gt;D2, A2, B2)) - 1)</f>
+        <v>SINNER</v>
+      </c>
+      <c r="G2">
+        <f>IF(F2=E2, 1, 0)</f>
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I2">
+        <f>IF(H2=E2, 1, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <f>1-0.568089</f>
+        <v>0.43191100000000004</v>
+      </c>
+      <c r="K2">
+        <f>1-J2</f>
+        <v>0.56808899999999996</v>
+      </c>
+      <c r="L2" t="str">
+        <f>IF(G2=I2, "Empat", IF(I2=1, "Guanyem", "Perdem"))</f>
+        <v>Perdem</v>
+      </c>
+      <c r="M2" s="7">
+        <f>IF(ISNUMBER(SEARCH(E2, A2)), J2-(C2/100), K2-(D2/100))</f>
+        <v>-9.8088999999999982E-2</v>
+      </c>
+      <c r="N2" s="7">
+        <f t="shared" ref="N2:O2" si="0">C2/100</f>
+        <v>0.53</v>
+      </c>
+      <c r="O2" s="7">
+        <f t="shared" si="0"/>
+        <v>0.47</v>
+      </c>
+      <c r="P2" t="str">
+        <f t="shared" ref="P2" si="1">_xlfn.TEXTBEFORE(A2, ",") &amp; " vs. " &amp; _xlfn.TEXTBEFORE(B2, ",")</f>
+        <v>SINNER vs. ALCARAZ</v>
+      </c>
+      <c r="Q2" s="7">
+        <f>IF(N2&gt;O2, N2, O2)</f>
+        <v>0.53</v>
+      </c>
+      <c r="R2">
+        <f>(Q2-G2)^2</f>
+        <v>0.22089999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="V4" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="W4" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="V5" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="W5" s="6">
+        <f>1/1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="V6" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="W6" s="6">
+        <f>0/1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="V7" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="W7" s="6">
+        <f>0/1</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="V9" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="W9" s="4">
+        <f>AVERAGE(R2:R2)</f>
+        <v>0.22089999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="V10" s="5" t="s">
+        <v>260</v>
+      </c>
+      <c r="W10" s="16">
+        <v>0.2387</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="G2">
+    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J1:P1">
+    <cfRule type="cellIs" dxfId="12" priority="9" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2">
+    <cfRule type="cellIs" dxfId="10" priority="7" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="9" priority="8" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L2">
+    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="Perdem">
+      <formula>NOT(ISERROR(SEARCH("Perdem",L2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="Guanyem">
+      <formula>NOT(ISERROR(SEARCH("Guanyem",L2)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="6" priority="6" operator="containsText" text="Empat">
+      <formula>NOT(ISERROR(SEARCH("Empat",L2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M2">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q1">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11938,113 +15011,6 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{290BA5AE-209F-4B33-912E-0B335547B6EF}">
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>192</v>
-      </c>
-      <c r="C2">
-        <v>53</v>
-      </c>
-      <c r="D2">
-        <v>47</v>
-      </c>
-      <c r="E2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" t="str">
-        <f>LEFT(IF(C2&gt;D2, A2, B2), FIND(",", IF(C2&gt;D2, A2, B2)) - 1)</f>
-        <v>SINNER</v>
-      </c>
-      <c r="G2">
-        <f>IF(F2=E2, 1, 0)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="J3" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K3" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="J4" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="K4" s="6">
-        <f>1/1</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="J5" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="K5" s="6">
-        <f>0/1</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="J6" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="K6" s="6">
-        <f>0/1</f>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="G2">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03439C7F-BE26-46C4-AF78-BFBDE843F874}">
   <dimension ref="B1:J11"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -12107,6 +15073,224 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2770F40-497A-498C-ABFF-A4B16B10C6BF}">
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="20.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B2">
+        <v>37</v>
+      </c>
+      <c r="C2">
+        <v>42</v>
+      </c>
+      <c r="D2" s="7">
+        <f>(B2/64)</f>
+        <v>0.578125</v>
+      </c>
+      <c r="E2" s="7">
+        <f>(C2/64)</f>
+        <v>0.65625</v>
+      </c>
+      <c r="F2">
+        <v>0.2387</v>
+      </c>
+      <c r="G2">
+        <v>0.2387</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B3">
+        <v>22</v>
+      </c>
+      <c r="C3">
+        <v>23</v>
+      </c>
+      <c r="D3" s="7">
+        <f>(B3/32)</f>
+        <v>0.6875</v>
+      </c>
+      <c r="E3" s="7">
+        <f>(C3/32)</f>
+        <v>0.71875</v>
+      </c>
+      <c r="F3">
+        <v>0.22245312499999995</v>
+      </c>
+      <c r="G3">
+        <v>0.2185</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B4">
+        <v>11</v>
+      </c>
+      <c r="C4">
+        <v>12</v>
+      </c>
+      <c r="D4" s="7">
+        <f>(B4/16)</f>
+        <v>0.6875</v>
+      </c>
+      <c r="E4" s="7">
+        <f>(C4/16)</f>
+        <v>0.75</v>
+      </c>
+      <c r="F4">
+        <v>0.18175624999999995</v>
+      </c>
+      <c r="G4">
+        <v>0.1578</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B5">
+        <v>8</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5" s="7">
+        <f>(B5/8)</f>
+        <v>1</v>
+      </c>
+      <c r="E5" s="7">
+        <f>(C5/8)</f>
+        <v>0.75</v>
+      </c>
+      <c r="F5">
+        <v>9.1112499999999999E-2</v>
+      </c>
+      <c r="G5">
+        <v>0.13400000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>248</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>4</v>
+      </c>
+      <c r="D6" s="7">
+        <f>(B6/4)</f>
+        <v>1</v>
+      </c>
+      <c r="E6" s="7">
+        <f>(C6/4)</f>
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>6.3750000000000001E-2</v>
+      </c>
+      <c r="G6">
+        <v>3.8399999999999997E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>252</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7" s="7">
+        <f>(B7/2)</f>
+        <v>1</v>
+      </c>
+      <c r="E7" s="7">
+        <f>(C7/2)</f>
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>0.16820000000000002</v>
+      </c>
+      <c r="G7">
+        <v>0.1293</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>249</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7">
+        <f>(B8/1)</f>
+        <v>1</v>
+      </c>
+      <c r="E8" s="7">
+        <f>(C8/1)</f>
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0.22089999999999999</v>
+      </c>
+      <c r="G8">
+        <v>0.32269999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/ResultatWimbeldon.xlsx
+++ b/ResultatWimbeldon.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ikerr\Code\TFG\Program\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/iker/Code/TFG/Me-vs.-IBM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0FF5199-3656-4F0A-AA04-74E5F4133A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07BAC0F2-BEEA-954E-A5BC-9BE9E91E2341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25420" windowHeight="16300" firstSheet="1" activeTab="8" xr2:uid="{0ED45994-5EFE-4A4E-8BA9-C3AA32741888}"/>
+    <workbookView xWindow="38400" yWindow="620" windowWidth="38400" windowHeight="20980" xr2:uid="{0ED45994-5EFE-4A4E-8BA9-C3AA32741888}"/>
   </bookViews>
   <sheets>
     <sheet name="Ronda 1" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,10 @@
     <sheet name="Quarts" sheetId="5" r:id="rId5"/>
     <sheet name="Semi" sheetId="6" r:id="rId6"/>
     <sheet name="Final" sheetId="7" r:id="rId7"/>
-    <sheet name="Resultats" sheetId="8" r:id="rId8"/>
-    <sheet name="Grafics" sheetId="17" r:id="rId9"/>
+    <sheet name="Grafics" sheetId="17" r:id="rId8"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Grafics!$A$1:$H$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ronda 1'!$A$1:$G$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Ronda 2'!$A$1:$G$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Ronda 3'!$A$1:$G$17</definedName>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="258">
   <si>
     <t>Jugador 1</t>
   </si>
@@ -657,27 +657,6 @@
     <t>Iker % acert:</t>
   </si>
   <si>
-    <t>IBM</t>
-  </si>
-  <si>
-    <t>Iker</t>
-  </si>
-  <si>
-    <t>Total  acertats</t>
-  </si>
-  <si>
-    <t>% acertats</t>
-  </si>
-  <si>
-    <t>Iker V2 % acert:</t>
-  </si>
-  <si>
-    <t>Iker V2</t>
-  </si>
-  <si>
-    <t>Iker V3 % acert:</t>
-  </si>
-  <si>
     <t>Iker Winner</t>
   </si>
   <si>
@@ -832,13 +811,25 @@
   </si>
   <si>
     <t>Brier Score Iker:</t>
+  </si>
+  <si>
+    <t>Iker encertats:</t>
+  </si>
+  <si>
+    <t>IBM encertats:</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Diferencia Brier Score</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -874,8 +865,30 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -890,18 +903,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -958,81 +974,66 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thick">
-        <color auto="1"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="thick">
-        <color auto="1"/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1045,21 +1046,56 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" xfId="4"/>
+    <xf numFmtId="10" fontId="7" fillId="5" borderId="5" xfId="4" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="5">
+    <cellStyle name="Bueno" xfId="2" builtinId="26"/>
+    <cellStyle name="Celda de comprobación" xfId="4" builtinId="23"/>
+    <cellStyle name="Incorrecto" xfId="3" builtinId="27"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="71">
+  <dxfs count="57">
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1091,6 +1127,43 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor theme="9" tint="0.39994506668294322"/>
         </patternFill>
       </fill>
@@ -1099,6 +1172,27 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF5050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1300,192 +1394,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF5050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FFFF5050"/>
         </patternFill>
       </fill>
@@ -1641,7 +1549,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -1862,7 +1770,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2494,6 +2402,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="693383296"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -2585,7 +2494,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
+  <c:lang val="es-ES"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2736,7 +2645,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>0.2387</c:v>
+                  <c:v>0.24228281249999994</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0.22245312499999995</c:v>
@@ -4821,7 +4730,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -5138,28 +5047,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{733616C7-25F8-4522-B3D0-0114E321248B}">
   <dimension ref="A1:V65"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="22.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.90625" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="48.36328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.7265625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="15.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="48.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.5" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5182,40 +5091,40 @@
         <v>197</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="R1" s="15" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+        <v>249</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -5283,7 +5192,7 @@
         <v>4.4099999999999986E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -5300,7 +5209,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="str">
-        <f t="shared" ref="F3:H65" si="0">LEFT(IF(C3&gt;D3, A3, B3), FIND(",", IF(C3&gt;D3, A3, B3)) - 1)</f>
+        <f t="shared" ref="F3:F65" si="0">LEFT(IF(C3&gt;D3, A3, B3), FIND(",", IF(C3&gt;D3, A3, B3)) - 1)</f>
         <v>TSENG</v>
       </c>
       <c r="G3">
@@ -5350,7 +5259,7 @@
         <v>0.28090000000000004</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -5375,7 +5284,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="I4">
         <f t="shared" ref="I4:I65" si="10">IF(H4=E4, 1, 0)</f>
@@ -5418,13 +5327,13 @@
         <v>9.0000000000000024E-2</v>
       </c>
       <c r="U4" s="3" t="s">
-        <v>199</v>
+        <v>255</v>
       </c>
       <c r="V4" s="4">
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -5449,7 +5358,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="I5">
         <f t="shared" si="10"/>
@@ -5498,7 +5407,7 @@
         <v>0.578125</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -5565,14 +5474,13 @@
         <v>0.10889999999999997</v>
       </c>
       <c r="U6" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="V6" s="6">
-        <f>58/64</f>
-        <v>0.90625</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>254</v>
+      </c>
+      <c r="V6" s="10">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -5639,14 +5547,14 @@
         <v>0.21159999999999995</v>
       </c>
       <c r="U7" s="5" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="V7" s="6">
         <f>42/64</f>
         <v>0.65625</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>21</v>
       </c>
@@ -5671,7 +5579,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="I8">
         <f t="shared" si="10"/>
@@ -5713,15 +5621,8 @@
         <f t="shared" si="9"/>
         <v>0.43560000000000004</v>
       </c>
-      <c r="U8" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="V8" s="6">
-        <f>41/64</f>
-        <v>0.640625</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="9" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -5788,7 +5689,7 @@
         <v>8.4100000000000022E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>27</v>
       </c>
@@ -5856,14 +5757,14 @@
         <v>7.8400000000000011E-2</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="V10" s="4">
         <f>AVERAGE(R2:R65)</f>
         <v>0.24228281249999994</v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -5931,13 +5832,13 @@
         <v>0.28090000000000004</v>
       </c>
       <c r="U11" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="V11" s="16">
+        <v>253</v>
+      </c>
+      <c r="V11" s="9">
         <v>0.2387</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -6005,7 +5906,7 @@
         <v>0.31360000000000005</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>36</v>
       </c>
@@ -6030,7 +5931,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="I13">
         <f t="shared" si="10"/>
@@ -6072,15 +5973,8 @@
         <f t="shared" si="9"/>
         <v>0.28090000000000004</v>
       </c>
-      <c r="U13">
-        <f>(42/64)*100</f>
-        <v>65.625</v>
-      </c>
-      <c r="V13">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -6148,7 +6042,7 @@
         <v>0.17640000000000003</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -6216,7 +6110,7 @@
         <v>0.16000000000000003</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -6283,7 +6177,7 @@
         <v>0.15210000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -6308,7 +6202,7 @@
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="I17">
         <f t="shared" si="10"/>
@@ -6351,7 +6245,7 @@
         <v>2.5600000000000012E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>51</v>
       </c>
@@ -6419,7 +6313,7 @@
         <v>3.999999999999998E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>54</v>
       </c>
@@ -6487,7 +6381,7 @@
         <v>0.32489999999999997</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>57</v>
       </c>
@@ -6555,7 +6449,7 @@
         <v>0.13689999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>60</v>
       </c>
@@ -6580,7 +6474,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="I21">
         <f t="shared" si="10"/>
@@ -6623,7 +6517,7 @@
         <v>0.27040000000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>63</v>
       </c>
@@ -6690,7 +6584,7 @@
         <v>9.6100000000000033E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>66</v>
       </c>
@@ -6715,7 +6609,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="I23">
         <f t="shared" si="10"/>
@@ -6757,7 +6651,7 @@
         <v>0.53289999999999993</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>69</v>
       </c>
@@ -6824,7 +6718,7 @@
         <v>0.22089999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>72</v>
       </c>
@@ -6891,7 +6785,7 @@
         <v>0.12249999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>75</v>
       </c>
@@ -6959,7 +6853,7 @@
         <v>0.12249999999999998</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>78</v>
       </c>
@@ -7026,7 +6920,7 @@
         <v>0.21159999999999995</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>81</v>
       </c>
@@ -7051,7 +6945,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="I28">
         <f t="shared" si="10"/>
@@ -7093,7 +6987,7 @@
         <v>0.47609999999999991</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>84</v>
       </c>
@@ -7160,7 +7054,7 @@
         <v>0.13689999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>87</v>
       </c>
@@ -7185,7 +7079,7 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="I30">
         <f t="shared" si="10"/>
@@ -7228,7 +7122,7 @@
         <v>0.2601</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>90</v>
       </c>
@@ -7295,7 +7189,7 @@
         <v>0.27040000000000003</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>93</v>
       </c>
@@ -7363,7 +7257,7 @@
         <v>0.23039999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>96</v>
       </c>
@@ -7431,7 +7325,7 @@
         <v>9.0000000000000024E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>99</v>
       </c>
@@ -7498,7 +7392,7 @@
         <v>0.24009999999999998</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>102</v>
       </c>
@@ -7566,7 +7460,7 @@
         <v>0.29160000000000003</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>105</v>
       </c>
@@ -7591,7 +7485,7 @@
         <v>0</v>
       </c>
       <c r="H36" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="I36">
         <f t="shared" si="10"/>
@@ -7633,7 +7527,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>108</v>
       </c>
@@ -7701,7 +7595,7 @@
         <v>0.11559999999999998</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>111</v>
       </c>
@@ -7726,7 +7620,7 @@
         <v>0</v>
       </c>
       <c r="H38" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="I38">
         <f t="shared" si="10"/>
@@ -7769,7 +7663,7 @@
         <v>0.5776</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>114</v>
       </c>
@@ -7794,7 +7688,7 @@
         <v>1</v>
       </c>
       <c r="H39" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="I39">
         <f t="shared" si="10"/>
@@ -7836,7 +7730,7 @@
         <v>0.19359999999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>117</v>
       </c>
@@ -7903,7 +7797,7 @@
         <v>0.23039999999999999</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>120</v>
       </c>
@@ -7928,7 +7822,7 @@
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="I41">
         <f t="shared" si="10"/>
@@ -7970,7 +7864,7 @@
         <v>0.5776</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>123</v>
       </c>
@@ -7995,7 +7889,7 @@
         <v>0</v>
       </c>
       <c r="H42" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="I42">
         <f t="shared" si="10"/>
@@ -8038,7 +7932,7 @@
         <v>0.33639999999999998</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>126</v>
       </c>
@@ -8105,7 +7999,7 @@
         <v>0.24009999999999998</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>129</v>
       </c>
@@ -8172,7 +8066,7 @@
         <v>9.6100000000000033E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>132</v>
       </c>
@@ -8240,7 +8134,7 @@
         <v>0.12249999999999998</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>135</v>
       </c>
@@ -8265,7 +8159,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="I46">
         <f t="shared" si="10"/>
@@ -8307,7 +8201,7 @@
         <v>0.40960000000000002</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>138</v>
       </c>
@@ -8374,7 +8268,7 @@
         <v>6.25E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>141</v>
       </c>
@@ -8441,7 +8335,7 @@
         <v>0.27040000000000003</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>144</v>
       </c>
@@ -8466,7 +8360,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="I49">
         <f t="shared" si="10"/>
@@ -8508,7 +8402,7 @@
         <v>0.59289999999999998</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>147</v>
       </c>
@@ -8533,7 +8427,7 @@
         <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="I50">
         <f t="shared" si="10"/>
@@ -8576,7 +8470,7 @@
         <v>0.75690000000000002</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>150</v>
       </c>
@@ -8644,7 +8538,7 @@
         <v>0.16000000000000003</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>153</v>
       </c>
@@ -8712,7 +8606,7 @@
         <v>0.13689999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>156</v>
       </c>
@@ -8737,7 +8631,7 @@
         <v>0</v>
       </c>
       <c r="H53" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="I53">
         <f t="shared" si="10"/>
@@ -8779,7 +8673,7 @@
         <v>0.42250000000000004</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>159</v>
       </c>
@@ -8847,7 +8741,7 @@
         <v>0.16810000000000003</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>162</v>
       </c>
@@ -8914,7 +8808,7 @@
         <v>8.4100000000000022E-2</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>165</v>
       </c>
@@ -8939,7 +8833,7 @@
         <v>1</v>
       </c>
       <c r="H56" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="I56">
         <f t="shared" si="10"/>
@@ -8982,7 +8876,7 @@
         <v>0.21159999999999995</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>168</v>
       </c>
@@ -9049,7 +8943,7 @@
         <v>9.6100000000000033E-2</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>171</v>
       </c>
@@ -9117,7 +9011,7 @@
         <v>0.1444</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>174</v>
       </c>
@@ -9142,7 +9036,7 @@
         <v>0</v>
       </c>
       <c r="H59" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="I59">
         <f t="shared" si="10"/>
@@ -9184,7 +9078,7 @@
         <v>0.53289999999999993</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>176</v>
       </c>
@@ -9251,7 +9145,7 @@
         <v>0.33639999999999998</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>179</v>
       </c>
@@ -9276,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="H61" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="I61">
         <f t="shared" si="10"/>
@@ -9318,7 +9212,7 @@
         <v>0.38440000000000002</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>182</v>
       </c>
@@ -9385,7 +9279,7 @@
         <v>9.6100000000000033E-2</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>185</v>
       </c>
@@ -9453,7 +9347,7 @@
         <v>0.33639999999999998</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>188</v>
       </c>
@@ -9478,7 +9372,7 @@
         <v>0</v>
       </c>
       <c r="H64" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="I64">
         <f t="shared" si="10"/>
@@ -9521,7 +9415,7 @@
         <v>0.29160000000000003</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>191</v>
       </c>
@@ -9591,30 +9485,30 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:G65" xr:uid="{733616C7-25F8-4522-B3D0-0114E321248B}"/>
-  <conditionalFormatting sqref="G1:G1048576 H1:Q1">
-    <cfRule type="cellIs" dxfId="70" priority="7" operator="equal">
+  <conditionalFormatting sqref="H1:Q1 G1:G1048576">
+    <cfRule type="cellIs" dxfId="56" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="69" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="55" priority="8" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I65">
-    <cfRule type="cellIs" dxfId="68" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="54" priority="5" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="67" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="53" priority="6" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L65">
-    <cfRule type="containsText" dxfId="66" priority="2" operator="containsText" text="Perdem">
+    <cfRule type="containsText" dxfId="52" priority="2" operator="containsText" text="Perdem">
       <formula>NOT(ISERROR(SEARCH("Perdem",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="65" priority="3" operator="containsText" text="Guanyem">
+    <cfRule type="containsText" dxfId="51" priority="3" operator="containsText" text="Guanyem">
       <formula>NOT(ISERROR(SEARCH("Guanyem",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="64" priority="4" operator="containsText" text="Empat">
+    <cfRule type="containsText" dxfId="50" priority="4" operator="containsText" text="Empat">
       <formula>NOT(ISERROR(SEARCH("Empat",L2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9638,24 +9532,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA468E2B-B98F-49D5-BB7C-817B60D20F6A}">
   <dimension ref="A1:V33"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7265625" customWidth="1"/>
-    <col min="10" max="11" width="22.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.90625" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="15.6328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="39.453125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" customWidth="1"/>
+    <col min="10" max="11" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="39.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="1" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:22" s="1" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9675,43 +9569,43 @@
         <v>198</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="R1" s="15" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+        <v>249</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>182</v>
       </c>
@@ -9728,7 +9622,7 @@
         <v>187</v>
       </c>
       <c r="F2" t="str">
-        <f t="shared" ref="F2:H33" si="0">LEFT(IF(C2&gt;D2, A2, B2), FIND(",", IF(C2&gt;D2, A2, B2)) - 1)</f>
+        <f t="shared" ref="F2:F33" si="0">LEFT(IF(C2&gt;D2, A2, B2), FIND(",", IF(C2&gt;D2, A2, B2)) - 1)</f>
         <v>AUGER-ALIASSIME</v>
       </c>
       <c r="G2">
@@ -9778,13 +9672,13 @@
         <v>0.51839999999999997</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>199</v>
+        <v>255</v>
       </c>
       <c r="V2" s="4">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>124</v>
       </c>
@@ -9858,7 +9752,7 @@
         <v>0.6875</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>63</v>
       </c>
@@ -9925,14 +9819,13 @@
         <v>6.25E-2</v>
       </c>
       <c r="U4" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="V4" s="6">
-        <f>27/32</f>
-        <v>0.84375</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>254</v>
+      </c>
+      <c r="V4" s="11">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>75</v>
       </c>
@@ -10000,14 +9893,14 @@
         <v>0.10239999999999996</v>
       </c>
       <c r="U5" s="5" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="V5" s="6">
         <f>23/32</f>
         <v>0.71875</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -10073,15 +9966,8 @@
         <f t="shared" si="9"/>
         <v>0.22089999999999999</v>
       </c>
-      <c r="U6" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="V6" s="6">
-        <f>22/32</f>
-        <v>0.6875</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>51</v>
       </c>
@@ -10149,7 +10035,7 @@
         <v>0.72249999999999992</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>93</v>
       </c>
@@ -10216,8 +10102,15 @@
         <f t="shared" si="9"/>
         <v>1.6900000000000002E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="U8" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="V8" s="4">
+        <f>AVERAGE(R2:R33)</f>
+        <v>0.22245312499999995</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>112</v>
       </c>
@@ -10284,15 +10177,14 @@
         <f t="shared" si="9"/>
         <v>5.7599999999999998E-2</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="V9" s="4">
-        <f>AVERAGE(R2:R33)</f>
-        <v>0.22245312499999995</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="U9" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="V9" s="9">
+        <v>0.2185</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>154</v>
       </c>
@@ -10359,14 +10251,8 @@
         <f t="shared" si="9"/>
         <v>0.13689999999999999</v>
       </c>
-      <c r="U10" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="V10" s="16">
-        <v>0.2387</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>99</v>
       </c>
@@ -10434,7 +10320,7 @@
         <v>7.8400000000000011E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>34</v>
       </c>
@@ -10501,7 +10387,7 @@
         <v>0.39690000000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>141</v>
       </c>
@@ -10568,7 +10454,7 @@
         <v>0.22089999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>69</v>
       </c>
@@ -10635,7 +10521,7 @@
         <v>0.15210000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>82</v>
       </c>
@@ -10702,7 +10588,7 @@
         <v>0.51839999999999997</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>148</v>
       </c>
@@ -10769,7 +10655,7 @@
         <v>0.38440000000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>88</v>
       </c>
@@ -10837,7 +10723,7 @@
         <v>0.1444</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>159</v>
       </c>
@@ -10905,7 +10791,7 @@
         <v>0.31360000000000005</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>136</v>
       </c>
@@ -10972,7 +10858,7 @@
         <v>0.33639999999999998</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>176</v>
       </c>
@@ -11039,7 +10925,7 @@
         <v>0.33639999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>58</v>
       </c>
@@ -11106,7 +10992,7 @@
         <v>0.17640000000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -11173,7 +11059,7 @@
         <v>0.20249999999999996</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>129</v>
       </c>
@@ -11241,7 +11127,7 @@
         <v>0.13689999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -11308,7 +11194,7 @@
         <v>0.20249999999999996</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>165</v>
       </c>
@@ -11375,7 +11261,7 @@
         <v>0.39690000000000003</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>21</v>
       </c>
@@ -11442,7 +11328,7 @@
         <v>0.53289999999999993</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>171</v>
       </c>
@@ -11510,7 +11396,7 @@
         <v>5.2899999999999989E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>27</v>
       </c>
@@ -11578,7 +11464,7 @@
         <v>0.10239999999999996</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>3</v>
       </c>
@@ -11645,7 +11531,7 @@
         <v>9.999999999999995E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>46</v>
       </c>
@@ -11713,7 +11599,7 @@
         <v>0.12249999999999998</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>188</v>
       </c>
@@ -11781,7 +11667,7 @@
         <v>3.6000000000000064E-3</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>118</v>
       </c>
@@ -11849,7 +11735,7 @@
         <v>0.22089999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>106</v>
       </c>
@@ -11924,37 +11810,37 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="G2:G33">
-    <cfRule type="cellIs" dxfId="63" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="49" priority="11" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="62" priority="12" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J1:P1">
-    <cfRule type="cellIs" dxfId="61" priority="9" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="60" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="48" priority="12" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I33">
-    <cfRule type="cellIs" dxfId="59" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="58" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="46" priority="8" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J1:Q1">
+    <cfRule type="cellIs" dxfId="45" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="44" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L33">
-    <cfRule type="containsText" dxfId="57" priority="4" operator="containsText" text="Perdem">
+    <cfRule type="containsText" dxfId="43" priority="4" operator="containsText" text="Perdem">
       <formula>NOT(ISERROR(SEARCH("Perdem",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="56" priority="5" operator="containsText" text="Guanyem">
+    <cfRule type="containsText" dxfId="42" priority="5" operator="containsText" text="Guanyem">
       <formula>NOT(ISERROR(SEARCH("Guanyem",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="55" priority="6" operator="containsText" text="Empat">
+    <cfRule type="containsText" dxfId="41" priority="6" operator="containsText" text="Empat">
       <formula>NOT(ISERROR(SEARCH("Empat",L2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11970,14 +11856,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q1">
-    <cfRule type="cellIs" dxfId="52" priority="1" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="51" priority="2" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -11985,26 +11863,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACEA3751-FF78-4C3C-8ABE-F983B99484C6}">
   <dimension ref="A1:Y17"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="22.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.90625" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="26" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12024,43 +11902,43 @@
         <v>198</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="R1" s="15" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+        <v>249</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -12128,7 +12006,7 @@
         <v>2.2500000000000006E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -12145,7 +12023,7 @@
         <v>17</v>
       </c>
       <c r="F3" t="str">
-        <f t="shared" ref="F3:H17" si="2">LEFT(IF(C3&gt;D3, A3, B3), FIND(",", IF(C3&gt;D3, A3, B3)) - 1)</f>
+        <f t="shared" ref="F3:F17" si="2">LEFT(IF(C3&gt;D3, A3, B3), FIND(",", IF(C3&gt;D3, A3, B3)) - 1)</f>
         <v>DIMITROV</v>
       </c>
       <c r="G3">
@@ -12195,7 +12073,7 @@
         <v>9.0000000000000024E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>27</v>
       </c>
@@ -12263,7 +12141,7 @@
         <v>0.10239999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -12330,13 +12208,13 @@
         <v>0.2601</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>199</v>
+        <v>255</v>
       </c>
       <c r="Y5" s="4">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>55</v>
       </c>
@@ -12410,7 +12288,7 @@
         <v>0.6875</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>63</v>
       </c>
@@ -12477,14 +12355,13 @@
         <v>0.33639999999999998</v>
       </c>
       <c r="X7" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="Y7" s="6">
-        <f>15/16</f>
-        <v>0.9375</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>254</v>
+      </c>
+      <c r="Y7" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>75</v>
       </c>
@@ -12551,14 +12428,14 @@
         <v>7.8400000000000011E-2</v>
       </c>
       <c r="X8" s="5" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="Y8" s="6">
         <f>12/16</f>
         <v>0.75</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>88</v>
       </c>
@@ -12625,15 +12502,8 @@
         <f t="shared" si="12"/>
         <v>5.2899999999999989E-2</v>
       </c>
-      <c r="X9" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="Y9" s="6">
-        <f>12/16</f>
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="10" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>99</v>
       </c>
@@ -12701,7 +12571,7 @@
         <v>0.12249999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>114</v>
       </c>
@@ -12715,7 +12585,7 @@
         <v>48</v>
       </c>
       <c r="E11" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="F11" t="str">
         <f t="shared" si="2"/>
@@ -12726,7 +12596,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="I11">
         <f t="shared" si="4"/>
@@ -12768,14 +12638,14 @@
         <v>0.27040000000000003</v>
       </c>
       <c r="X11" s="3" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="Y11" s="4">
         <f>AVERAGE(R2:R17)</f>
         <v>0.18175624999999995</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:25" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>124</v>
       </c>
@@ -12842,13 +12712,13 @@
         <v>0.23039999999999999</v>
       </c>
       <c r="X12" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="Y12" s="16">
-        <v>0.2387</v>
-      </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+        <v>253</v>
+      </c>
+      <c r="Y12" s="9">
+        <v>0.1578</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>136</v>
       </c>
@@ -12916,7 +12786,7 @@
         <v>0.18490000000000004</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>148</v>
       </c>
@@ -12984,7 +12854,7 @@
         <v>0.42250000000000004</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>162</v>
       </c>
@@ -13051,7 +12921,7 @@
         <v>0.31360000000000005</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>171</v>
       </c>
@@ -13119,7 +12989,7 @@
         <v>8.4100000000000022E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>185</v>
       </c>
@@ -13194,37 +13064,37 @@
     </sortState>
   </autoFilter>
   <conditionalFormatting sqref="G2:G17">
-    <cfRule type="cellIs" dxfId="50" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="40" priority="11" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="49" priority="12" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J1:P1">
-    <cfRule type="cellIs" dxfId="48" priority="9" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="47" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="39" priority="12" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I17">
-    <cfRule type="cellIs" dxfId="46" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="8" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J1:Q1">
+    <cfRule type="cellIs" dxfId="36" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="35" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L17">
-    <cfRule type="containsText" dxfId="44" priority="4" operator="containsText" text="Perdem">
+    <cfRule type="containsText" dxfId="34" priority="4" operator="containsText" text="Perdem">
       <formula>NOT(ISERROR(SEARCH("Perdem",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="43" priority="5" operator="containsText" text="Guanyem">
+    <cfRule type="containsText" dxfId="33" priority="5" operator="containsText" text="Guanyem">
       <formula>NOT(ISERROR(SEARCH("Guanyem",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="42" priority="6" operator="containsText" text="Empat">
+    <cfRule type="containsText" dxfId="32" priority="6" operator="containsText" text="Empat">
       <formula>NOT(ISERROR(SEARCH("Empat",L2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13240,14 +13110,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q1">
-    <cfRule type="cellIs" dxfId="41" priority="1" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="40" priority="2" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13255,22 +13117,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7B8FC45-B22C-4AD5-9F0B-B6BE598565A3}">
   <dimension ref="A1:W10"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="24.6328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13293,40 +13155,40 @@
         <v>197</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="R1" s="15" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>249</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -13394,7 +13256,7 @@
         <v>1.9600000000000003E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -13461,13 +13323,13 @@
         <v>0.13689999999999999</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>199</v>
+        <v>255</v>
       </c>
       <c r="W3" s="4">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:23" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>55</v>
       </c>
@@ -13541,7 +13403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:23" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>75</v>
       </c>
@@ -13608,14 +13470,13 @@
         <v>8.4100000000000022E-2</v>
       </c>
       <c r="V5" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="W5" s="6">
-        <f>7/8</f>
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+        <v>254</v>
+      </c>
+      <c r="W5" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>99</v>
       </c>
@@ -13682,14 +13543,14 @@
         <v>5.2899999999999989E-2</v>
       </c>
       <c r="V6" s="5" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="W6" s="6">
         <f>6/8</f>
         <v>0.75</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>133</v>
       </c>
@@ -13755,15 +13616,8 @@
         <f t="shared" si="12"/>
         <v>0.10239999999999996</v>
       </c>
-      <c r="V7" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="W7" s="6">
-        <f>7/8</f>
-        <v>0.875</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    </row>
+    <row r="8" spans="1:23" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>148</v>
       </c>
@@ -13830,7 +13684,7 @@
         <v>0.16810000000000003</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>171</v>
       </c>
@@ -13898,51 +13752,51 @@
         <v>6.25E-2</v>
       </c>
       <c r="V9" s="3" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="W9" s="4">
         <f>AVERAGE(R2:R9)</f>
         <v>9.1112499999999999E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:23" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="V10" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="W10" s="16">
-        <v>0.2387</v>
+        <v>253</v>
+      </c>
+      <c r="W10" s="9">
+        <v>0.13400000000000001</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G9">
-    <cfRule type="cellIs" dxfId="39" priority="11" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J1:P1">
-    <cfRule type="cellIs" dxfId="38" priority="9" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="11" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I9">
-    <cfRule type="cellIs" dxfId="36" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="30" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="29" priority="8" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J1:Q1">
+    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="27" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L9">
-    <cfRule type="containsText" dxfId="34" priority="4" operator="containsText" text="Perdem">
+    <cfRule type="containsText" dxfId="26" priority="4" operator="containsText" text="Perdem">
       <formula>NOT(ISERROR(SEARCH("Perdem",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="33" priority="5" operator="containsText" text="Guanyem">
+    <cfRule type="containsText" dxfId="25" priority="5" operator="containsText" text="Guanyem">
       <formula>NOT(ISERROR(SEARCH("Guanyem",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="32" priority="6" operator="containsText" text="Empat">
+    <cfRule type="containsText" dxfId="24" priority="6" operator="containsText" text="Empat">
       <formula>NOT(ISERROR(SEARCH("Empat",L2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13958,14 +13812,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q1">
-    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="2" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -13973,27 +13819,27 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B426FC20-F2D4-42EE-B26E-57F7A91BDF6D}">
   <dimension ref="A1:X11"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="22.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.90625" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="15.6328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="19.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14016,40 +13862,40 @@
         <v>197</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="R1" s="15" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+        <v>249</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -14116,7 +13962,7 @@
         <v>4.4099999999999986E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>63</v>
       </c>
@@ -14183,7 +14029,7 @@
         <v>7.8400000000000011E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>133</v>
       </c>
@@ -14257,7 +14103,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>192</v>
       </c>
@@ -14331,81 +14177,72 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="W6" s="5" t="s">
-        <v>201</v>
+        <v>254</v>
       </c>
       <c r="X6" s="6">
         <f>4/4</f>
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="W7" s="5" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="X7" s="6">
         <f>4/4</f>
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="W8" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="X8" s="6">
-        <f>4/4</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:24" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="W10" s="3" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="X10" s="4">
         <f>AVERAGE(R2:R5)</f>
         <v>6.3750000000000001E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:24" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="W11" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="X11" s="16">
-        <v>0.2387</v>
+        <v>253</v>
+      </c>
+      <c r="X11" s="9">
+        <v>3.8399999999999997E-2</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G5">
-    <cfRule type="cellIs" dxfId="29" priority="11" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J1:P1">
-    <cfRule type="cellIs" dxfId="28" priority="9" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="27" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="11" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I5">
-    <cfRule type="cellIs" dxfId="26" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="25" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="8" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J1:Q1">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L5">
-    <cfRule type="containsText" dxfId="24" priority="4" operator="containsText" text="Perdem">
+    <cfRule type="containsText" dxfId="18" priority="4" operator="containsText" text="Perdem">
       <formula>NOT(ISERROR(SEARCH("Perdem",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="23" priority="5" operator="containsText" text="Guanyem">
+    <cfRule type="containsText" dxfId="17" priority="5" operator="containsText" text="Guanyem">
       <formula>NOT(ISERROR(SEARCH("Guanyem",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="22" priority="6" operator="containsText" text="Empat">
+    <cfRule type="containsText" dxfId="16" priority="6" operator="containsText" text="Empat">
       <formula>NOT(ISERROR(SEARCH("Empat",L2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14421,14 +14258,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q1">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14436,21 +14265,21 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F3217C8-0180-4F68-B33D-869F44F7E5B7}">
   <dimension ref="A1:V13"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.54296875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14473,40 +14302,40 @@
         <v>197</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="R1" s="15" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+        <v>249</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -14574,7 +14403,7 @@
         <v>0.17640000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>192</v>
       </c>
@@ -14641,8 +14470,8 @@
         <v>0.16000000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="U7" s="3" t="s">
         <v>199</v>
       </c>
@@ -14650,7 +14479,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="U8" s="5" t="s">
         <v>200</v>
       </c>
@@ -14659,72 +14488,71 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="U9" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="V9" s="10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="U10" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="V9" s="6">
-        <f>2/2</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="U10" s="5" t="s">
-        <v>206</v>
       </c>
       <c r="V10" s="6">
         <f>2/2</f>
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="U12" s="3" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="V12" s="4">
         <f>AVERAGE(R2:R3)</f>
         <v>0.16820000000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:22" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="U13" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="V13" s="16">
-        <v>0.2387</v>
+        <v>253</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0.1293</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2:G3">
-    <cfRule type="cellIs" dxfId="21" priority="11" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J1:P1">
-    <cfRule type="cellIs" dxfId="20" priority="9" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="19" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="11" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I3">
-    <cfRule type="cellIs" dxfId="18" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="8" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J1:Q1">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L3">
-    <cfRule type="containsText" dxfId="16" priority="4" operator="containsText" text="Perdem">
+    <cfRule type="containsText" dxfId="10" priority="4" operator="containsText" text="Perdem">
       <formula>NOT(ISERROR(SEARCH("Perdem",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="15" priority="5" operator="containsText" text="Guanyem">
+    <cfRule type="containsText" dxfId="9" priority="5" operator="containsText" text="Guanyem">
       <formula>NOT(ISERROR(SEARCH("Guanyem",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="6" operator="containsText" text="Empat">
+    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="Empat">
       <formula>NOT(ISERROR(SEARCH("Empat",L2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14740,14 +14568,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q1">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14755,27 +14575,27 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{290BA5AE-209F-4B33-912E-0B335547B6EF}">
   <dimension ref="A1:W10"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.26953125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.1796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="22.54296875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="25.81640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.90625" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="15.6328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="17.54296875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.90625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="7.83203125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14798,40 +14618,40 @@
         <v>197</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="R1" s="15" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+        <v>249</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -14899,8 +14719,8 @@
         <v>0.22089999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:23" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="V4" s="3" t="s">
         <v>199</v>
       </c>
@@ -14908,7 +14728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:23" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="V5" s="5" t="s">
         <v>200</v>
       </c>
@@ -14917,72 +14737,72 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:23" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="V6" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="W6" s="6">
+        <v>254</v>
+      </c>
+      <c r="W6" s="10">
         <f>0/1</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:23" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="V7" s="5" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="W7" s="6">
         <f>0/1</f>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:23" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="V9" s="3" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="W9" s="4">
         <f>AVERAGE(R2:R2)</f>
         <v>0.22089999999999999</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:23" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="V10" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="W10" s="16">
-        <v>0.2387</v>
+        <v>253</v>
+      </c>
+      <c r="W10" s="9">
+        <v>0.32269999999999999</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="G2">
-    <cfRule type="cellIs" dxfId="13" priority="11" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J1:P1">
-    <cfRule type="cellIs" dxfId="12" priority="9" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="11" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2">
-    <cfRule type="cellIs" dxfId="10" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J1:Q1">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2">
-    <cfRule type="containsText" dxfId="8" priority="4" operator="containsText" text="Perdem">
+    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="Perdem">
       <formula>NOT(ISERROR(SEARCH("Perdem",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="Guanyem">
+    <cfRule type="containsText" dxfId="1" priority="5" operator="containsText" text="Guanyem">
       <formula>NOT(ISERROR(SEARCH("Guanyem",L2)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="6" operator="containsText" text="Empat">
+    <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="Empat">
       <formula>NOT(ISERROR(SEARCH("Empat",L2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -14998,123 +14818,53 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q1">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>0</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03439C7F-BE26-46C4-AF78-BFBDE843F874}">
-  <dimension ref="B1:J11"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2770F40-497A-498C-ABFF-A4B16B10C6BF}">
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="8" max="8" width="7.81640625" customWidth="1"/>
-    <col min="9" max="9" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B1" s="7"/>
-    </row>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B2" s="7"/>
-    </row>
-    <row r="8" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="H8" s="8"/>
-      <c r="I8" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="H9" s="13" t="s">
-        <v>202</v>
-      </c>
-      <c r="I9" s="11">
-        <v>85</v>
-      </c>
-      <c r="J9" s="12">
-        <f>I9/127</f>
-        <v>0.6692913385826772</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="H10" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="I10" s="10">
-        <v>113</v>
-      </c>
-      <c r="J10" s="9">
-        <f>I10/127</f>
-        <v>0.88976377952755903</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="H11" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="I11" s="10">
-        <v>89</v>
-      </c>
-      <c r="J11" s="9">
-        <f>I11/127</f>
-        <v>0.70078740157480313</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2770F40-497A-498C-ABFF-A4B16B10C6BF}">
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="13.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="20.1796875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
+        <v>236</v>
+      </c>
+      <c r="B1" s="17" t="s">
         <v>243</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="17" t="s">
+        <v>244</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="F1" s="17" t="s">
         <v>251</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G1" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B2">
         <v>37</v>
@@ -15131,15 +14881,19 @@
         <v>0.65625</v>
       </c>
       <c r="F2">
-        <v>0.2387</v>
+        <v>0.24228281249999994</v>
       </c>
       <c r="G2">
         <v>0.2387</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H2" s="14">
+        <f>G2-F2</f>
+        <v>-3.5828124999999489E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B3">
         <v>22</v>
@@ -15161,10 +14915,14 @@
       <c r="G3">
         <v>0.2185</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H3" s="14">
+        <f t="shared" ref="H3:H8" si="0">G3-F3</f>
+        <v>-3.9531249999999463E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B4">
         <v>11</v>
@@ -15186,10 +14944,14 @@
       <c r="G4">
         <v>0.1578</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H4" s="14">
+        <f t="shared" si="0"/>
+        <v>-2.3956249999999957E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B5">
         <v>8</v>
@@ -15211,10 +14973,14 @@
       <c r="G5">
         <v>0.13400000000000001</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H5" s="15">
+        <f t="shared" si="0"/>
+        <v>4.2887500000000009E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B6">
         <v>4</v>
@@ -15236,10 +15002,14 @@
       <c r="G6">
         <v>3.8399999999999997E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H6" s="14">
+        <f t="shared" si="0"/>
+        <v>-2.5350000000000004E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B7">
         <v>2</v>
@@ -15261,10 +15031,14 @@
       <c r="G7">
         <v>0.1293</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H7" s="14">
+        <f t="shared" si="0"/>
+        <v>-3.8900000000000018E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -15286,8 +15060,47 @@
       <c r="G8">
         <v>0.32269999999999999</v>
       </c>
-    </row>
+      <c r="H8" s="15">
+        <f t="shared" si="0"/>
+        <v>0.1018</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="B9" s="12">
+        <f>SUM(B2:B8)</f>
+        <v>85</v>
+      </c>
+      <c r="C9" s="12">
+        <f>SUM(C2:C8)</f>
+        <v>89</v>
+      </c>
+      <c r="D9" s="13">
+        <f>B9/127</f>
+        <v>0.6692913385826772</v>
+      </c>
+      <c r="E9" s="13">
+        <f>C9/127</f>
+        <v>0.70078740157480313</v>
+      </c>
+      <c r="F9" s="12">
+        <f>AVERAGE(F2:F8)</f>
+        <v>0.17006495535714286</v>
+      </c>
+      <c r="G9" s="12">
+        <f>AVERAGE(G2:G8)</f>
+        <v>0.17705714285714283</v>
+      </c>
+      <c r="H9" s="12">
+        <f>AVERAGE(H2:H8)</f>
+        <v>6.9921875000000192E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="16" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
+  <autoFilter ref="A1:H1" xr:uid="{D2770F40-497A-498C-ABFF-A4B16B10C6BF}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/ResultatWimbeldon.xlsx
+++ b/ResultatWimbeldon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/iker/Code/TFG/Me-vs.-IBM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07BAC0F2-BEEA-954E-A5BC-9BE9E91E2341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0807D231-3ED1-D243-86D1-0144693EA0E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38400" yWindow="620" windowWidth="38400" windowHeight="20980" xr2:uid="{0ED45994-5EFE-4A4E-8BA9-C3AA32741888}"/>
+    <workbookView xWindow="38400" yWindow="620" windowWidth="38400" windowHeight="20980" activeTab="7" xr2:uid="{0ED45994-5EFE-4A4E-8BA9-C3AA32741888}"/>
   </bookViews>
   <sheets>
     <sheet name="Ronda 1" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="259">
   <si>
     <t>Jugador 1</t>
   </si>
@@ -823,6 +823,9 @@
   </si>
   <si>
     <t>Diferencia Brier Score</t>
+  </si>
+  <si>
+    <t>% Encert</t>
   </si>
 </sst>
 </file>
@@ -917,7 +920,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -988,43 +991,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1033,7 +999,7 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1054,9 +1020,8 @@
     <xf numFmtId="10" fontId="7" fillId="5" borderId="5" xfId="4" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Bueno" xfId="2" builtinId="26"/>
@@ -1547,227 +1512,6 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="693340096"/>
-        <c:axId val="693327136"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="693340096"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="693327136"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="693327136"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="693340096"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="es-ES"/>
@@ -2491,7 +2235,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="es-ES"/>
@@ -3062,46 +2806,6 @@
 </cs:colorStyle>
 </file>
 
-<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -3606,509 +3310,6 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -4615,47 +3816,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>367393</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>11794</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>984250</xdr:colOff>
-      <xdr:row>80</xdr:row>
-      <xdr:rowOff>33565</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Chart 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B2E80DA1-27BE-9393-BECF-8BC8B2B153E8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>790575</xdr:colOff>
       <xdr:row>13</xdr:row>
@@ -4698,7 +3858,7 @@
       <xdr:rowOff>172322</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>184896</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>114051</xdr:rowOff>
@@ -9525,7 +8685,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -14824,7 +13983,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2770F40-497A-498C-ABFF-A4B16B10C6BF}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.1640625" bestFit="1" customWidth="1"/>
@@ -14834,10 +13993,11 @@
     <col min="5" max="5" width="18.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="20.1640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="17" t="s">
         <v>236</v>
       </c>
       <c r="B1" s="17" t="s">
@@ -14858,11 +14018,14 @@
       <c r="G1" s="17" t="s">
         <v>248</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="H1" s="17" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I1" s="16" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>237</v>
       </c>
@@ -14890,8 +14053,12 @@
         <f>G2-F2</f>
         <v>-3.5828124999999489E-3</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I2" s="7">
+        <f>AVERAGE('Ronda 1'!M2:M65)</f>
+        <v>5.2480968750000009E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>238</v>
       </c>
@@ -14919,8 +14086,12 @@
         <f t="shared" ref="H3:H8" si="0">G3-F3</f>
         <v>-3.9531249999999463E-3</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I3" s="7">
+        <f>AVERAGE('Ronda 2'!M2:M33)</f>
+        <v>2.047212499999999E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>239</v>
       </c>
@@ -14948,8 +14119,12 @@
         <f t="shared" si="0"/>
         <v>-2.3956249999999957E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I4" s="7">
+        <f>AVERAGE('Ronda 3'!M2:M17)</f>
+        <v>6.5845062499999996E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>240</v>
       </c>
@@ -14977,8 +14152,12 @@
         <f t="shared" si="0"/>
         <v>4.2887500000000009E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I5" s="7">
+        <f>AVERAGE('Ronda 4'!M5:M68)</f>
+        <v>5.5384999999999976E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>241</v>
       </c>
@@ -15006,8 +14185,12 @@
         <f t="shared" si="0"/>
         <v>-2.5350000000000004E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="16" x14ac:dyDescent="0.2">
+      <c r="I6" s="7">
+        <f>AVERAGE(Quarts!M2:M5)</f>
+        <v>6.2348749999999981E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>245</v>
       </c>
@@ -15035,8 +14218,12 @@
         <f t="shared" si="0"/>
         <v>-3.8900000000000018E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="I7" s="7">
+        <f>AVERAGE(Semi!M2:M3)</f>
+        <v>7.6527500000000026E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>242</v>
       </c>
@@ -15064,8 +14251,12 @@
         <f t="shared" si="0"/>
         <v>0.1018</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="I8" s="7">
+        <f>AVERAGE(Final!M2)</f>
+        <v>-9.8088999999999982E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
         <v>256</v>
       </c>
@@ -15097,11 +14288,27 @@
         <f>AVERAGE(H2:H8)</f>
         <v>6.9921875000000192E-3</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="16" thickTop="1" x14ac:dyDescent="0.2"/>
+      <c r="I9" s="13">
+        <f t="shared" ref="I9" si="1">AVERAGE(I2:I8)</f>
+        <v>3.3567200892857148E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="16" thickTop="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <autoFilter ref="A1:H1" xr:uid="{D2770F40-497A-498C-ABFF-A4B16B10C6BF}"/>
   <phoneticPr fontId="3" type="noConversion"/>
+  <conditionalFormatting sqref="I2:I8">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
